--- a/光伏配储项目/电价数据/2026/兆丰站.xlsx
+++ b/光伏配储项目/电价数据/2026/兆丰站.xlsx
@@ -16,10 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="yyyy/mm/dd"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -64,7 +63,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,13 +429,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CS116"/>
+  <dimension ref="A1:CS143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>日期</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -34613,6 +34612,7917 @@
       </c>
       <c r="CS116" t="n">
         <v>0.54375</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>46138</v>
+      </c>
+      <c r="B117" t="n">
+        <v>0.38463</v>
+      </c>
+      <c r="C117" t="n">
+        <v>0.7680900000000001</v>
+      </c>
+      <c r="D117" t="n">
+        <v>0.61178</v>
+      </c>
+      <c r="E117" t="n">
+        <v>0.59333</v>
+      </c>
+      <c r="F117" t="n">
+        <v>0.54031</v>
+      </c>
+      <c r="G117" t="n">
+        <v>0.55538</v>
+      </c>
+      <c r="H117" t="n">
+        <v>0.44285</v>
+      </c>
+      <c r="I117" t="n">
+        <v>0.46056</v>
+      </c>
+      <c r="J117" t="n">
+        <v>0.43233</v>
+      </c>
+      <c r="K117" t="n">
+        <v>0.42721</v>
+      </c>
+      <c r="L117" t="n">
+        <v>0.42594</v>
+      </c>
+      <c r="M117" t="n">
+        <v>0.41353</v>
+      </c>
+      <c r="N117" t="n">
+        <v>0.40099</v>
+      </c>
+      <c r="O117" t="n">
+        <v>0.40038</v>
+      </c>
+      <c r="P117" t="n">
+        <v>0.38823</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>0.40527</v>
+      </c>
+      <c r="R117" t="n">
+        <v>0.42881</v>
+      </c>
+      <c r="S117" t="n">
+        <v>0.41726</v>
+      </c>
+      <c r="T117" t="n">
+        <v>0.35583</v>
+      </c>
+      <c r="U117" t="n">
+        <v>0.39514</v>
+      </c>
+      <c r="V117" t="n">
+        <v>0.38826</v>
+      </c>
+      <c r="W117" t="n">
+        <v>0.42108</v>
+      </c>
+      <c r="X117" t="n">
+        <v>0.39551</v>
+      </c>
+      <c r="Y117" t="n">
+        <v>0.42497</v>
+      </c>
+      <c r="Z117" t="n">
+        <v>0.41795</v>
+      </c>
+      <c r="AA117" t="n">
+        <v>0.42816</v>
+      </c>
+      <c r="AB117" t="n">
+        <v>0.41564</v>
+      </c>
+      <c r="AC117" t="n">
+        <v>0.44805</v>
+      </c>
+      <c r="AD117" t="n">
+        <v>0.5028</v>
+      </c>
+      <c r="AE117" t="n">
+        <v>0.30003</v>
+      </c>
+      <c r="AF117" t="n">
+        <v>0.40123</v>
+      </c>
+      <c r="AG117" t="n">
+        <v>0.30827</v>
+      </c>
+      <c r="AH117" t="n">
+        <v>0.31212</v>
+      </c>
+      <c r="AI117" t="n">
+        <v>0.32842</v>
+      </c>
+      <c r="AJ117" t="n">
+        <v>0.35162</v>
+      </c>
+      <c r="AK117" t="n">
+        <v>0.3758</v>
+      </c>
+      <c r="AL117" t="n">
+        <v>0.32322</v>
+      </c>
+      <c r="AM117" t="n">
+        <v>0.35011</v>
+      </c>
+      <c r="AN117" t="n">
+        <v>0.12534</v>
+      </c>
+      <c r="AO117" t="n">
+        <v>0.13808</v>
+      </c>
+      <c r="AP117" t="n">
+        <v>0.27702</v>
+      </c>
+      <c r="AQ117" t="n">
+        <v>0.14404</v>
+      </c>
+      <c r="AR117" t="n">
+        <v>0.07762000000000001</v>
+      </c>
+      <c r="AS117" t="n">
+        <v>0.11692</v>
+      </c>
+      <c r="AT117" t="n">
+        <v>0.26247</v>
+      </c>
+      <c r="AU117" t="n">
+        <v>0.16579</v>
+      </c>
+      <c r="AV117" t="n">
+        <v>0.31196</v>
+      </c>
+      <c r="AW117" t="n">
+        <v>0.28739</v>
+      </c>
+      <c r="AX117" t="n">
+        <v>0.05213</v>
+      </c>
+      <c r="AY117" t="n">
+        <v>0.86276</v>
+      </c>
+      <c r="AZ117" t="n">
+        <v>1.3587</v>
+      </c>
+      <c r="BA117" t="n">
+        <v>0.14834</v>
+      </c>
+      <c r="BB117" t="n">
+        <v>0.21828</v>
+      </c>
+      <c r="BC117" t="n">
+        <v>0.23026</v>
+      </c>
+      <c r="BD117" t="n">
+        <v>0.23606</v>
+      </c>
+      <c r="BE117" t="n">
+        <v>0.21942</v>
+      </c>
+      <c r="BF117" t="n">
+        <v>0.76351</v>
+      </c>
+      <c r="BG117" t="n">
+        <v>0.12714</v>
+      </c>
+      <c r="BH117" t="n">
+        <v>0.44628</v>
+      </c>
+      <c r="BI117" t="n">
+        <v>0.15168</v>
+      </c>
+      <c r="BJ117" t="n">
+        <v>0.33767</v>
+      </c>
+      <c r="BK117" t="n">
+        <v>0.35065</v>
+      </c>
+      <c r="BL117" t="n">
+        <v>0.2921</v>
+      </c>
+      <c r="BM117" t="n">
+        <v>0.27598</v>
+      </c>
+      <c r="BN117" t="n">
+        <v>0.30636</v>
+      </c>
+      <c r="BO117" t="n">
+        <v>0.52227</v>
+      </c>
+      <c r="BP117" t="n">
+        <v>0.61773</v>
+      </c>
+      <c r="BQ117" t="n">
+        <v>0.5122899999999999</v>
+      </c>
+      <c r="BR117" t="n">
+        <v>0.7321299999999999</v>
+      </c>
+      <c r="BS117" t="n">
+        <v>1.07767</v>
+      </c>
+      <c r="BT117" t="n">
+        <v>0.39473</v>
+      </c>
+      <c r="BU117" t="n">
+        <v>0.92662</v>
+      </c>
+      <c r="BV117" t="n">
+        <v>0.43179</v>
+      </c>
+      <c r="BW117" t="n">
+        <v>0.4367</v>
+      </c>
+      <c r="BX117" t="n">
+        <v>0.65879</v>
+      </c>
+      <c r="BY117" t="n">
+        <v>0.8171799999999999</v>
+      </c>
+      <c r="BZ117" t="n">
+        <v>0.42584</v>
+      </c>
+      <c r="CA117" t="n">
+        <v>1.15309</v>
+      </c>
+      <c r="CB117" t="n">
+        <v>1.25317</v>
+      </c>
+      <c r="CC117" t="n">
+        <v>0.98117</v>
+      </c>
+      <c r="CD117" t="n">
+        <v>1.14012</v>
+      </c>
+      <c r="CE117" t="n">
+        <v>1.23451</v>
+      </c>
+      <c r="CF117" t="n">
+        <v>1.37667</v>
+      </c>
+      <c r="CG117" t="n">
+        <v>0.39286</v>
+      </c>
+      <c r="CH117" t="n">
+        <v>0.6366900000000001</v>
+      </c>
+      <c r="CI117" t="n">
+        <v>0.68892</v>
+      </c>
+      <c r="CJ117" t="n">
+        <v>1.33943</v>
+      </c>
+      <c r="CK117" t="n">
+        <v>1.08878</v>
+      </c>
+      <c r="CL117" t="n">
+        <v>0.8676699999999999</v>
+      </c>
+      <c r="CM117" t="n">
+        <v>0.7965</v>
+      </c>
+      <c r="CN117" t="n">
+        <v>0.75722</v>
+      </c>
+      <c r="CO117" t="n">
+        <v>0.5194099999999999</v>
+      </c>
+      <c r="CP117" t="n">
+        <v>0.47952</v>
+      </c>
+      <c r="CQ117" t="n">
+        <v>0.4715</v>
+      </c>
+      <c r="CR117" t="n">
+        <v>0.41571</v>
+      </c>
+      <c r="CS117" t="n">
+        <v>0.42536</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>46139</v>
+      </c>
+      <c r="B118" t="n">
+        <v>0.32887</v>
+      </c>
+      <c r="C118" t="n">
+        <v>0.7092000000000001</v>
+      </c>
+      <c r="D118" t="n">
+        <v>1.76065</v>
+      </c>
+      <c r="E118" t="n">
+        <v>0.8696900000000001</v>
+      </c>
+      <c r="F118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="G118" t="n">
+        <v>0.9137000000000001</v>
+      </c>
+      <c r="H118" t="n">
+        <v>0.49396</v>
+      </c>
+      <c r="I118" t="n">
+        <v>0.51481</v>
+      </c>
+      <c r="J118" t="n">
+        <v>0.5028899999999999</v>
+      </c>
+      <c r="K118" t="n">
+        <v>0.50317</v>
+      </c>
+      <c r="L118" t="n">
+        <v>0.48538</v>
+      </c>
+      <c r="M118" t="n">
+        <v>0.39952</v>
+      </c>
+      <c r="N118" t="n">
+        <v>0.46748</v>
+      </c>
+      <c r="O118" t="n">
+        <v>0.37819</v>
+      </c>
+      <c r="P118" t="n">
+        <v>0.37812</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>0.37543</v>
+      </c>
+      <c r="R118" t="n">
+        <v>0.33627</v>
+      </c>
+      <c r="S118" t="n">
+        <v>0.36596</v>
+      </c>
+      <c r="T118" t="n">
+        <v>0.35133</v>
+      </c>
+      <c r="U118" t="n">
+        <v>0.35121</v>
+      </c>
+      <c r="V118" t="n">
+        <v>0.36166</v>
+      </c>
+      <c r="W118" t="n">
+        <v>0.36738</v>
+      </c>
+      <c r="X118" t="n">
+        <v>0.3494</v>
+      </c>
+      <c r="Y118" t="n">
+        <v>0.37356</v>
+      </c>
+      <c r="Z118" t="n">
+        <v>0.40719</v>
+      </c>
+      <c r="AA118" t="n">
+        <v>0.86964</v>
+      </c>
+      <c r="AB118" t="n">
+        <v>0.70365</v>
+      </c>
+      <c r="AC118" t="n">
+        <v>0.8054600000000001</v>
+      </c>
+      <c r="AD118" t="n">
+        <v>0.45552</v>
+      </c>
+      <c r="AE118" t="n">
+        <v>0.43592</v>
+      </c>
+      <c r="AF118" t="n">
+        <v>0.37648</v>
+      </c>
+      <c r="AG118" t="n">
+        <v>0.34757</v>
+      </c>
+      <c r="AH118" t="n">
+        <v>0.38796</v>
+      </c>
+      <c r="AI118" t="n">
+        <v>0.42792</v>
+      </c>
+      <c r="AJ118" t="n">
+        <v>0.5095500000000001</v>
+      </c>
+      <c r="AK118" t="n">
+        <v>0.36205</v>
+      </c>
+      <c r="AL118" t="n">
+        <v>0.34145</v>
+      </c>
+      <c r="AM118" t="n">
+        <v>0.35694</v>
+      </c>
+      <c r="AN118" t="n">
+        <v>0.34162</v>
+      </c>
+      <c r="AO118" t="n">
+        <v>0.32224</v>
+      </c>
+      <c r="AP118" t="n">
+        <v>0.3143</v>
+      </c>
+      <c r="AQ118" t="n">
+        <v>0.29987</v>
+      </c>
+      <c r="AR118" t="n">
+        <v>0.33267</v>
+      </c>
+      <c r="AS118" t="n">
+        <v>0.34157</v>
+      </c>
+      <c r="AT118" t="n">
+        <v>0.3713399999999999</v>
+      </c>
+      <c r="AU118" t="n">
+        <v>0.5087</v>
+      </c>
+      <c r="AV118" t="n">
+        <v>0.7822899999999999</v>
+      </c>
+      <c r="AW118" t="n">
+        <v>0.99901</v>
+      </c>
+      <c r="AX118" t="n">
+        <v>0.32941</v>
+      </c>
+      <c r="AY118" t="n">
+        <v>0.52947</v>
+      </c>
+      <c r="AZ118" t="n">
+        <v>0.91211</v>
+      </c>
+      <c r="BA118" t="n">
+        <v>0.8636</v>
+      </c>
+      <c r="BB118" t="n">
+        <v>0.5054</v>
+      </c>
+      <c r="BC118" t="n">
+        <v>0.7222799999999999</v>
+      </c>
+      <c r="BD118" t="n">
+        <v>1.42507</v>
+      </c>
+      <c r="BE118" t="n">
+        <v>1.10882</v>
+      </c>
+      <c r="BF118" t="n">
+        <v>1.05758</v>
+      </c>
+      <c r="BG118" t="n">
+        <v>0.28768</v>
+      </c>
+      <c r="BH118" t="n">
+        <v>0.35603</v>
+      </c>
+      <c r="BI118" t="n">
+        <v>0.37661</v>
+      </c>
+      <c r="BJ118" t="n">
+        <v>0.47929</v>
+      </c>
+      <c r="BK118" t="n">
+        <v>0.5486</v>
+      </c>
+      <c r="BL118" t="n">
+        <v>0.5012099999999999</v>
+      </c>
+      <c r="BM118" t="n">
+        <v>0.5314099999999999</v>
+      </c>
+      <c r="BN118" t="n">
+        <v>0.8769600000000001</v>
+      </c>
+      <c r="BO118" t="n">
+        <v>0.63585</v>
+      </c>
+      <c r="BP118" t="n">
+        <v>0.7700900000000001</v>
+      </c>
+      <c r="BQ118" t="n">
+        <v>0.7824500000000001</v>
+      </c>
+      <c r="BR118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BS118" t="n">
+        <v>1.14995</v>
+      </c>
+      <c r="BT118" t="n">
+        <v>1.18643</v>
+      </c>
+      <c r="BU118" t="n">
+        <v>1.19491</v>
+      </c>
+      <c r="BV118" t="n">
+        <v>0.8503200000000001</v>
+      </c>
+      <c r="BW118" t="n">
+        <v>1.19509</v>
+      </c>
+      <c r="BX118" t="n">
+        <v>1.09683</v>
+      </c>
+      <c r="BY118" t="n">
+        <v>1.25228</v>
+      </c>
+      <c r="BZ118" t="n">
+        <v>1.03258</v>
+      </c>
+      <c r="CA118" t="n">
+        <v>1.08199</v>
+      </c>
+      <c r="CB118" t="n">
+        <v>0.63695</v>
+      </c>
+      <c r="CC118" t="n">
+        <v>0.97492</v>
+      </c>
+      <c r="CD118" t="n">
+        <v>0.90211</v>
+      </c>
+      <c r="CE118" t="n">
+        <v>0.97927</v>
+      </c>
+      <c r="CF118" t="n">
+        <v>0.89102</v>
+      </c>
+      <c r="CG118" t="n">
+        <v>0.9707100000000001</v>
+      </c>
+      <c r="CH118" t="n">
+        <v>0.79291</v>
+      </c>
+      <c r="CI118" t="n">
+        <v>1.72894</v>
+      </c>
+      <c r="CJ118" t="n">
+        <v>0.45111</v>
+      </c>
+      <c r="CK118" t="n">
+        <v>0.7922</v>
+      </c>
+      <c r="CL118" t="n">
+        <v>0.81016</v>
+      </c>
+      <c r="CM118" t="n">
+        <v>0.44941</v>
+      </c>
+      <c r="CN118" t="n">
+        <v>0.42849</v>
+      </c>
+      <c r="CO118" t="n">
+        <v>0.44418</v>
+      </c>
+      <c r="CP118" t="n">
+        <v>0.33398</v>
+      </c>
+      <c r="CQ118" t="n">
+        <v>0.37581</v>
+      </c>
+      <c r="CR118" t="n">
+        <v>0.35481</v>
+      </c>
+      <c r="CS118" t="n">
+        <v>0.33462</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>46140</v>
+      </c>
+      <c r="B119" t="n">
+        <v>0.32142</v>
+      </c>
+      <c r="C119" t="n">
+        <v>0.50817</v>
+      </c>
+      <c r="D119" t="n">
+        <v>0.48655</v>
+      </c>
+      <c r="E119" t="n">
+        <v>0.48904</v>
+      </c>
+      <c r="F119" t="n">
+        <v>0.38337</v>
+      </c>
+      <c r="G119" t="n">
+        <v>0.45047</v>
+      </c>
+      <c r="H119" t="n">
+        <v>0.41494</v>
+      </c>
+      <c r="I119" t="n">
+        <v>0.36937</v>
+      </c>
+      <c r="J119" t="n">
+        <v>0.38932</v>
+      </c>
+      <c r="K119" t="n">
+        <v>0.3829</v>
+      </c>
+      <c r="L119" t="n">
+        <v>0.36326</v>
+      </c>
+      <c r="M119" t="n">
+        <v>0.42795</v>
+      </c>
+      <c r="N119" t="n">
+        <v>0.44343</v>
+      </c>
+      <c r="O119" t="n">
+        <v>0.33579</v>
+      </c>
+      <c r="P119" t="n">
+        <v>0.37015</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>0.39565</v>
+      </c>
+      <c r="R119" t="n">
+        <v>0.36702</v>
+      </c>
+      <c r="S119" t="n">
+        <v>0.36789</v>
+      </c>
+      <c r="T119" t="n">
+        <v>0.35572</v>
+      </c>
+      <c r="U119" t="n">
+        <v>0.36121</v>
+      </c>
+      <c r="V119" t="n">
+        <v>0.35169</v>
+      </c>
+      <c r="W119" t="n">
+        <v>0.36295</v>
+      </c>
+      <c r="X119" t="n">
+        <v>0.35714</v>
+      </c>
+      <c r="Y119" t="n">
+        <v>0.38346</v>
+      </c>
+      <c r="Z119" t="n">
+        <v>0.39518</v>
+      </c>
+      <c r="AA119" t="n">
+        <v>0.47235</v>
+      </c>
+      <c r="AB119" t="n">
+        <v>0.44417</v>
+      </c>
+      <c r="AC119" t="n">
+        <v>0.43815</v>
+      </c>
+      <c r="AD119" t="n">
+        <v>0.34737</v>
+      </c>
+      <c r="AE119" t="n">
+        <v>0.39448</v>
+      </c>
+      <c r="AF119" t="n">
+        <v>0.3528</v>
+      </c>
+      <c r="AG119" t="n">
+        <v>0.36731</v>
+      </c>
+      <c r="AH119" t="n">
+        <v>0.34746</v>
+      </c>
+      <c r="AI119" t="n">
+        <v>0.30332</v>
+      </c>
+      <c r="AJ119" t="n">
+        <v>0.29384</v>
+      </c>
+      <c r="AK119" t="n">
+        <v>0.38707</v>
+      </c>
+      <c r="AL119" t="n">
+        <v>0.43264</v>
+      </c>
+      <c r="AM119" t="n">
+        <v>0.34188</v>
+      </c>
+      <c r="AN119" t="n">
+        <v>0.2265</v>
+      </c>
+      <c r="AO119" t="n">
+        <v>0.35685</v>
+      </c>
+      <c r="AP119" t="n">
+        <v>0.36853</v>
+      </c>
+      <c r="AQ119" t="n">
+        <v>0.33332</v>
+      </c>
+      <c r="AR119" t="n">
+        <v>0.36893</v>
+      </c>
+      <c r="AS119" t="n">
+        <v>0.40045</v>
+      </c>
+      <c r="AT119" t="n">
+        <v>0.41287</v>
+      </c>
+      <c r="AU119" t="n">
+        <v>0.56184</v>
+      </c>
+      <c r="AV119" t="n">
+        <v>0.50473</v>
+      </c>
+      <c r="AW119" t="n">
+        <v>0.8305499999999999</v>
+      </c>
+      <c r="AX119" t="n">
+        <v>0.39775</v>
+      </c>
+      <c r="AY119" t="n">
+        <v>0.59933</v>
+      </c>
+      <c r="AZ119" t="n">
+        <v>0.73365</v>
+      </c>
+      <c r="BA119" t="n">
+        <v>0.82262</v>
+      </c>
+      <c r="BB119" t="n">
+        <v>0.54206</v>
+      </c>
+      <c r="BC119" t="n">
+        <v>0.51271</v>
+      </c>
+      <c r="BD119" t="n">
+        <v>0.8115399999999999</v>
+      </c>
+      <c r="BE119" t="n">
+        <v>0.80249</v>
+      </c>
+      <c r="BF119" t="n">
+        <v>0.66361</v>
+      </c>
+      <c r="BG119" t="n">
+        <v>0.6084400000000001</v>
+      </c>
+      <c r="BH119" t="n">
+        <v>0.49556</v>
+      </c>
+      <c r="BI119" t="n">
+        <v>0.45255</v>
+      </c>
+      <c r="BJ119" t="n">
+        <v>0.42932</v>
+      </c>
+      <c r="BK119" t="n">
+        <v>0.39977</v>
+      </c>
+      <c r="BL119" t="n">
+        <v>0.5163300000000001</v>
+      </c>
+      <c r="BM119" t="n">
+        <v>0.49995</v>
+      </c>
+      <c r="BN119" t="n">
+        <v>0.50847</v>
+      </c>
+      <c r="BO119" t="n">
+        <v>0.57085</v>
+      </c>
+      <c r="BP119" t="n">
+        <v>0.5965199999999999</v>
+      </c>
+      <c r="BQ119" t="n">
+        <v>0.5480499999999999</v>
+      </c>
+      <c r="BR119" t="n">
+        <v>0.5679</v>
+      </c>
+      <c r="BS119" t="n">
+        <v>1.27079</v>
+      </c>
+      <c r="BT119" t="n">
+        <v>0.6173200000000001</v>
+      </c>
+      <c r="BU119" t="n">
+        <v>0.6098899999999999</v>
+      </c>
+      <c r="BV119" t="n">
+        <v>0.46282</v>
+      </c>
+      <c r="BW119" t="n">
+        <v>0.50605</v>
+      </c>
+      <c r="BX119" t="n">
+        <v>0.5431</v>
+      </c>
+      <c r="BY119" t="n">
+        <v>0.62862</v>
+      </c>
+      <c r="BZ119" t="n">
+        <v>0.59745</v>
+      </c>
+      <c r="CA119" t="n">
+        <v>0.64408</v>
+      </c>
+      <c r="CB119" t="n">
+        <v>0.34335</v>
+      </c>
+      <c r="CC119" t="n">
+        <v>0.48995</v>
+      </c>
+      <c r="CD119" t="n">
+        <v>0.41979</v>
+      </c>
+      <c r="CE119" t="n">
+        <v>0.47699</v>
+      </c>
+      <c r="CF119" t="n">
+        <v>0.61153</v>
+      </c>
+      <c r="CG119" t="n">
+        <v>0.65498</v>
+      </c>
+      <c r="CH119" t="n">
+        <v>0.56392</v>
+      </c>
+      <c r="CI119" t="n">
+        <v>0.7649600000000001</v>
+      </c>
+      <c r="CJ119" t="n">
+        <v>0.6456499999999999</v>
+      </c>
+      <c r="CK119" t="n">
+        <v>0.5630599999999999</v>
+      </c>
+      <c r="CL119" t="n">
+        <v>0.48685</v>
+      </c>
+      <c r="CM119" t="n">
+        <v>0.6206699999999999</v>
+      </c>
+      <c r="CN119" t="n">
+        <v>0.45282</v>
+      </c>
+      <c r="CO119" t="n">
+        <v>0.45714</v>
+      </c>
+      <c r="CP119" t="n">
+        <v>0.39772</v>
+      </c>
+      <c r="CQ119" t="n">
+        <v>0.36213</v>
+      </c>
+      <c r="CR119" t="n">
+        <v>0.34855</v>
+      </c>
+      <c r="CS119" t="n">
+        <v>0.34198</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n">
+        <v>46141</v>
+      </c>
+      <c r="B120" t="n">
+        <v>0.31894</v>
+      </c>
+      <c r="C120" t="n">
+        <v>0.5262899999999999</v>
+      </c>
+      <c r="D120" t="n">
+        <v>0.49213</v>
+      </c>
+      <c r="E120" t="n">
+        <v>0.44805</v>
+      </c>
+      <c r="F120" t="n">
+        <v>0.38862</v>
+      </c>
+      <c r="G120" t="n">
+        <v>0.38892</v>
+      </c>
+      <c r="H120" t="n">
+        <v>0.39854</v>
+      </c>
+      <c r="I120" t="n">
+        <v>0.36663</v>
+      </c>
+      <c r="J120" t="n">
+        <v>0.35853</v>
+      </c>
+      <c r="K120" t="n">
+        <v>0.38643</v>
+      </c>
+      <c r="L120" t="n">
+        <v>0.38473</v>
+      </c>
+      <c r="M120" t="n">
+        <v>0.36035</v>
+      </c>
+      <c r="N120" t="n">
+        <v>0.44888</v>
+      </c>
+      <c r="O120" t="n">
+        <v>0.35909</v>
+      </c>
+      <c r="P120" t="n">
+        <v>0.34807</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>0.36197</v>
+      </c>
+      <c r="R120" t="n">
+        <v>0.35676</v>
+      </c>
+      <c r="S120" t="n">
+        <v>0.35775</v>
+      </c>
+      <c r="T120" t="n">
+        <v>0.33698</v>
+      </c>
+      <c r="U120" t="n">
+        <v>0.33445</v>
+      </c>
+      <c r="V120" t="n">
+        <v>0.33085</v>
+      </c>
+      <c r="W120" t="n">
+        <v>0.33363</v>
+      </c>
+      <c r="X120" t="n">
+        <v>0.33072</v>
+      </c>
+      <c r="Y120" t="n">
+        <v>0.34977</v>
+      </c>
+      <c r="Z120" t="n">
+        <v>0.33897</v>
+      </c>
+      <c r="AA120" t="n">
+        <v>0.35114</v>
+      </c>
+      <c r="AB120" t="n">
+        <v>0.38435</v>
+      </c>
+      <c r="AC120" t="n">
+        <v>0.38855</v>
+      </c>
+      <c r="AD120" t="n">
+        <v>0.34755</v>
+      </c>
+      <c r="AE120" t="n">
+        <v>0.37391</v>
+      </c>
+      <c r="AF120" t="n">
+        <v>0.34361</v>
+      </c>
+      <c r="AG120" t="n">
+        <v>0.39269</v>
+      </c>
+      <c r="AH120" t="n">
+        <v>0.41494</v>
+      </c>
+      <c r="AI120" t="n">
+        <v>0.42432</v>
+      </c>
+      <c r="AJ120" t="n">
+        <v>0.35571</v>
+      </c>
+      <c r="AK120" t="n">
+        <v>0.40042</v>
+      </c>
+      <c r="AL120" t="n">
+        <v>0.34017</v>
+      </c>
+      <c r="AM120" t="n">
+        <v>0.33506</v>
+      </c>
+      <c r="AN120" t="n">
+        <v>0.31377</v>
+      </c>
+      <c r="AO120" t="n">
+        <v>0.2972</v>
+      </c>
+      <c r="AP120" t="n">
+        <v>0.35604</v>
+      </c>
+      <c r="AQ120" t="n">
+        <v>0.27735</v>
+      </c>
+      <c r="AR120" t="n">
+        <v>0.30995</v>
+      </c>
+      <c r="AS120" t="n">
+        <v>0.30258</v>
+      </c>
+      <c r="AT120" t="n">
+        <v>0.65911</v>
+      </c>
+      <c r="AU120" t="n">
+        <v>0.85194</v>
+      </c>
+      <c r="AV120" t="n">
+        <v>0.49898</v>
+      </c>
+      <c r="AW120" t="n">
+        <v>0.41004</v>
+      </c>
+      <c r="AX120" t="n">
+        <v>0.19013</v>
+      </c>
+      <c r="AY120" t="n">
+        <v>0.35059</v>
+      </c>
+      <c r="AZ120" t="n">
+        <v>0.71535</v>
+      </c>
+      <c r="BA120" t="n">
+        <v>0.3627</v>
+      </c>
+      <c r="BB120" t="n">
+        <v>0.3511</v>
+      </c>
+      <c r="BC120" t="n">
+        <v>0.34568</v>
+      </c>
+      <c r="BD120" t="n">
+        <v>0.42521</v>
+      </c>
+      <c r="BE120" t="n">
+        <v>0.60366</v>
+      </c>
+      <c r="BF120" t="n">
+        <v>0.35958</v>
+      </c>
+      <c r="BG120" t="n">
+        <v>0.34786</v>
+      </c>
+      <c r="BH120" t="n">
+        <v>0.32335</v>
+      </c>
+      <c r="BI120" t="n">
+        <v>0.34979</v>
+      </c>
+      <c r="BJ120" t="n">
+        <v>0.48504</v>
+      </c>
+      <c r="BK120" t="n">
+        <v>0.40661</v>
+      </c>
+      <c r="BL120" t="n">
+        <v>0.39781</v>
+      </c>
+      <c r="BM120" t="n">
+        <v>0.28292</v>
+      </c>
+      <c r="BN120" t="n">
+        <v>0.2985</v>
+      </c>
+      <c r="BO120" t="n">
+        <v>0.30788</v>
+      </c>
+      <c r="BP120" t="n">
+        <v>0.5470499999999999</v>
+      </c>
+      <c r="BQ120" t="n">
+        <v>0.4802</v>
+      </c>
+      <c r="BR120" t="n">
+        <v>0.42929</v>
+      </c>
+      <c r="BS120" t="n">
+        <v>0.49604</v>
+      </c>
+      <c r="BT120" t="n">
+        <v>0.4499</v>
+      </c>
+      <c r="BU120" t="n">
+        <v>0.46253</v>
+      </c>
+      <c r="BV120" t="n">
+        <v>0.3995</v>
+      </c>
+      <c r="BW120" t="n">
+        <v>0.47547</v>
+      </c>
+      <c r="BX120" t="n">
+        <v>0.52335</v>
+      </c>
+      <c r="BY120" t="n">
+        <v>0.57265</v>
+      </c>
+      <c r="BZ120" t="n">
+        <v>0.43372</v>
+      </c>
+      <c r="CA120" t="n">
+        <v>0.54243</v>
+      </c>
+      <c r="CB120" t="n">
+        <v>0.46175</v>
+      </c>
+      <c r="CC120" t="n">
+        <v>0.44905</v>
+      </c>
+      <c r="CD120" t="n">
+        <v>0.49923</v>
+      </c>
+      <c r="CE120" t="n">
+        <v>0.41454</v>
+      </c>
+      <c r="CF120" t="n">
+        <v>0.3952</v>
+      </c>
+      <c r="CG120" t="n">
+        <v>0.39032</v>
+      </c>
+      <c r="CH120" t="n">
+        <v>0.41566</v>
+      </c>
+      <c r="CI120" t="n">
+        <v>0.34021</v>
+      </c>
+      <c r="CJ120" t="n">
+        <v>0.35822</v>
+      </c>
+      <c r="CK120" t="n">
+        <v>0.34622</v>
+      </c>
+      <c r="CL120" t="n">
+        <v>0.34108</v>
+      </c>
+      <c r="CM120" t="n">
+        <v>0.31906</v>
+      </c>
+      <c r="CN120" t="n">
+        <v>0.32313</v>
+      </c>
+      <c r="CO120" t="n">
+        <v>0.32049</v>
+      </c>
+      <c r="CP120" t="n">
+        <v>0.31479</v>
+      </c>
+      <c r="CQ120" t="n">
+        <v>0.31836</v>
+      </c>
+      <c r="CR120" t="n">
+        <v>0.32078</v>
+      </c>
+      <c r="CS120" t="n">
+        <v>0.31949</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n">
+        <v>46142</v>
+      </c>
+      <c r="B121" t="n">
+        <v>0.3051</v>
+      </c>
+      <c r="C121" t="n">
+        <v>0.46077</v>
+      </c>
+      <c r="D121" t="n">
+        <v>0.45834</v>
+      </c>
+      <c r="E121" t="n">
+        <v>0.38248</v>
+      </c>
+      <c r="F121" t="n">
+        <v>0.36147</v>
+      </c>
+      <c r="G121" t="n">
+        <v>0.34431</v>
+      </c>
+      <c r="H121" t="n">
+        <v>0.33009</v>
+      </c>
+      <c r="I121" t="n">
+        <v>0.32838</v>
+      </c>
+      <c r="J121" t="n">
+        <v>0.33294</v>
+      </c>
+      <c r="K121" t="n">
+        <v>0.32098</v>
+      </c>
+      <c r="L121" t="n">
+        <v>0.31916</v>
+      </c>
+      <c r="M121" t="n">
+        <v>0.31631</v>
+      </c>
+      <c r="N121" t="n">
+        <v>0.31926</v>
+      </c>
+      <c r="O121" t="n">
+        <v>0.31836</v>
+      </c>
+      <c r="P121" t="n">
+        <v>0.3151600000000001</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>0.31609</v>
+      </c>
+      <c r="R121" t="n">
+        <v>0.31373</v>
+      </c>
+      <c r="S121" t="n">
+        <v>0.31513</v>
+      </c>
+      <c r="T121" t="n">
+        <v>0.32048</v>
+      </c>
+      <c r="U121" t="n">
+        <v>0.31627</v>
+      </c>
+      <c r="V121" t="n">
+        <v>0.31142</v>
+      </c>
+      <c r="W121" t="n">
+        <v>0.31075</v>
+      </c>
+      <c r="X121" t="n">
+        <v>0.31346</v>
+      </c>
+      <c r="Y121" t="n">
+        <v>0.31481</v>
+      </c>
+      <c r="Z121" t="n">
+        <v>0.31646</v>
+      </c>
+      <c r="AA121" t="n">
+        <v>0.32452</v>
+      </c>
+      <c r="AB121" t="n">
+        <v>0.32434</v>
+      </c>
+      <c r="AC121" t="n">
+        <v>0.3326</v>
+      </c>
+      <c r="AD121" t="n">
+        <v>0.32612</v>
+      </c>
+      <c r="AE121" t="n">
+        <v>0.3226</v>
+      </c>
+      <c r="AF121" t="n">
+        <v>0.32466</v>
+      </c>
+      <c r="AG121" t="n">
+        <v>0.33087</v>
+      </c>
+      <c r="AH121" t="n">
+        <v>0.34269</v>
+      </c>
+      <c r="AI121" t="n">
+        <v>0.37987</v>
+      </c>
+      <c r="AJ121" t="n">
+        <v>0.32285</v>
+      </c>
+      <c r="AK121" t="n">
+        <v>0.28649</v>
+      </c>
+      <c r="AL121" t="n">
+        <v>0.34042</v>
+      </c>
+      <c r="AM121" t="n">
+        <v>0.33558</v>
+      </c>
+      <c r="AN121" t="n">
+        <v>0.30259</v>
+      </c>
+      <c r="AO121" t="n">
+        <v>0.31861</v>
+      </c>
+      <c r="AP121" t="n">
+        <v>0.30378</v>
+      </c>
+      <c r="AQ121" t="n">
+        <v>0.31777</v>
+      </c>
+      <c r="AR121" t="n">
+        <v>0.21291</v>
+      </c>
+      <c r="AS121" t="n">
+        <v>0.31137</v>
+      </c>
+      <c r="AT121" t="n">
+        <v>0.24575</v>
+      </c>
+      <c r="AU121" t="n">
+        <v>0.23533</v>
+      </c>
+      <c r="AV121" t="n">
+        <v>0.15725</v>
+      </c>
+      <c r="AW121" t="n">
+        <v>0.30029</v>
+      </c>
+      <c r="AX121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY121" t="n">
+        <v>0.18922</v>
+      </c>
+      <c r="AZ121" t="n">
+        <v>0.2801</v>
+      </c>
+      <c r="BA121" t="n">
+        <v>0.18005</v>
+      </c>
+      <c r="BB121" t="n">
+        <v>0.01784</v>
+      </c>
+      <c r="BC121" t="n">
+        <v>-0.009010000000000001</v>
+      </c>
+      <c r="BD121" t="n">
+        <v>0.05303</v>
+      </c>
+      <c r="BE121" t="n">
+        <v>0.39139</v>
+      </c>
+      <c r="BF121" t="n">
+        <v>0.38962</v>
+      </c>
+      <c r="BG121" t="n">
+        <v>0.22254</v>
+      </c>
+      <c r="BH121" t="n">
+        <v>0.1899</v>
+      </c>
+      <c r="BI121" t="n">
+        <v>0.21921</v>
+      </c>
+      <c r="BJ121" t="n">
+        <v>0.06186999999999999</v>
+      </c>
+      <c r="BK121" t="n">
+        <v>0.0055</v>
+      </c>
+      <c r="BL121" t="n">
+        <v>0.00207</v>
+      </c>
+      <c r="BM121" t="n">
+        <v>0.00358</v>
+      </c>
+      <c r="BN121" t="n">
+        <v>1.05835</v>
+      </c>
+      <c r="BO121" t="n">
+        <v>0.27949</v>
+      </c>
+      <c r="BP121" t="n">
+        <v>0.29792</v>
+      </c>
+      <c r="BQ121" t="n">
+        <v>0.30021</v>
+      </c>
+      <c r="BR121" t="n">
+        <v>0.30811</v>
+      </c>
+      <c r="BS121" t="n">
+        <v>0.29399</v>
+      </c>
+      <c r="BT121" t="n">
+        <v>0.30162</v>
+      </c>
+      <c r="BU121" t="n">
+        <v>0.31995</v>
+      </c>
+      <c r="BV121" t="n">
+        <v>0.32957</v>
+      </c>
+      <c r="BW121" t="n">
+        <v>0.31546</v>
+      </c>
+      <c r="BX121" t="n">
+        <v>0.33545</v>
+      </c>
+      <c r="BY121" t="n">
+        <v>0.33573</v>
+      </c>
+      <c r="BZ121" t="n">
+        <v>0.33586</v>
+      </c>
+      <c r="CA121" t="n">
+        <v>0.3331</v>
+      </c>
+      <c r="CB121" t="n">
+        <v>0.37474</v>
+      </c>
+      <c r="CC121" t="n">
+        <v>0.38065</v>
+      </c>
+      <c r="CD121" t="n">
+        <v>0.37508</v>
+      </c>
+      <c r="CE121" t="n">
+        <v>0.37007</v>
+      </c>
+      <c r="CF121" t="n">
+        <v>0.35686</v>
+      </c>
+      <c r="CG121" t="n">
+        <v>0.38663</v>
+      </c>
+      <c r="CH121" t="n">
+        <v>0.39036</v>
+      </c>
+      <c r="CI121" t="n">
+        <v>0.39883</v>
+      </c>
+      <c r="CJ121" t="n">
+        <v>0.45976</v>
+      </c>
+      <c r="CK121" t="n">
+        <v>0.36992</v>
+      </c>
+      <c r="CL121" t="n">
+        <v>0.38886</v>
+      </c>
+      <c r="CM121" t="n">
+        <v>0.39015</v>
+      </c>
+      <c r="CN121" t="n">
+        <v>0.48223</v>
+      </c>
+      <c r="CO121" t="n">
+        <v>0.35173</v>
+      </c>
+      <c r="CP121" t="n">
+        <v>0.3564</v>
+      </c>
+      <c r="CQ121" t="n">
+        <v>0.34427</v>
+      </c>
+      <c r="CR121" t="n">
+        <v>0.35361</v>
+      </c>
+      <c r="CS121" t="n">
+        <v>0.34244</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B122" t="n">
+        <v>0.36699</v>
+      </c>
+      <c r="C122" t="n">
+        <v>0.57212</v>
+      </c>
+      <c r="D122" t="n">
+        <v>0.37491</v>
+      </c>
+      <c r="E122" t="n">
+        <v>0.39431</v>
+      </c>
+      <c r="F122" t="n">
+        <v>0.37882</v>
+      </c>
+      <c r="G122" t="n">
+        <v>0.37344</v>
+      </c>
+      <c r="H122" t="n">
+        <v>0.35142</v>
+      </c>
+      <c r="I122" t="n">
+        <v>0.34095</v>
+      </c>
+      <c r="J122" t="n">
+        <v>0.34985</v>
+      </c>
+      <c r="K122" t="n">
+        <v>0.29705</v>
+      </c>
+      <c r="L122" t="n">
+        <v>0.30026</v>
+      </c>
+      <c r="M122" t="n">
+        <v>0.27927</v>
+      </c>
+      <c r="N122" t="n">
+        <v>0.3287</v>
+      </c>
+      <c r="O122" t="n">
+        <v>0.24806</v>
+      </c>
+      <c r="P122" t="n">
+        <v>0.33963</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>0.33739</v>
+      </c>
+      <c r="R122" t="n">
+        <v>0.32745</v>
+      </c>
+      <c r="S122" t="n">
+        <v>0.27795</v>
+      </c>
+      <c r="T122" t="n">
+        <v>0.30937</v>
+      </c>
+      <c r="U122" t="n">
+        <v>0.30486</v>
+      </c>
+      <c r="V122" t="n">
+        <v>0.28961</v>
+      </c>
+      <c r="W122" t="n">
+        <v>0.29146</v>
+      </c>
+      <c r="X122" t="n">
+        <v>0.28493</v>
+      </c>
+      <c r="Y122" t="n">
+        <v>0.32775</v>
+      </c>
+      <c r="Z122" t="n">
+        <v>0.31617</v>
+      </c>
+      <c r="AA122" t="n">
+        <v>0.32997</v>
+      </c>
+      <c r="AB122" t="n">
+        <v>0.34444</v>
+      </c>
+      <c r="AC122" t="n">
+        <v>0.30679</v>
+      </c>
+      <c r="AD122" t="n">
+        <v>0.30367</v>
+      </c>
+      <c r="AE122" t="n">
+        <v>0.10251</v>
+      </c>
+      <c r="AF122" t="n">
+        <v>0.10265</v>
+      </c>
+      <c r="AG122" t="n">
+        <v>0.04351</v>
+      </c>
+      <c r="AH122" t="n">
+        <v>-0.04699</v>
+      </c>
+      <c r="AI122" t="n">
+        <v>-0.04573</v>
+      </c>
+      <c r="AJ122" t="n">
+        <v>-0.04621</v>
+      </c>
+      <c r="AK122" t="n">
+        <v>-0.0441</v>
+      </c>
+      <c r="AL122" t="n">
+        <v>-0.04621</v>
+      </c>
+      <c r="AM122" t="n">
+        <v>-0.0447</v>
+      </c>
+      <c r="AN122" t="n">
+        <v>-0.04398</v>
+      </c>
+      <c r="AO122" t="n">
+        <v>0.38412</v>
+      </c>
+      <c r="AP122" t="n">
+        <v>0.01926</v>
+      </c>
+      <c r="AQ122" t="n">
+        <v>0.22384</v>
+      </c>
+      <c r="AR122" t="n">
+        <v>0.05805</v>
+      </c>
+      <c r="AS122" t="n">
+        <v>0.30143</v>
+      </c>
+      <c r="AT122" t="n">
+        <v>0.22279</v>
+      </c>
+      <c r="AU122" t="n">
+        <v>0.08337</v>
+      </c>
+      <c r="AV122" t="n">
+        <v>-0.04392</v>
+      </c>
+      <c r="AW122" t="n">
+        <v>-0.04394</v>
+      </c>
+      <c r="AX122" t="n">
+        <v>-0.04574</v>
+      </c>
+      <c r="AY122" t="n">
+        <v>-0.0456</v>
+      </c>
+      <c r="AZ122" t="n">
+        <v>-0.04561</v>
+      </c>
+      <c r="BA122" t="n">
+        <v>-0.04369</v>
+      </c>
+      <c r="BB122" t="n">
+        <v>-0.04335</v>
+      </c>
+      <c r="BC122" t="n">
+        <v>-0.04549</v>
+      </c>
+      <c r="BD122" t="n">
+        <v>-0.04339</v>
+      </c>
+      <c r="BE122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BF122" t="n">
+        <v>-0.04529</v>
+      </c>
+      <c r="BG122" t="n">
+        <v>-0.04525</v>
+      </c>
+      <c r="BH122" t="n">
+        <v>-0.04538</v>
+      </c>
+      <c r="BI122" t="n">
+        <v>-0.04358</v>
+      </c>
+      <c r="BJ122" t="n">
+        <v>-0.04423</v>
+      </c>
+      <c r="BK122" t="n">
+        <v>0.07798000000000001</v>
+      </c>
+      <c r="BL122" t="n">
+        <v>0.07625</v>
+      </c>
+      <c r="BM122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN122" t="n">
+        <v>-0.04471</v>
+      </c>
+      <c r="BO122" t="n">
+        <v>-0.04997</v>
+      </c>
+      <c r="BP122" t="n">
+        <v>-0.04984</v>
+      </c>
+      <c r="BQ122" t="n">
+        <v>-0.0474</v>
+      </c>
+      <c r="BR122" t="n">
+        <v>-0.04790999999999999</v>
+      </c>
+      <c r="BS122" t="n">
+        <v>0.19975</v>
+      </c>
+      <c r="BT122" t="n">
+        <v>0.14272</v>
+      </c>
+      <c r="BU122" t="n">
+        <v>0.28994</v>
+      </c>
+      <c r="BV122" t="n">
+        <v>0.29465</v>
+      </c>
+      <c r="BW122" t="n">
+        <v>0.30454</v>
+      </c>
+      <c r="BX122" t="n">
+        <v>0.29982</v>
+      </c>
+      <c r="BY122" t="n">
+        <v>0.29492</v>
+      </c>
+      <c r="BZ122" t="n">
+        <v>0.29282</v>
+      </c>
+      <c r="CA122" t="n">
+        <v>0.29329</v>
+      </c>
+      <c r="CB122" t="n">
+        <v>0.29225</v>
+      </c>
+      <c r="CC122" t="n">
+        <v>0.29678</v>
+      </c>
+      <c r="CD122" t="n">
+        <v>0.29074</v>
+      </c>
+      <c r="CE122" t="n">
+        <v>0.29497</v>
+      </c>
+      <c r="CF122" t="n">
+        <v>0.26875</v>
+      </c>
+      <c r="CG122" t="n">
+        <v>0.29381</v>
+      </c>
+      <c r="CH122" t="n">
+        <v>0.29802</v>
+      </c>
+      <c r="CI122" t="n">
+        <v>0.30855</v>
+      </c>
+      <c r="CJ122" t="n">
+        <v>0.30375</v>
+      </c>
+      <c r="CK122" t="n">
+        <v>0.30221</v>
+      </c>
+      <c r="CL122" t="n">
+        <v>0.31434</v>
+      </c>
+      <c r="CM122" t="n">
+        <v>0.31839</v>
+      </c>
+      <c r="CN122" t="n">
+        <v>0.34714</v>
+      </c>
+      <c r="CO122" t="n">
+        <v>0.34684</v>
+      </c>
+      <c r="CP122" t="n">
+        <v>0.33956</v>
+      </c>
+      <c r="CQ122" t="n">
+        <v>0.3594</v>
+      </c>
+      <c r="CR122" t="n">
+        <v>0.35916</v>
+      </c>
+      <c r="CS122" t="n">
+        <v>0.33046</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n">
+        <v>46144</v>
+      </c>
+      <c r="B123" t="n">
+        <v>0.32316</v>
+      </c>
+      <c r="C123" t="n">
+        <v>1.31476</v>
+      </c>
+      <c r="D123" t="n">
+        <v>0.31033</v>
+      </c>
+      <c r="E123" t="n">
+        <v>0.39326</v>
+      </c>
+      <c r="F123" t="n">
+        <v>0.34407</v>
+      </c>
+      <c r="G123" t="n">
+        <v>0.3203</v>
+      </c>
+      <c r="H123" t="n">
+        <v>0.30704</v>
+      </c>
+      <c r="I123" t="n">
+        <v>0.31463</v>
+      </c>
+      <c r="J123" t="n">
+        <v>0.30134</v>
+      </c>
+      <c r="K123" t="n">
+        <v>0.28114</v>
+      </c>
+      <c r="L123" t="n">
+        <v>0.29441</v>
+      </c>
+      <c r="M123" t="n">
+        <v>0.29069</v>
+      </c>
+      <c r="N123" t="n">
+        <v>0.28802</v>
+      </c>
+      <c r="O123" t="n">
+        <v>0.28084</v>
+      </c>
+      <c r="P123" t="n">
+        <v>0.27116</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>0.27089</v>
+      </c>
+      <c r="R123" t="n">
+        <v>0.2810299999999999</v>
+      </c>
+      <c r="S123" t="n">
+        <v>0.17236</v>
+      </c>
+      <c r="T123" t="n">
+        <v>0.1586</v>
+      </c>
+      <c r="U123" t="n">
+        <v>0.17092</v>
+      </c>
+      <c r="V123" t="n">
+        <v>0.1477</v>
+      </c>
+      <c r="W123" t="n">
+        <v>0.15943</v>
+      </c>
+      <c r="X123" t="n">
+        <v>0.15858</v>
+      </c>
+      <c r="Y123" t="n">
+        <v>0.23612</v>
+      </c>
+      <c r="Z123" t="n">
+        <v>0.214</v>
+      </c>
+      <c r="AA123" t="n">
+        <v>0.22651</v>
+      </c>
+      <c r="AB123" t="n">
+        <v>0.26883</v>
+      </c>
+      <c r="AC123" t="n">
+        <v>0.28566</v>
+      </c>
+      <c r="AD123" t="n">
+        <v>0.29075</v>
+      </c>
+      <c r="AE123" t="n">
+        <v>0.31932</v>
+      </c>
+      <c r="AF123" t="n">
+        <v>0.28069</v>
+      </c>
+      <c r="AG123" t="n">
+        <v>0.28084</v>
+      </c>
+      <c r="AH123" t="n">
+        <v>0.2810299999999999</v>
+      </c>
+      <c r="AI123" t="n">
+        <v>0.28043</v>
+      </c>
+      <c r="AJ123" t="n">
+        <v>0.27072</v>
+      </c>
+      <c r="AK123" t="n">
+        <v>0.28091</v>
+      </c>
+      <c r="AL123" t="n">
+        <v>0.32236</v>
+      </c>
+      <c r="AM123" t="n">
+        <v>0.31015</v>
+      </c>
+      <c r="AN123" t="n">
+        <v>0.30493</v>
+      </c>
+      <c r="AO123" t="n">
+        <v>0.3163</v>
+      </c>
+      <c r="AP123" t="n">
+        <v>0.30939</v>
+      </c>
+      <c r="AQ123" t="n">
+        <v>0.35894</v>
+      </c>
+      <c r="AR123" t="n">
+        <v>0.31626</v>
+      </c>
+      <c r="AS123" t="n">
+        <v>0.29734</v>
+      </c>
+      <c r="AT123" t="n">
+        <v>0.38815</v>
+      </c>
+      <c r="AU123" t="n">
+        <v>0.37962</v>
+      </c>
+      <c r="AV123" t="n">
+        <v>0.42783</v>
+      </c>
+      <c r="AW123" t="n">
+        <v>0.45579</v>
+      </c>
+      <c r="AX123" t="n">
+        <v>0.33182</v>
+      </c>
+      <c r="AY123" t="n">
+        <v>0.41846</v>
+      </c>
+      <c r="AZ123" t="n">
+        <v>0.41529</v>
+      </c>
+      <c r="BA123" t="n">
+        <v>0.38765</v>
+      </c>
+      <c r="BB123" t="n">
+        <v>0.40243</v>
+      </c>
+      <c r="BC123" t="n">
+        <v>0.30005</v>
+      </c>
+      <c r="BD123" t="n">
+        <v>0.30095</v>
+      </c>
+      <c r="BE123" t="n">
+        <v>0.2993</v>
+      </c>
+      <c r="BF123" t="n">
+        <v>0.29998</v>
+      </c>
+      <c r="BG123" t="n">
+        <v>0.15654</v>
+      </c>
+      <c r="BH123" t="n">
+        <v>0.29432</v>
+      </c>
+      <c r="BI123" t="n">
+        <v>0.31094</v>
+      </c>
+      <c r="BJ123" t="n">
+        <v>0.31343</v>
+      </c>
+      <c r="BK123" t="n">
+        <v>0.31271</v>
+      </c>
+      <c r="BL123" t="n">
+        <v>0.32184</v>
+      </c>
+      <c r="BM123" t="n">
+        <v>0.34628</v>
+      </c>
+      <c r="BN123" t="n">
+        <v>0.30067</v>
+      </c>
+      <c r="BO123" t="n">
+        <v>0.33083</v>
+      </c>
+      <c r="BP123" t="n">
+        <v>0.38546</v>
+      </c>
+      <c r="BQ123" t="n">
+        <v>0.47916</v>
+      </c>
+      <c r="BR123" t="n">
+        <v>0.5076700000000001</v>
+      </c>
+      <c r="BS123" t="n">
+        <v>0.79098</v>
+      </c>
+      <c r="BT123" t="n">
+        <v>0.6220399999999999</v>
+      </c>
+      <c r="BU123" t="n">
+        <v>0.78527</v>
+      </c>
+      <c r="BV123" t="n">
+        <v>0.40003</v>
+      </c>
+      <c r="BW123" t="n">
+        <v>0.49798</v>
+      </c>
+      <c r="BX123" t="n">
+        <v>0.7810199999999999</v>
+      </c>
+      <c r="BY123" t="n">
+        <v>0.92039</v>
+      </c>
+      <c r="BZ123" t="n">
+        <v>0.49456</v>
+      </c>
+      <c r="CA123" t="n">
+        <v>0.9142100000000001</v>
+      </c>
+      <c r="CB123" t="n">
+        <v>0.8629</v>
+      </c>
+      <c r="CC123" t="n">
+        <v>1.29623</v>
+      </c>
+      <c r="CD123" t="n">
+        <v>0.35368</v>
+      </c>
+      <c r="CE123" t="n">
+        <v>0.8875299999999999</v>
+      </c>
+      <c r="CF123" t="n">
+        <v>0.63161</v>
+      </c>
+      <c r="CG123" t="n">
+        <v>1.18711</v>
+      </c>
+      <c r="CH123" t="n">
+        <v>0.8680599999999999</v>
+      </c>
+      <c r="CI123" t="n">
+        <v>0.49412</v>
+      </c>
+      <c r="CJ123" t="n">
+        <v>1.33087</v>
+      </c>
+      <c r="CK123" t="n">
+        <v>1.03293</v>
+      </c>
+      <c r="CL123" t="n">
+        <v>0.5308099999999999</v>
+      </c>
+      <c r="CM123" t="n">
+        <v>0.791</v>
+      </c>
+      <c r="CN123" t="n">
+        <v>0.52001</v>
+      </c>
+      <c r="CO123" t="n">
+        <v>0.77299</v>
+      </c>
+      <c r="CP123" t="n">
+        <v>0.7775599999999999</v>
+      </c>
+      <c r="CQ123" t="n">
+        <v>0.8767699999999999</v>
+      </c>
+      <c r="CR123" t="n">
+        <v>0.87387</v>
+      </c>
+      <c r="CS123" t="n">
+        <v>0.49317</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>46145</v>
+      </c>
+      <c r="B124" t="n">
+        <v>0.39869</v>
+      </c>
+      <c r="C124" t="n">
+        <v>1.39991</v>
+      </c>
+      <c r="D124" t="n">
+        <v>0.44996</v>
+      </c>
+      <c r="E124" t="n">
+        <v>1.20702</v>
+      </c>
+      <c r="F124" t="n">
+        <v>0.87883</v>
+      </c>
+      <c r="G124" t="n">
+        <v>0.55102</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0.62187</v>
+      </c>
+      <c r="I124" t="n">
+        <v>0.5383300000000001</v>
+      </c>
+      <c r="J124" t="n">
+        <v>0.4977</v>
+      </c>
+      <c r="K124" t="n">
+        <v>0.45582</v>
+      </c>
+      <c r="L124" t="n">
+        <v>0.42426</v>
+      </c>
+      <c r="M124" t="n">
+        <v>0.43715</v>
+      </c>
+      <c r="N124" t="n">
+        <v>0.44974</v>
+      </c>
+      <c r="O124" t="n">
+        <v>0.38818</v>
+      </c>
+      <c r="P124" t="n">
+        <v>0.45268</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>0.41971</v>
+      </c>
+      <c r="R124" t="n">
+        <v>0.34585</v>
+      </c>
+      <c r="S124" t="n">
+        <v>0.39813</v>
+      </c>
+      <c r="T124" t="n">
+        <v>0.3622</v>
+      </c>
+      <c r="U124" t="n">
+        <v>0.38318</v>
+      </c>
+      <c r="V124" t="n">
+        <v>0.40783</v>
+      </c>
+      <c r="W124" t="n">
+        <v>0.42474</v>
+      </c>
+      <c r="X124" t="n">
+        <v>0.33875</v>
+      </c>
+      <c r="Y124" t="n">
+        <v>0.38619</v>
+      </c>
+      <c r="Z124" t="n">
+        <v>0.34475</v>
+      </c>
+      <c r="AA124" t="n">
+        <v>0.33534</v>
+      </c>
+      <c r="AB124" t="n">
+        <v>0.32892</v>
+      </c>
+      <c r="AC124" t="n">
+        <v>0.33916</v>
+      </c>
+      <c r="AD124" t="n">
+        <v>0.38059</v>
+      </c>
+      <c r="AE124" t="n">
+        <v>0.34746</v>
+      </c>
+      <c r="AF124" t="n">
+        <v>0.44895</v>
+      </c>
+      <c r="AG124" t="n">
+        <v>0.3452</v>
+      </c>
+      <c r="AH124" t="n">
+        <v>0.39088</v>
+      </c>
+      <c r="AI124" t="n">
+        <v>0.3802</v>
+      </c>
+      <c r="AJ124" t="n">
+        <v>0.5525</v>
+      </c>
+      <c r="AK124" t="n">
+        <v>0.40592</v>
+      </c>
+      <c r="AL124" t="n">
+        <v>0.58274</v>
+      </c>
+      <c r="AM124" t="n">
+        <v>0.7021900000000001</v>
+      </c>
+      <c r="AN124" t="n">
+        <v>0.8773500000000001</v>
+      </c>
+      <c r="AO124" t="n">
+        <v>0.46745</v>
+      </c>
+      <c r="AP124" t="n">
+        <v>0.3857</v>
+      </c>
+      <c r="AQ124" t="n">
+        <v>0.54525</v>
+      </c>
+      <c r="AR124" t="n">
+        <v>0.43105</v>
+      </c>
+      <c r="AS124" t="n">
+        <v>0.8047799999999999</v>
+      </c>
+      <c r="AT124" t="n">
+        <v>0.55604</v>
+      </c>
+      <c r="AU124" t="n">
+        <v>0.8547899999999999</v>
+      </c>
+      <c r="AV124" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AW124" t="n">
+        <v>0.8749600000000001</v>
+      </c>
+      <c r="AX124" t="n">
+        <v>0.3407</v>
+      </c>
+      <c r="AY124" t="n">
+        <v>0.41019</v>
+      </c>
+      <c r="AZ124" t="n">
+        <v>0.6115499999999999</v>
+      </c>
+      <c r="BA124" t="n">
+        <v>0.32947</v>
+      </c>
+      <c r="BB124" t="n">
+        <v>0.30222</v>
+      </c>
+      <c r="BC124" t="n">
+        <v>0.29285</v>
+      </c>
+      <c r="BD124" t="n">
+        <v>0.62846</v>
+      </c>
+      <c r="BE124" t="n">
+        <v>0.5985499999999999</v>
+      </c>
+      <c r="BF124" t="n">
+        <v>0.28488</v>
+      </c>
+      <c r="BG124" t="n">
+        <v>0.31058</v>
+      </c>
+      <c r="BH124" t="n">
+        <v>0.35207</v>
+      </c>
+      <c r="BI124" t="n">
+        <v>0.32998</v>
+      </c>
+      <c r="BJ124" t="n">
+        <v>0.3208</v>
+      </c>
+      <c r="BK124" t="n">
+        <v>0.4064700000000001</v>
+      </c>
+      <c r="BL124" t="n">
+        <v>0.33356</v>
+      </c>
+      <c r="BM124" t="n">
+        <v>0.31705</v>
+      </c>
+      <c r="BN124" t="n">
+        <v>0.31954</v>
+      </c>
+      <c r="BO124" t="n">
+        <v>0.31907</v>
+      </c>
+      <c r="BP124" t="n">
+        <v>0.31926</v>
+      </c>
+      <c r="BQ124" t="n">
+        <v>0.33395</v>
+      </c>
+      <c r="BR124" t="n">
+        <v>0.31711</v>
+      </c>
+      <c r="BS124" t="n">
+        <v>0.3075</v>
+      </c>
+      <c r="BT124" t="n">
+        <v>0.31831</v>
+      </c>
+      <c r="BU124" t="n">
+        <v>0.301</v>
+      </c>
+      <c r="BV124" t="n">
+        <v>0.29581</v>
+      </c>
+      <c r="BW124" t="n">
+        <v>0.31111</v>
+      </c>
+      <c r="BX124" t="n">
+        <v>0.30888</v>
+      </c>
+      <c r="BY124" t="n">
+        <v>0.31041</v>
+      </c>
+      <c r="BZ124" t="n">
+        <v>0.28086</v>
+      </c>
+      <c r="CA124" t="n">
+        <v>0.29806</v>
+      </c>
+      <c r="CB124" t="n">
+        <v>0.30166</v>
+      </c>
+      <c r="CC124" t="n">
+        <v>0.31079</v>
+      </c>
+      <c r="CD124" t="n">
+        <v>0.30769</v>
+      </c>
+      <c r="CE124" t="n">
+        <v>0.3136</v>
+      </c>
+      <c r="CF124" t="n">
+        <v>0.34676</v>
+      </c>
+      <c r="CG124" t="n">
+        <v>0.32827</v>
+      </c>
+      <c r="CH124" t="n">
+        <v>0.33269</v>
+      </c>
+      <c r="CI124" t="n">
+        <v>0.33058</v>
+      </c>
+      <c r="CJ124" t="n">
+        <v>0.32288</v>
+      </c>
+      <c r="CK124" t="n">
+        <v>0.32641</v>
+      </c>
+      <c r="CL124" t="n">
+        <v>0.32473</v>
+      </c>
+      <c r="CM124" t="n">
+        <v>0.38287</v>
+      </c>
+      <c r="CN124" t="n">
+        <v>0.38491</v>
+      </c>
+      <c r="CO124" t="n">
+        <v>0.4162</v>
+      </c>
+      <c r="CP124" t="n">
+        <v>0.38673</v>
+      </c>
+      <c r="CQ124" t="n">
+        <v>0.36981</v>
+      </c>
+      <c r="CR124" t="n">
+        <v>0.35362</v>
+      </c>
+      <c r="CS124" t="n">
+        <v>0.3459</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>46146</v>
+      </c>
+      <c r="B125" t="n">
+        <v>0.32835</v>
+      </c>
+      <c r="C125" t="n">
+        <v>0.91164</v>
+      </c>
+      <c r="D125" t="n">
+        <v>0.34717</v>
+      </c>
+      <c r="E125" t="n">
+        <v>0.4391600000000001</v>
+      </c>
+      <c r="F125" t="n">
+        <v>0.40662</v>
+      </c>
+      <c r="G125" t="n">
+        <v>0.38987</v>
+      </c>
+      <c r="H125" t="n">
+        <v>0.43037</v>
+      </c>
+      <c r="I125" t="n">
+        <v>0.36338</v>
+      </c>
+      <c r="J125" t="n">
+        <v>0.38539</v>
+      </c>
+      <c r="K125" t="n">
+        <v>0.35008</v>
+      </c>
+      <c r="L125" t="n">
+        <v>0.35269</v>
+      </c>
+      <c r="M125" t="n">
+        <v>0.33862</v>
+      </c>
+      <c r="N125" t="n">
+        <v>0.3382</v>
+      </c>
+      <c r="O125" t="n">
+        <v>0.33275</v>
+      </c>
+      <c r="P125" t="n">
+        <v>0.32308</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>0.34594</v>
+      </c>
+      <c r="R125" t="n">
+        <v>0.33444</v>
+      </c>
+      <c r="S125" t="n">
+        <v>0.31619</v>
+      </c>
+      <c r="T125" t="n">
+        <v>0.37271</v>
+      </c>
+      <c r="U125" t="n">
+        <v>0.45339</v>
+      </c>
+      <c r="V125" t="n">
+        <v>0.34372</v>
+      </c>
+      <c r="W125" t="n">
+        <v>0.36474</v>
+      </c>
+      <c r="X125" t="n">
+        <v>0.33183</v>
+      </c>
+      <c r="Y125" t="n">
+        <v>0.33741</v>
+      </c>
+      <c r="Z125" t="n">
+        <v>0.34061</v>
+      </c>
+      <c r="AA125" t="n">
+        <v>0.35216</v>
+      </c>
+      <c r="AB125" t="n">
+        <v>0.34331</v>
+      </c>
+      <c r="AC125" t="n">
+        <v>0.34825</v>
+      </c>
+      <c r="AD125" t="n">
+        <v>0.30686</v>
+      </c>
+      <c r="AE125" t="n">
+        <v>0.30821</v>
+      </c>
+      <c r="AF125" t="n">
+        <v>0.32346</v>
+      </c>
+      <c r="AG125" t="n">
+        <v>0.32888</v>
+      </c>
+      <c r="AH125" t="n">
+        <v>0.32977</v>
+      </c>
+      <c r="AI125" t="n">
+        <v>0.339</v>
+      </c>
+      <c r="AJ125" t="n">
+        <v>0.31207</v>
+      </c>
+      <c r="AK125" t="n">
+        <v>0.31062</v>
+      </c>
+      <c r="AL125" t="n">
+        <v>0.28901</v>
+      </c>
+      <c r="AM125" t="n">
+        <v>0.31319</v>
+      </c>
+      <c r="AN125" t="n">
+        <v>0.31797</v>
+      </c>
+      <c r="AO125" t="n">
+        <v>0.30277</v>
+      </c>
+      <c r="AP125" t="n">
+        <v>0.19602</v>
+      </c>
+      <c r="AQ125" t="n">
+        <v>0.30439</v>
+      </c>
+      <c r="AR125" t="n">
+        <v>0.30829</v>
+      </c>
+      <c r="AS125" t="n">
+        <v>0.34299</v>
+      </c>
+      <c r="AT125" t="n">
+        <v>0.33949</v>
+      </c>
+      <c r="AU125" t="n">
+        <v>0.36477</v>
+      </c>
+      <c r="AV125" t="n">
+        <v>0.31458</v>
+      </c>
+      <c r="AW125" t="n">
+        <v>0.27462</v>
+      </c>
+      <c r="AX125" t="n">
+        <v>0.19827</v>
+      </c>
+      <c r="AY125" t="n">
+        <v>0.30622</v>
+      </c>
+      <c r="AZ125" t="n">
+        <v>0.29867</v>
+      </c>
+      <c r="BA125" t="n">
+        <v>0.32119</v>
+      </c>
+      <c r="BB125" t="n">
+        <v>0.28281</v>
+      </c>
+      <c r="BC125" t="n">
+        <v>0.31016</v>
+      </c>
+      <c r="BD125" t="n">
+        <v>0.31061</v>
+      </c>
+      <c r="BE125" t="n">
+        <v>0.35026</v>
+      </c>
+      <c r="BF125" t="n">
+        <v>0.35857</v>
+      </c>
+      <c r="BG125" t="n">
+        <v>0.30992</v>
+      </c>
+      <c r="BH125" t="n">
+        <v>0.30215</v>
+      </c>
+      <c r="BI125" t="n">
+        <v>0.31119</v>
+      </c>
+      <c r="BJ125" t="n">
+        <v>0.31475</v>
+      </c>
+      <c r="BK125" t="n">
+        <v>0.31083</v>
+      </c>
+      <c r="BL125" t="n">
+        <v>0.31145</v>
+      </c>
+      <c r="BM125" t="n">
+        <v>0.29992</v>
+      </c>
+      <c r="BN125" t="n">
+        <v>0.29865</v>
+      </c>
+      <c r="BO125" t="n">
+        <v>0.30158</v>
+      </c>
+      <c r="BP125" t="n">
+        <v>0.30904</v>
+      </c>
+      <c r="BQ125" t="n">
+        <v>0.30876</v>
+      </c>
+      <c r="BR125" t="n">
+        <v>0.28918</v>
+      </c>
+      <c r="BS125" t="n">
+        <v>0.33626</v>
+      </c>
+      <c r="BT125" t="n">
+        <v>0.25455</v>
+      </c>
+      <c r="BU125" t="n">
+        <v>0.3366</v>
+      </c>
+      <c r="BV125" t="n">
+        <v>0.31191</v>
+      </c>
+      <c r="BW125" t="n">
+        <v>0.32521</v>
+      </c>
+      <c r="BX125" t="n">
+        <v>0.32799</v>
+      </c>
+      <c r="BY125" t="n">
+        <v>0.27531</v>
+      </c>
+      <c r="BZ125" t="n">
+        <v>0.33458</v>
+      </c>
+      <c r="CA125" t="n">
+        <v>0.32025</v>
+      </c>
+      <c r="CB125" t="n">
+        <v>0.32818</v>
+      </c>
+      <c r="CC125" t="n">
+        <v>0.3013</v>
+      </c>
+      <c r="CD125" t="n">
+        <v>0.33679</v>
+      </c>
+      <c r="CE125" t="n">
+        <v>0.32784</v>
+      </c>
+      <c r="CF125" t="n">
+        <v>0.36691</v>
+      </c>
+      <c r="CG125" t="n">
+        <v>0.33941</v>
+      </c>
+      <c r="CH125" t="n">
+        <v>0.40628</v>
+      </c>
+      <c r="CI125" t="n">
+        <v>0.33901</v>
+      </c>
+      <c r="CJ125" t="n">
+        <v>0.33042</v>
+      </c>
+      <c r="CK125" t="n">
+        <v>0.42153</v>
+      </c>
+      <c r="CL125" t="n">
+        <v>0.34441</v>
+      </c>
+      <c r="CM125" t="n">
+        <v>0.44032</v>
+      </c>
+      <c r="CN125" t="n">
+        <v>0.32581</v>
+      </c>
+      <c r="CO125" t="n">
+        <v>0.39744</v>
+      </c>
+      <c r="CP125" t="n">
+        <v>0.35069</v>
+      </c>
+      <c r="CQ125" t="n">
+        <v>0.37676</v>
+      </c>
+      <c r="CR125" t="n">
+        <v>0.37426</v>
+      </c>
+      <c r="CS125" t="n">
+        <v>0.52019</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>46147</v>
+      </c>
+      <c r="B126" t="n">
+        <v>0.31632</v>
+      </c>
+      <c r="C126" t="n">
+        <v>0.86726</v>
+      </c>
+      <c r="D126" t="n">
+        <v>1.45576</v>
+      </c>
+      <c r="E126" t="n">
+        <v>1.14407</v>
+      </c>
+      <c r="F126" t="n">
+        <v>0.6883400000000001</v>
+      </c>
+      <c r="G126" t="n">
+        <v>0.77876</v>
+      </c>
+      <c r="H126" t="n">
+        <v>0.6395700000000001</v>
+      </c>
+      <c r="I126" t="n">
+        <v>0.48976</v>
+      </c>
+      <c r="J126" t="n">
+        <v>0.39113</v>
+      </c>
+      <c r="K126" t="n">
+        <v>0.44067</v>
+      </c>
+      <c r="L126" t="n">
+        <v>0.49079</v>
+      </c>
+      <c r="M126" t="n">
+        <v>0.43053</v>
+      </c>
+      <c r="N126" t="n">
+        <v>0.41355</v>
+      </c>
+      <c r="O126" t="n">
+        <v>0.4055299999999999</v>
+      </c>
+      <c r="P126" t="n">
+        <v>0.40424</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>0.40165</v>
+      </c>
+      <c r="R126" t="n">
+        <v>0.45483</v>
+      </c>
+      <c r="S126" t="n">
+        <v>0.40438</v>
+      </c>
+      <c r="T126" t="n">
+        <v>0.42523</v>
+      </c>
+      <c r="U126" t="n">
+        <v>0.38403</v>
+      </c>
+      <c r="V126" t="n">
+        <v>0.42556</v>
+      </c>
+      <c r="W126" t="n">
+        <v>0.38287</v>
+      </c>
+      <c r="X126" t="n">
+        <v>0.39331</v>
+      </c>
+      <c r="Y126" t="n">
+        <v>0.41035</v>
+      </c>
+      <c r="Z126" t="n">
+        <v>0.38783</v>
+      </c>
+      <c r="AA126" t="n">
+        <v>0.41536</v>
+      </c>
+      <c r="AB126" t="n">
+        <v>0.39866</v>
+      </c>
+      <c r="AC126" t="n">
+        <v>0.4044</v>
+      </c>
+      <c r="AD126" t="n">
+        <v>0.40571</v>
+      </c>
+      <c r="AE126" t="n">
+        <v>0.3727</v>
+      </c>
+      <c r="AF126" t="n">
+        <v>0.38806</v>
+      </c>
+      <c r="AG126" t="n">
+        <v>0.38999</v>
+      </c>
+      <c r="AH126" t="n">
+        <v>0.37359</v>
+      </c>
+      <c r="AI126" t="n">
+        <v>0.48618</v>
+      </c>
+      <c r="AJ126" t="n">
+        <v>0.35546</v>
+      </c>
+      <c r="AK126" t="n">
+        <v>0.2998</v>
+      </c>
+      <c r="AL126" t="n">
+        <v>0.2875</v>
+      </c>
+      <c r="AM126" t="n">
+        <v>0.3418</v>
+      </c>
+      <c r="AN126" t="n">
+        <v>0.3535</v>
+      </c>
+      <c r="AO126" t="n">
+        <v>0.30481</v>
+      </c>
+      <c r="AP126" t="n">
+        <v>0.33246</v>
+      </c>
+      <c r="AQ126" t="n">
+        <v>0.30397</v>
+      </c>
+      <c r="AR126" t="n">
+        <v>0.30909</v>
+      </c>
+      <c r="AS126" t="n">
+        <v>0.29868</v>
+      </c>
+      <c r="AT126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU126" t="n">
+        <v>0.5194299999999999</v>
+      </c>
+      <c r="AV126" t="n">
+        <v>0.3562</v>
+      </c>
+      <c r="AW126" t="n">
+        <v>0.20815</v>
+      </c>
+      <c r="AX126" t="n">
+        <v>0.24893</v>
+      </c>
+      <c r="AY126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ126" t="n">
+        <v>0.29655</v>
+      </c>
+      <c r="BA126" t="n">
+        <v>0.15826</v>
+      </c>
+      <c r="BB126" t="n">
+        <v>0.27451</v>
+      </c>
+      <c r="BC126" t="n">
+        <v>0.27606</v>
+      </c>
+      <c r="BD126" t="n">
+        <v>-0.00173</v>
+      </c>
+      <c r="BE126" t="n">
+        <v>0.33568</v>
+      </c>
+      <c r="BF126" t="n">
+        <v>0.30114</v>
+      </c>
+      <c r="BG126" t="n">
+        <v>0.26062</v>
+      </c>
+      <c r="BH126" t="n">
+        <v>0.25404</v>
+      </c>
+      <c r="BI126" t="n">
+        <v>0.3073</v>
+      </c>
+      <c r="BJ126" t="n">
+        <v>0.2823</v>
+      </c>
+      <c r="BK126" t="n">
+        <v>0.28526</v>
+      </c>
+      <c r="BL126" t="n">
+        <v>0.29417</v>
+      </c>
+      <c r="BM126" t="n">
+        <v>0.28917</v>
+      </c>
+      <c r="BN126" t="n">
+        <v>0.30507</v>
+      </c>
+      <c r="BO126" t="n">
+        <v>0.31054</v>
+      </c>
+      <c r="BP126" t="n">
+        <v>0.31797</v>
+      </c>
+      <c r="BQ126" t="n">
+        <v>0.31879</v>
+      </c>
+      <c r="BR126" t="n">
+        <v>0.31024</v>
+      </c>
+      <c r="BS126" t="n">
+        <v>0.32772</v>
+      </c>
+      <c r="BT126" t="n">
+        <v>0.32888</v>
+      </c>
+      <c r="BU126" t="n">
+        <v>0.38496</v>
+      </c>
+      <c r="BV126" t="n">
+        <v>0.3815</v>
+      </c>
+      <c r="BW126" t="n">
+        <v>0.34349</v>
+      </c>
+      <c r="BX126" t="n">
+        <v>0.35196</v>
+      </c>
+      <c r="BY126" t="n">
+        <v>0.33235</v>
+      </c>
+      <c r="BZ126" t="n">
+        <v>0.31924</v>
+      </c>
+      <c r="CA126" t="n">
+        <v>0.35907</v>
+      </c>
+      <c r="CB126" t="n">
+        <v>0.3337</v>
+      </c>
+      <c r="CC126" t="n">
+        <v>0.34153</v>
+      </c>
+      <c r="CD126" t="n">
+        <v>0.35311</v>
+      </c>
+      <c r="CE126" t="n">
+        <v>0.35379</v>
+      </c>
+      <c r="CF126" t="n">
+        <v>0.34064</v>
+      </c>
+      <c r="CG126" t="n">
+        <v>0.5371900000000001</v>
+      </c>
+      <c r="CH126" t="n">
+        <v>0.42767</v>
+      </c>
+      <c r="CI126" t="n">
+        <v>0.7729299999999999</v>
+      </c>
+      <c r="CJ126" t="n">
+        <v>0.42814</v>
+      </c>
+      <c r="CK126" t="n">
+        <v>0.40559</v>
+      </c>
+      <c r="CL126" t="n">
+        <v>0.36134</v>
+      </c>
+      <c r="CM126" t="n">
+        <v>0.43968</v>
+      </c>
+      <c r="CN126" t="n">
+        <v>0.36706</v>
+      </c>
+      <c r="CO126" t="n">
+        <v>0.35326</v>
+      </c>
+      <c r="CP126" t="n">
+        <v>0.32289</v>
+      </c>
+      <c r="CQ126" t="n">
+        <v>0.32128</v>
+      </c>
+      <c r="CR126" t="n">
+        <v>0.3185</v>
+      </c>
+      <c r="CS126" t="n">
+        <v>0.30489</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>46148</v>
+      </c>
+      <c r="B127" t="n">
+        <v>0.3183</v>
+      </c>
+      <c r="C127" t="n">
+        <v>0.3829</v>
+      </c>
+      <c r="D127" t="n">
+        <v>0.31635</v>
+      </c>
+      <c r="E127" t="n">
+        <v>0.31851</v>
+      </c>
+      <c r="F127" t="n">
+        <v>0.29263</v>
+      </c>
+      <c r="G127" t="n">
+        <v>0.32721</v>
+      </c>
+      <c r="H127" t="n">
+        <v>0.2892</v>
+      </c>
+      <c r="I127" t="n">
+        <v>0.29268</v>
+      </c>
+      <c r="J127" t="n">
+        <v>0.28749</v>
+      </c>
+      <c r="K127" t="n">
+        <v>0.28863</v>
+      </c>
+      <c r="L127" t="n">
+        <v>0.27896</v>
+      </c>
+      <c r="M127" t="n">
+        <v>0.28857</v>
+      </c>
+      <c r="N127" t="n">
+        <v>0.30684</v>
+      </c>
+      <c r="O127" t="n">
+        <v>0.30517</v>
+      </c>
+      <c r="P127" t="n">
+        <v>0.31043</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>0.30651</v>
+      </c>
+      <c r="R127" t="n">
+        <v>0.27501</v>
+      </c>
+      <c r="S127" t="n">
+        <v>0.27503</v>
+      </c>
+      <c r="T127" t="n">
+        <v>0.30033</v>
+      </c>
+      <c r="U127" t="n">
+        <v>0.3152</v>
+      </c>
+      <c r="V127" t="n">
+        <v>0.30198</v>
+      </c>
+      <c r="W127" t="n">
+        <v>0.22645</v>
+      </c>
+      <c r="X127" t="n">
+        <v>0.28343</v>
+      </c>
+      <c r="Y127" t="n">
+        <v>0.33943</v>
+      </c>
+      <c r="Z127" t="n">
+        <v>0.2302</v>
+      </c>
+      <c r="AA127" t="n">
+        <v>0.3105</v>
+      </c>
+      <c r="AB127" t="n">
+        <v>0.34564</v>
+      </c>
+      <c r="AC127" t="n">
+        <v>0.32413</v>
+      </c>
+      <c r="AD127" t="n">
+        <v>0.32724</v>
+      </c>
+      <c r="AE127" t="n">
+        <v>0.32946</v>
+      </c>
+      <c r="AF127" t="n">
+        <v>0.32362</v>
+      </c>
+      <c r="AG127" t="n">
+        <v>0.31548</v>
+      </c>
+      <c r="AH127" t="n">
+        <v>0.28901</v>
+      </c>
+      <c r="AI127" t="n">
+        <v>0.31077</v>
+      </c>
+      <c r="AJ127" t="n">
+        <v>0.22857</v>
+      </c>
+      <c r="AK127" t="n">
+        <v>0.32201</v>
+      </c>
+      <c r="AL127" t="n">
+        <v>0.26884</v>
+      </c>
+      <c r="AM127" t="n">
+        <v>0.26327</v>
+      </c>
+      <c r="AN127" t="n">
+        <v>0.28214</v>
+      </c>
+      <c r="AO127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP127" t="n">
+        <v>0.26639</v>
+      </c>
+      <c r="AQ127" t="n">
+        <v>0.23001</v>
+      </c>
+      <c r="AR127" t="n">
+        <v>0.1657</v>
+      </c>
+      <c r="AS127" t="n">
+        <v>0.15674</v>
+      </c>
+      <c r="AT127" t="n">
+        <v>0.27706</v>
+      </c>
+      <c r="AU127" t="n">
+        <v>0.15946</v>
+      </c>
+      <c r="AV127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX127" t="n">
+        <v>0.1609</v>
+      </c>
+      <c r="AY127" t="n">
+        <v>0.15718</v>
+      </c>
+      <c r="AZ127" t="n">
+        <v>0.25539</v>
+      </c>
+      <c r="BA127" t="n">
+        <v>0.15695</v>
+      </c>
+      <c r="BB127" t="n">
+        <v>0.25291</v>
+      </c>
+      <c r="BC127" t="n">
+        <v>0.1603</v>
+      </c>
+      <c r="BD127" t="n">
+        <v>0.25237</v>
+      </c>
+      <c r="BE127" t="n">
+        <v>0.27866</v>
+      </c>
+      <c r="BF127" t="n">
+        <v>0.22918</v>
+      </c>
+      <c r="BG127" t="n">
+        <v>0.14572</v>
+      </c>
+      <c r="BH127" t="n">
+        <v>0.13201</v>
+      </c>
+      <c r="BI127" t="n">
+        <v>0.14143</v>
+      </c>
+      <c r="BJ127" t="n">
+        <v>0.14973</v>
+      </c>
+      <c r="BK127" t="n">
+        <v>0.2105</v>
+      </c>
+      <c r="BL127" t="n">
+        <v>0.16301</v>
+      </c>
+      <c r="BM127" t="n">
+        <v>0.26939</v>
+      </c>
+      <c r="BN127" t="n">
+        <v>0.31061</v>
+      </c>
+      <c r="BO127" t="n">
+        <v>0.29903</v>
+      </c>
+      <c r="BP127" t="n">
+        <v>0.30796</v>
+      </c>
+      <c r="BQ127" t="n">
+        <v>0.33097</v>
+      </c>
+      <c r="BR127" t="n">
+        <v>0.31833</v>
+      </c>
+      <c r="BS127" t="n">
+        <v>0.34012</v>
+      </c>
+      <c r="BT127" t="n">
+        <v>0.32843</v>
+      </c>
+      <c r="BU127" t="n">
+        <v>0.33559</v>
+      </c>
+      <c r="BV127" t="n">
+        <v>0.33192</v>
+      </c>
+      <c r="BW127" t="n">
+        <v>0.36024</v>
+      </c>
+      <c r="BX127" t="n">
+        <v>0.33552</v>
+      </c>
+      <c r="BY127" t="n">
+        <v>0.37511</v>
+      </c>
+      <c r="BZ127" t="n">
+        <v>0.3431</v>
+      </c>
+      <c r="CA127" t="n">
+        <v>0.36165</v>
+      </c>
+      <c r="CB127" t="n">
+        <v>0.41013</v>
+      </c>
+      <c r="CC127" t="n">
+        <v>0.37277</v>
+      </c>
+      <c r="CD127" t="n">
+        <v>0.36691</v>
+      </c>
+      <c r="CE127" t="n">
+        <v>0.37396</v>
+      </c>
+      <c r="CF127" t="n">
+        <v>0.37192</v>
+      </c>
+      <c r="CG127" t="n">
+        <v>0.41413</v>
+      </c>
+      <c r="CH127" t="n">
+        <v>0.40218</v>
+      </c>
+      <c r="CI127" t="n">
+        <v>0.40282</v>
+      </c>
+      <c r="CJ127" t="n">
+        <v>0.40707</v>
+      </c>
+      <c r="CK127" t="n">
+        <v>0.43632</v>
+      </c>
+      <c r="CL127" t="n">
+        <v>0.39375</v>
+      </c>
+      <c r="CM127" t="n">
+        <v>0.38183</v>
+      </c>
+      <c r="CN127" t="n">
+        <v>0.38927</v>
+      </c>
+      <c r="CO127" t="n">
+        <v>0.38314</v>
+      </c>
+      <c r="CP127" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="CQ127" t="n">
+        <v>0.34101</v>
+      </c>
+      <c r="CR127" t="n">
+        <v>0.32233</v>
+      </c>
+      <c r="CS127" t="n">
+        <v>0.33146</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>46149</v>
+      </c>
+      <c r="B128" t="n">
+        <v>0.32633</v>
+      </c>
+      <c r="C128" t="n">
+        <v>0.48067</v>
+      </c>
+      <c r="D128" t="n">
+        <v>0.38102</v>
+      </c>
+      <c r="E128" t="n">
+        <v>0.42812</v>
+      </c>
+      <c r="F128" t="n">
+        <v>0.3941</v>
+      </c>
+      <c r="G128" t="n">
+        <v>0.38774</v>
+      </c>
+      <c r="H128" t="n">
+        <v>0.35198</v>
+      </c>
+      <c r="I128" t="n">
+        <v>0.36065</v>
+      </c>
+      <c r="J128" t="n">
+        <v>0.35956</v>
+      </c>
+      <c r="K128" t="n">
+        <v>0.37042</v>
+      </c>
+      <c r="L128" t="n">
+        <v>0.37188</v>
+      </c>
+      <c r="M128" t="n">
+        <v>0.36243</v>
+      </c>
+      <c r="N128" t="n">
+        <v>0.36228</v>
+      </c>
+      <c r="O128" t="n">
+        <v>0.3462</v>
+      </c>
+      <c r="P128" t="n">
+        <v>0.37006</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>0.35356</v>
+      </c>
+      <c r="R128" t="n">
+        <v>0.35942</v>
+      </c>
+      <c r="S128" t="n">
+        <v>0.33639</v>
+      </c>
+      <c r="T128" t="n">
+        <v>0.33409</v>
+      </c>
+      <c r="U128" t="n">
+        <v>0.34099</v>
+      </c>
+      <c r="V128" t="n">
+        <v>0.3322</v>
+      </c>
+      <c r="W128" t="n">
+        <v>0.32845</v>
+      </c>
+      <c r="X128" t="n">
+        <v>0.33259</v>
+      </c>
+      <c r="Y128" t="n">
+        <v>0.32845</v>
+      </c>
+      <c r="Z128" t="n">
+        <v>0.33752</v>
+      </c>
+      <c r="AA128" t="n">
+        <v>0.4124</v>
+      </c>
+      <c r="AB128" t="n">
+        <v>0.35136</v>
+      </c>
+      <c r="AC128" t="n">
+        <v>0.3602</v>
+      </c>
+      <c r="AD128" t="n">
+        <v>0.34489</v>
+      </c>
+      <c r="AE128" t="n">
+        <v>0.33026</v>
+      </c>
+      <c r="AF128" t="n">
+        <v>0.32782</v>
+      </c>
+      <c r="AG128" t="n">
+        <v>0.33045</v>
+      </c>
+      <c r="AH128" t="n">
+        <v>0.3195</v>
+      </c>
+      <c r="AI128" t="n">
+        <v>0.33175</v>
+      </c>
+      <c r="AJ128" t="n">
+        <v>0.33846</v>
+      </c>
+      <c r="AK128" t="n">
+        <v>0.35335</v>
+      </c>
+      <c r="AL128" t="n">
+        <v>0.29391</v>
+      </c>
+      <c r="AM128" t="n">
+        <v>0.30875</v>
+      </c>
+      <c r="AN128" t="n">
+        <v>0.31286</v>
+      </c>
+      <c r="AO128" t="n">
+        <v>0.30555</v>
+      </c>
+      <c r="AP128" t="n">
+        <v>0.29221</v>
+      </c>
+      <c r="AQ128" t="n">
+        <v>0.2943</v>
+      </c>
+      <c r="AR128" t="n">
+        <v>0.27332</v>
+      </c>
+      <c r="AS128" t="n">
+        <v>0.31955</v>
+      </c>
+      <c r="AT128" t="n">
+        <v>0.26319</v>
+      </c>
+      <c r="AU128" t="n">
+        <v>0.3018</v>
+      </c>
+      <c r="AV128" t="n">
+        <v>0.28941</v>
+      </c>
+      <c r="AW128" t="n">
+        <v>0.25412</v>
+      </c>
+      <c r="AX128" t="n">
+        <v>0.28628</v>
+      </c>
+      <c r="AY128" t="n">
+        <v>0.30087</v>
+      </c>
+      <c r="AZ128" t="n">
+        <v>0.30137</v>
+      </c>
+      <c r="BA128" t="n">
+        <v>0.3181</v>
+      </c>
+      <c r="BB128" t="n">
+        <v>0.31729</v>
+      </c>
+      <c r="BC128" t="n">
+        <v>0.32564</v>
+      </c>
+      <c r="BD128" t="n">
+        <v>0.36508</v>
+      </c>
+      <c r="BE128" t="n">
+        <v>0.31359</v>
+      </c>
+      <c r="BF128" t="n">
+        <v>0.31354</v>
+      </c>
+      <c r="BG128" t="n">
+        <v>0.29655</v>
+      </c>
+      <c r="BH128" t="n">
+        <v>0.23587</v>
+      </c>
+      <c r="BI128" t="n">
+        <v>0.3113</v>
+      </c>
+      <c r="BJ128" t="n">
+        <v>0.30225</v>
+      </c>
+      <c r="BK128" t="n">
+        <v>0.31851</v>
+      </c>
+      <c r="BL128" t="n">
+        <v>0.32219</v>
+      </c>
+      <c r="BM128" t="n">
+        <v>0.29257</v>
+      </c>
+      <c r="BN128" t="n">
+        <v>0.42158</v>
+      </c>
+      <c r="BO128" t="n">
+        <v>0.3312</v>
+      </c>
+      <c r="BP128" t="n">
+        <v>0.36263</v>
+      </c>
+      <c r="BQ128" t="n">
+        <v>0.34124</v>
+      </c>
+      <c r="BR128" t="n">
+        <v>0.33278</v>
+      </c>
+      <c r="BS128" t="n">
+        <v>0.3185</v>
+      </c>
+      <c r="BT128" t="n">
+        <v>0.40431</v>
+      </c>
+      <c r="BU128" t="n">
+        <v>0.37309</v>
+      </c>
+      <c r="BV128" t="n">
+        <v>0.34446</v>
+      </c>
+      <c r="BW128" t="n">
+        <v>0.34055</v>
+      </c>
+      <c r="BX128" t="n">
+        <v>0.34319</v>
+      </c>
+      <c r="BY128" t="n">
+        <v>0.35125</v>
+      </c>
+      <c r="BZ128" t="n">
+        <v>0.35875</v>
+      </c>
+      <c r="CA128" t="n">
+        <v>0.36763</v>
+      </c>
+      <c r="CB128" t="n">
+        <v>0.37507</v>
+      </c>
+      <c r="CC128" t="n">
+        <v>0.23358</v>
+      </c>
+      <c r="CD128" t="n">
+        <v>0.37693</v>
+      </c>
+      <c r="CE128" t="n">
+        <v>0.37023</v>
+      </c>
+      <c r="CF128" t="n">
+        <v>0.3462</v>
+      </c>
+      <c r="CG128" t="n">
+        <v>0.34434</v>
+      </c>
+      <c r="CH128" t="n">
+        <v>0.34189</v>
+      </c>
+      <c r="CI128" t="n">
+        <v>0.39233</v>
+      </c>
+      <c r="CJ128" t="n">
+        <v>0.33963</v>
+      </c>
+      <c r="CK128" t="n">
+        <v>0.34242</v>
+      </c>
+      <c r="CL128" t="n">
+        <v>0.35498</v>
+      </c>
+      <c r="CM128" t="n">
+        <v>0.35674</v>
+      </c>
+      <c r="CN128" t="n">
+        <v>0.34954</v>
+      </c>
+      <c r="CO128" t="n">
+        <v>0.35668</v>
+      </c>
+      <c r="CP128" t="n">
+        <v>0.36247</v>
+      </c>
+      <c r="CQ128" t="n">
+        <v>0.36626</v>
+      </c>
+      <c r="CR128" t="n">
+        <v>0.33835</v>
+      </c>
+      <c r="CS128" t="n">
+        <v>0.34614</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="B129" t="n">
+        <v>0.33474</v>
+      </c>
+      <c r="C129" t="n">
+        <v>0.35107</v>
+      </c>
+      <c r="D129" t="n">
+        <v>0.45133</v>
+      </c>
+      <c r="E129" t="n">
+        <v>0.36286</v>
+      </c>
+      <c r="F129" t="n">
+        <v>0.46423</v>
+      </c>
+      <c r="G129" t="n">
+        <v>0.36266</v>
+      </c>
+      <c r="H129" t="n">
+        <v>0.34013</v>
+      </c>
+      <c r="I129" t="n">
+        <v>0.34893</v>
+      </c>
+      <c r="J129" t="n">
+        <v>0.34271</v>
+      </c>
+      <c r="K129" t="n">
+        <v>0.3349</v>
+      </c>
+      <c r="L129" t="n">
+        <v>0.3289</v>
+      </c>
+      <c r="M129" t="n">
+        <v>0.33374</v>
+      </c>
+      <c r="N129" t="n">
+        <v>0.33324</v>
+      </c>
+      <c r="O129" t="n">
+        <v>0.33662</v>
+      </c>
+      <c r="P129" t="n">
+        <v>0.33898</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>0.33531</v>
+      </c>
+      <c r="R129" t="n">
+        <v>0.33115</v>
+      </c>
+      <c r="S129" t="n">
+        <v>0.32987</v>
+      </c>
+      <c r="T129" t="n">
+        <v>0.33518</v>
+      </c>
+      <c r="U129" t="n">
+        <v>0.33064</v>
+      </c>
+      <c r="V129" t="n">
+        <v>0.32662</v>
+      </c>
+      <c r="W129" t="n">
+        <v>0.33197</v>
+      </c>
+      <c r="X129" t="n">
+        <v>0.32786</v>
+      </c>
+      <c r="Y129" t="n">
+        <v>0.32875</v>
+      </c>
+      <c r="Z129" t="n">
+        <v>0.33241</v>
+      </c>
+      <c r="AA129" t="n">
+        <v>0.33605</v>
+      </c>
+      <c r="AB129" t="n">
+        <v>0.35745</v>
+      </c>
+      <c r="AC129" t="n">
+        <v>0.37228</v>
+      </c>
+      <c r="AD129" t="n">
+        <v>0.36798</v>
+      </c>
+      <c r="AE129" t="n">
+        <v>0.35903</v>
+      </c>
+      <c r="AF129" t="n">
+        <v>0.32647</v>
+      </c>
+      <c r="AG129" t="n">
+        <v>0.33128</v>
+      </c>
+      <c r="AH129" t="n">
+        <v>0.32423</v>
+      </c>
+      <c r="AI129" t="n">
+        <v>0.3435</v>
+      </c>
+      <c r="AJ129" t="n">
+        <v>0.39025</v>
+      </c>
+      <c r="AK129" t="n">
+        <v>1.24784</v>
+      </c>
+      <c r="AL129" t="n">
+        <v>0.36282</v>
+      </c>
+      <c r="AM129" t="n">
+        <v>0.71941</v>
+      </c>
+      <c r="AN129" t="n">
+        <v>0.41824</v>
+      </c>
+      <c r="AO129" t="n">
+        <v>0.44453</v>
+      </c>
+      <c r="AP129" t="n">
+        <v>0.43185</v>
+      </c>
+      <c r="AQ129" t="n">
+        <v>0.39775</v>
+      </c>
+      <c r="AR129" t="n">
+        <v>0.40515</v>
+      </c>
+      <c r="AS129" t="n">
+        <v>0.57233</v>
+      </c>
+      <c r="AT129" t="n">
+        <v>0.43789</v>
+      </c>
+      <c r="AU129" t="n">
+        <v>0.46475</v>
+      </c>
+      <c r="AV129" t="n">
+        <v>0.39212</v>
+      </c>
+      <c r="AW129" t="n">
+        <v>0.53284</v>
+      </c>
+      <c r="AX129" t="n">
+        <v>0.23959</v>
+      </c>
+      <c r="AY129" t="n">
+        <v>0.5910700000000001</v>
+      </c>
+      <c r="AZ129" t="n">
+        <v>0.40726</v>
+      </c>
+      <c r="BA129" t="n">
+        <v>0.43561</v>
+      </c>
+      <c r="BB129" t="n">
+        <v>0.5658200000000001</v>
+      </c>
+      <c r="BC129" t="n">
+        <v>0.5300499999999999</v>
+      </c>
+      <c r="BD129" t="n">
+        <v>0.4482</v>
+      </c>
+      <c r="BE129" t="n">
+        <v>0.86376</v>
+      </c>
+      <c r="BF129" t="n">
+        <v>0.42184</v>
+      </c>
+      <c r="BG129" t="n">
+        <v>0.36937</v>
+      </c>
+      <c r="BH129" t="n">
+        <v>0.37944</v>
+      </c>
+      <c r="BI129" t="n">
+        <v>0.37549</v>
+      </c>
+      <c r="BJ129" t="n">
+        <v>0.36254</v>
+      </c>
+      <c r="BK129" t="n">
+        <v>0.47938</v>
+      </c>
+      <c r="BL129" t="n">
+        <v>0.37763</v>
+      </c>
+      <c r="BM129" t="n">
+        <v>0.47724</v>
+      </c>
+      <c r="BN129" t="n">
+        <v>0.49518</v>
+      </c>
+      <c r="BO129" t="n">
+        <v>0.39596</v>
+      </c>
+      <c r="BP129" t="n">
+        <v>0.41675</v>
+      </c>
+      <c r="BQ129" t="n">
+        <v>0.32929</v>
+      </c>
+      <c r="BR129" t="n">
+        <v>0.44829</v>
+      </c>
+      <c r="BS129" t="n">
+        <v>0.3373</v>
+      </c>
+      <c r="BT129" t="n">
+        <v>0.3037</v>
+      </c>
+      <c r="BU129" t="n">
+        <v>0.39561</v>
+      </c>
+      <c r="BV129" t="n">
+        <v>0.32137</v>
+      </c>
+      <c r="BW129" t="n">
+        <v>0.3148</v>
+      </c>
+      <c r="BX129" t="n">
+        <v>0.64232</v>
+      </c>
+      <c r="BY129" t="n">
+        <v>0.44094</v>
+      </c>
+      <c r="BZ129" t="n">
+        <v>0.42314</v>
+      </c>
+      <c r="CA129" t="n">
+        <v>0.42181</v>
+      </c>
+      <c r="CB129" t="n">
+        <v>0.40396</v>
+      </c>
+      <c r="CC129" t="n">
+        <v>0.67801</v>
+      </c>
+      <c r="CD129" t="n">
+        <v>0.35013</v>
+      </c>
+      <c r="CE129" t="n">
+        <v>0.63739</v>
+      </c>
+      <c r="CF129" t="n">
+        <v>0.59554</v>
+      </c>
+      <c r="CG129" t="n">
+        <v>0.5105500000000001</v>
+      </c>
+      <c r="CH129" t="n">
+        <v>0.36688</v>
+      </c>
+      <c r="CI129" t="n">
+        <v>0.50246</v>
+      </c>
+      <c r="CJ129" t="n">
+        <v>0.24038</v>
+      </c>
+      <c r="CK129" t="n">
+        <v>0.36732</v>
+      </c>
+      <c r="CL129" t="n">
+        <v>0.35283</v>
+      </c>
+      <c r="CM129" t="n">
+        <v>0.32904</v>
+      </c>
+      <c r="CN129" t="n">
+        <v>0.33108</v>
+      </c>
+      <c r="CO129" t="n">
+        <v>0.33407</v>
+      </c>
+      <c r="CP129" t="n">
+        <v>0.31286</v>
+      </c>
+      <c r="CQ129" t="n">
+        <v>0.34008</v>
+      </c>
+      <c r="CR129" t="n">
+        <v>0.25488</v>
+      </c>
+      <c r="CS129" t="n">
+        <v>0.30824</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="n">
+        <v>46151</v>
+      </c>
+      <c r="B130" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="C130" t="n">
+        <v>0.34524</v>
+      </c>
+      <c r="D130" t="n">
+        <v>0.39298</v>
+      </c>
+      <c r="E130" t="n">
+        <v>0.41721</v>
+      </c>
+      <c r="F130" t="n">
+        <v>0.33672</v>
+      </c>
+      <c r="G130" t="n">
+        <v>0.32052</v>
+      </c>
+      <c r="H130" t="n">
+        <v>0.33258</v>
+      </c>
+      <c r="I130" t="n">
+        <v>0.34921</v>
+      </c>
+      <c r="J130" t="n">
+        <v>0.30897</v>
+      </c>
+      <c r="K130" t="n">
+        <v>0.30831</v>
+      </c>
+      <c r="L130" t="n">
+        <v>0.32601</v>
+      </c>
+      <c r="M130" t="n">
+        <v>0.32841</v>
+      </c>
+      <c r="N130" t="n">
+        <v>0.31732</v>
+      </c>
+      <c r="O130" t="n">
+        <v>0.31714</v>
+      </c>
+      <c r="P130" t="n">
+        <v>0.31581</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>0.31337</v>
+      </c>
+      <c r="R130" t="n">
+        <v>0.30848</v>
+      </c>
+      <c r="S130" t="n">
+        <v>0.31881</v>
+      </c>
+      <c r="T130" t="n">
+        <v>0.295</v>
+      </c>
+      <c r="U130" t="n">
+        <v>0.28205</v>
+      </c>
+      <c r="V130" t="n">
+        <v>0.29886</v>
+      </c>
+      <c r="W130" t="n">
+        <v>0.31226</v>
+      </c>
+      <c r="X130" t="n">
+        <v>0.31544</v>
+      </c>
+      <c r="Y130" t="n">
+        <v>0.31004</v>
+      </c>
+      <c r="Z130" t="n">
+        <v>0.29473</v>
+      </c>
+      <c r="AA130" t="n">
+        <v>0.2996</v>
+      </c>
+      <c r="AB130" t="n">
+        <v>0.31196</v>
+      </c>
+      <c r="AC130" t="n">
+        <v>0.31273</v>
+      </c>
+      <c r="AD130" t="n">
+        <v>0.30374</v>
+      </c>
+      <c r="AE130" t="n">
+        <v>0.28992</v>
+      </c>
+      <c r="AF130" t="n">
+        <v>0.31569</v>
+      </c>
+      <c r="AG130" t="n">
+        <v>0.3079</v>
+      </c>
+      <c r="AH130" t="n">
+        <v>0.32951</v>
+      </c>
+      <c r="AI130" t="n">
+        <v>0.34811</v>
+      </c>
+      <c r="AJ130" t="n">
+        <v>0.3719</v>
+      </c>
+      <c r="AK130" t="n">
+        <v>0.37094</v>
+      </c>
+      <c r="AL130" t="n">
+        <v>0.32698</v>
+      </c>
+      <c r="AM130" t="n">
+        <v>0.41746</v>
+      </c>
+      <c r="AN130" t="n">
+        <v>0.36219</v>
+      </c>
+      <c r="AO130" t="n">
+        <v>0.34195</v>
+      </c>
+      <c r="AP130" t="n">
+        <v>0.31772</v>
+      </c>
+      <c r="AQ130" t="n">
+        <v>0.34251</v>
+      </c>
+      <c r="AR130" t="n">
+        <v>0.33011</v>
+      </c>
+      <c r="AS130" t="n">
+        <v>0.31511</v>
+      </c>
+      <c r="AT130" t="n">
+        <v>0.33168</v>
+      </c>
+      <c r="AU130" t="n">
+        <v>0.33185</v>
+      </c>
+      <c r="AV130" t="n">
+        <v>0.30866</v>
+      </c>
+      <c r="AW130" t="n">
+        <v>0.32494</v>
+      </c>
+      <c r="AX130" t="n">
+        <v>0.27585</v>
+      </c>
+      <c r="AY130" t="n">
+        <v>0.32358</v>
+      </c>
+      <c r="AZ130" t="n">
+        <v>0.31113</v>
+      </c>
+      <c r="BA130" t="n">
+        <v>0.3116</v>
+      </c>
+      <c r="BB130" t="n">
+        <v>0.31773</v>
+      </c>
+      <c r="BC130" t="n">
+        <v>0.32012</v>
+      </c>
+      <c r="BD130" t="n">
+        <v>0.32673</v>
+      </c>
+      <c r="BE130" t="n">
+        <v>0.3295</v>
+      </c>
+      <c r="BF130" t="n">
+        <v>0.31977</v>
+      </c>
+      <c r="BG130" t="n">
+        <v>0.31596</v>
+      </c>
+      <c r="BH130" t="n">
+        <v>0.30557</v>
+      </c>
+      <c r="BI130" t="n">
+        <v>0.30863</v>
+      </c>
+      <c r="BJ130" t="n">
+        <v>0.31037</v>
+      </c>
+      <c r="BK130" t="n">
+        <v>0.32725</v>
+      </c>
+      <c r="BL130" t="n">
+        <v>0.33572</v>
+      </c>
+      <c r="BM130" t="n">
+        <v>0.3785</v>
+      </c>
+      <c r="BN130" t="n">
+        <v>0.5307799999999999</v>
+      </c>
+      <c r="BO130" t="n">
+        <v>0.37584</v>
+      </c>
+      <c r="BP130" t="n">
+        <v>0.35487</v>
+      </c>
+      <c r="BQ130" t="n">
+        <v>0.32977</v>
+      </c>
+      <c r="BR130" t="n">
+        <v>0.33781</v>
+      </c>
+      <c r="BS130" t="n">
+        <v>0.3468</v>
+      </c>
+      <c r="BT130" t="n">
+        <v>0.34076</v>
+      </c>
+      <c r="BU130" t="n">
+        <v>0.33815</v>
+      </c>
+      <c r="BV130" t="n">
+        <v>0.33724</v>
+      </c>
+      <c r="BW130" t="n">
+        <v>0.31232</v>
+      </c>
+      <c r="BX130" t="n">
+        <v>0.31796</v>
+      </c>
+      <c r="BY130" t="n">
+        <v>0.2934</v>
+      </c>
+      <c r="BZ130" t="n">
+        <v>0.33668</v>
+      </c>
+      <c r="CA130" t="n">
+        <v>0.34724</v>
+      </c>
+      <c r="CB130" t="n">
+        <v>0.35436</v>
+      </c>
+      <c r="CC130" t="n">
+        <v>0.34626</v>
+      </c>
+      <c r="CD130" t="n">
+        <v>0.33704</v>
+      </c>
+      <c r="CE130" t="n">
+        <v>0.34745</v>
+      </c>
+      <c r="CF130" t="n">
+        <v>0.34418</v>
+      </c>
+      <c r="CG130" t="n">
+        <v>0.35154</v>
+      </c>
+      <c r="CH130" t="n">
+        <v>0.35415</v>
+      </c>
+      <c r="CI130" t="n">
+        <v>0.36113</v>
+      </c>
+      <c r="CJ130" t="n">
+        <v>0.36392</v>
+      </c>
+      <c r="CK130" t="n">
+        <v>0.35632</v>
+      </c>
+      <c r="CL130" t="n">
+        <v>0.34719</v>
+      </c>
+      <c r="CM130" t="n">
+        <v>0.35397</v>
+      </c>
+      <c r="CN130" t="n">
+        <v>0.35554</v>
+      </c>
+      <c r="CO130" t="n">
+        <v>0.32183</v>
+      </c>
+      <c r="CP130" t="n">
+        <v>0.30274</v>
+      </c>
+      <c r="CQ130" t="n">
+        <v>0.3424</v>
+      </c>
+      <c r="CR130" t="n">
+        <v>0.32007</v>
+      </c>
+      <c r="CS130" t="n">
+        <v>0.342</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="n">
+        <v>46152</v>
+      </c>
+      <c r="B131" t="n">
+        <v>0.32759</v>
+      </c>
+      <c r="C131" t="n">
+        <v>0.34277</v>
+      </c>
+      <c r="D131" t="n">
+        <v>0.34176</v>
+      </c>
+      <c r="E131" t="n">
+        <v>0.34277</v>
+      </c>
+      <c r="F131" t="n">
+        <v>0.34374</v>
+      </c>
+      <c r="G131" t="n">
+        <v>0.3432</v>
+      </c>
+      <c r="H131" t="n">
+        <v>0.3424</v>
+      </c>
+      <c r="I131" t="n">
+        <v>0.33195</v>
+      </c>
+      <c r="J131" t="n">
+        <v>0.34178</v>
+      </c>
+      <c r="K131" t="n">
+        <v>0.33863</v>
+      </c>
+      <c r="L131" t="n">
+        <v>0.2639</v>
+      </c>
+      <c r="M131" t="n">
+        <v>0.33941</v>
+      </c>
+      <c r="N131" t="n">
+        <v>0.33229</v>
+      </c>
+      <c r="O131" t="n">
+        <v>0.33317</v>
+      </c>
+      <c r="P131" t="n">
+        <v>0.32088</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>0.33195</v>
+      </c>
+      <c r="R131" t="n">
+        <v>0.33241</v>
+      </c>
+      <c r="S131" t="n">
+        <v>0.32585</v>
+      </c>
+      <c r="T131" t="n">
+        <v>0.34734</v>
+      </c>
+      <c r="U131" t="n">
+        <v>0.31675</v>
+      </c>
+      <c r="V131" t="n">
+        <v>0.32421</v>
+      </c>
+      <c r="W131" t="n">
+        <v>0.33195</v>
+      </c>
+      <c r="X131" t="n">
+        <v>0.33269</v>
+      </c>
+      <c r="Y131" t="n">
+        <v>0.32358</v>
+      </c>
+      <c r="Z131" t="n">
+        <v>0.32266</v>
+      </c>
+      <c r="AA131" t="n">
+        <v>0.33741</v>
+      </c>
+      <c r="AB131" t="n">
+        <v>0.32271</v>
+      </c>
+      <c r="AC131" t="n">
+        <v>0.33425</v>
+      </c>
+      <c r="AD131" t="n">
+        <v>0.33412</v>
+      </c>
+      <c r="AE131" t="n">
+        <v>0.32873</v>
+      </c>
+      <c r="AF131" t="n">
+        <v>0.3249</v>
+      </c>
+      <c r="AG131" t="n">
+        <v>0.3145</v>
+      </c>
+      <c r="AH131" t="n">
+        <v>0.33212</v>
+      </c>
+      <c r="AI131" t="n">
+        <v>0.32831</v>
+      </c>
+      <c r="AJ131" t="n">
+        <v>0.31704</v>
+      </c>
+      <c r="AK131" t="n">
+        <v>0.32337</v>
+      </c>
+      <c r="AL131" t="n">
+        <v>0.29896</v>
+      </c>
+      <c r="AM131" t="n">
+        <v>0.31749</v>
+      </c>
+      <c r="AN131" t="n">
+        <v>0.32103</v>
+      </c>
+      <c r="AO131" t="n">
+        <v>0.32374</v>
+      </c>
+      <c r="AP131" t="n">
+        <v>0.32258</v>
+      </c>
+      <c r="AQ131" t="n">
+        <v>0.31401</v>
+      </c>
+      <c r="AR131" t="n">
+        <v>0.32256</v>
+      </c>
+      <c r="AS131" t="n">
+        <v>0.31407</v>
+      </c>
+      <c r="AT131" t="n">
+        <v>0.31513</v>
+      </c>
+      <c r="AU131" t="n">
+        <v>0.32259</v>
+      </c>
+      <c r="AV131" t="n">
+        <v>0.32028</v>
+      </c>
+      <c r="AW131" t="n">
+        <v>0.3282</v>
+      </c>
+      <c r="AX131" t="n">
+        <v>0.31715</v>
+      </c>
+      <c r="AY131" t="n">
+        <v>0.36929</v>
+      </c>
+      <c r="AZ131" t="n">
+        <v>0.32652</v>
+      </c>
+      <c r="BA131" t="n">
+        <v>0.31882</v>
+      </c>
+      <c r="BB131" t="n">
+        <v>0.39554</v>
+      </c>
+      <c r="BC131" t="n">
+        <v>0.5098199999999999</v>
+      </c>
+      <c r="BD131" t="n">
+        <v>0.3404700000000001</v>
+      </c>
+      <c r="BE131" t="n">
+        <v>0.3691</v>
+      </c>
+      <c r="BF131" t="n">
+        <v>0.3454</v>
+      </c>
+      <c r="BG131" t="n">
+        <v>0.33452</v>
+      </c>
+      <c r="BH131" t="n">
+        <v>0.33833</v>
+      </c>
+      <c r="BI131" t="n">
+        <v>0.35774</v>
+      </c>
+      <c r="BJ131" t="n">
+        <v>0.34032</v>
+      </c>
+      <c r="BK131" t="n">
+        <v>0.33531</v>
+      </c>
+      <c r="BL131" t="n">
+        <v>0.33288</v>
+      </c>
+      <c r="BM131" t="n">
+        <v>0.34095</v>
+      </c>
+      <c r="BN131" t="n">
+        <v>0.34917</v>
+      </c>
+      <c r="BO131" t="n">
+        <v>0.38338</v>
+      </c>
+      <c r="BP131" t="n">
+        <v>0.34626</v>
+      </c>
+      <c r="BQ131" t="n">
+        <v>0.34609</v>
+      </c>
+      <c r="BR131" t="n">
+        <v>0.35199</v>
+      </c>
+      <c r="BS131" t="n">
+        <v>0.35804</v>
+      </c>
+      <c r="BT131" t="n">
+        <v>0.34219</v>
+      </c>
+      <c r="BU131" t="n">
+        <v>0.34798</v>
+      </c>
+      <c r="BV131" t="n">
+        <v>0.33695</v>
+      </c>
+      <c r="BW131" t="n">
+        <v>0.34776</v>
+      </c>
+      <c r="BX131" t="n">
+        <v>0.35113</v>
+      </c>
+      <c r="BY131" t="n">
+        <v>0.3526</v>
+      </c>
+      <c r="BZ131" t="n">
+        <v>0.34108</v>
+      </c>
+      <c r="CA131" t="n">
+        <v>0.36835</v>
+      </c>
+      <c r="CB131" t="n">
+        <v>0.35794</v>
+      </c>
+      <c r="CC131" t="n">
+        <v>0.3642</v>
+      </c>
+      <c r="CD131" t="n">
+        <v>0.36931</v>
+      </c>
+      <c r="CE131" t="n">
+        <v>0.40061</v>
+      </c>
+      <c r="CF131" t="n">
+        <v>0.40146</v>
+      </c>
+      <c r="CG131" t="n">
+        <v>0.36448</v>
+      </c>
+      <c r="CH131" t="n">
+        <v>0.36817</v>
+      </c>
+      <c r="CI131" t="n">
+        <v>0.64922</v>
+      </c>
+      <c r="CJ131" t="n">
+        <v>0.64471</v>
+      </c>
+      <c r="CK131" t="n">
+        <v>0.42397</v>
+      </c>
+      <c r="CL131" t="n">
+        <v>0.24534</v>
+      </c>
+      <c r="CM131" t="n">
+        <v>0.42188</v>
+      </c>
+      <c r="CN131" t="n">
+        <v>0.44922</v>
+      </c>
+      <c r="CO131" t="n">
+        <v>0.34275</v>
+      </c>
+      <c r="CP131" t="n">
+        <v>0.41153</v>
+      </c>
+      <c r="CQ131" t="n">
+        <v>0.35165</v>
+      </c>
+      <c r="CR131" t="n">
+        <v>0.33207</v>
+      </c>
+      <c r="CS131" t="n">
+        <v>0.3324</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="B132" t="n">
+        <v>0.32215</v>
+      </c>
+      <c r="C132" t="n">
+        <v>0.40339</v>
+      </c>
+      <c r="D132" t="n">
+        <v>0.36852</v>
+      </c>
+      <c r="E132" t="n">
+        <v>0.35846</v>
+      </c>
+      <c r="F132" t="n">
+        <v>0.35428</v>
+      </c>
+      <c r="G132" t="n">
+        <v>0.35142</v>
+      </c>
+      <c r="H132" t="n">
+        <v>0.35109</v>
+      </c>
+      <c r="I132" t="n">
+        <v>0.35425</v>
+      </c>
+      <c r="J132" t="n">
+        <v>0.35036</v>
+      </c>
+      <c r="K132" t="n">
+        <v>0.34862</v>
+      </c>
+      <c r="L132" t="n">
+        <v>0.35121</v>
+      </c>
+      <c r="M132" t="n">
+        <v>0.34507</v>
+      </c>
+      <c r="N132" t="n">
+        <v>0.35222</v>
+      </c>
+      <c r="O132" t="n">
+        <v>0.34788</v>
+      </c>
+      <c r="P132" t="n">
+        <v>0.34836</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>0.34431</v>
+      </c>
+      <c r="R132" t="n">
+        <v>0.34685</v>
+      </c>
+      <c r="S132" t="n">
+        <v>0.35171</v>
+      </c>
+      <c r="T132" t="n">
+        <v>0.35204</v>
+      </c>
+      <c r="U132" t="n">
+        <v>0.33998</v>
+      </c>
+      <c r="V132" t="n">
+        <v>0.34829</v>
+      </c>
+      <c r="W132" t="n">
+        <v>0.35101</v>
+      </c>
+      <c r="X132" t="n">
+        <v>0.34875</v>
+      </c>
+      <c r="Y132" t="n">
+        <v>0.35231</v>
+      </c>
+      <c r="Z132" t="n">
+        <v>0.35231</v>
+      </c>
+      <c r="AA132" t="n">
+        <v>0.36085</v>
+      </c>
+      <c r="AB132" t="n">
+        <v>0.35811</v>
+      </c>
+      <c r="AC132" t="n">
+        <v>0.37212</v>
+      </c>
+      <c r="AD132" t="n">
+        <v>0.3488</v>
+      </c>
+      <c r="AE132" t="n">
+        <v>0.34871</v>
+      </c>
+      <c r="AF132" t="n">
+        <v>0.34342</v>
+      </c>
+      <c r="AG132" t="n">
+        <v>0.34411</v>
+      </c>
+      <c r="AH132" t="n">
+        <v>0.35016</v>
+      </c>
+      <c r="AI132" t="n">
+        <v>0.34118</v>
+      </c>
+      <c r="AJ132" t="n">
+        <v>0.32401</v>
+      </c>
+      <c r="AK132" t="n">
+        <v>0.22915</v>
+      </c>
+      <c r="AL132" t="n">
+        <v>0.31404</v>
+      </c>
+      <c r="AM132" t="n">
+        <v>0.26866</v>
+      </c>
+      <c r="AN132" t="n">
+        <v>0.2479</v>
+      </c>
+      <c r="AO132" t="n">
+        <v>0.11593</v>
+      </c>
+      <c r="AP132" t="n">
+        <v>0.28706</v>
+      </c>
+      <c r="AQ132" t="n">
+        <v>0.26678</v>
+      </c>
+      <c r="AR132" t="n">
+        <v>0.3011</v>
+      </c>
+      <c r="AS132" t="n">
+        <v>0.22138</v>
+      </c>
+      <c r="AT132" t="n">
+        <v>0.21326</v>
+      </c>
+      <c r="AU132" t="n">
+        <v>0.32482</v>
+      </c>
+      <c r="AV132" t="n">
+        <v>0.32524</v>
+      </c>
+      <c r="AW132" t="n">
+        <v>0.29067</v>
+      </c>
+      <c r="AX132" t="n">
+        <v>0.23722</v>
+      </c>
+      <c r="AY132" t="n">
+        <v>0.26688</v>
+      </c>
+      <c r="AZ132" t="n">
+        <v>0.29527</v>
+      </c>
+      <c r="BA132" t="n">
+        <v>0.28843</v>
+      </c>
+      <c r="BB132" t="n">
+        <v>0.30576</v>
+      </c>
+      <c r="BC132" t="n">
+        <v>0.2935</v>
+      </c>
+      <c r="BD132" t="n">
+        <v>0.30343</v>
+      </c>
+      <c r="BE132" t="n">
+        <v>0.27915</v>
+      </c>
+      <c r="BF132" t="n">
+        <v>0.3692</v>
+      </c>
+      <c r="BG132" t="n">
+        <v>0.31887</v>
+      </c>
+      <c r="BH132" t="n">
+        <v>0.3071</v>
+      </c>
+      <c r="BI132" t="n">
+        <v>0.29617</v>
+      </c>
+      <c r="BJ132" t="n">
+        <v>0.34052</v>
+      </c>
+      <c r="BK132" t="n">
+        <v>0.27986</v>
+      </c>
+      <c r="BL132" t="n">
+        <v>0.31155</v>
+      </c>
+      <c r="BM132" t="n">
+        <v>0.27351</v>
+      </c>
+      <c r="BN132" t="n">
+        <v>0.29163</v>
+      </c>
+      <c r="BO132" t="n">
+        <v>0.267</v>
+      </c>
+      <c r="BP132" t="n">
+        <v>0.30663</v>
+      </c>
+      <c r="BQ132" t="n">
+        <v>0.28358</v>
+      </c>
+      <c r="BR132" t="n">
+        <v>0.33234</v>
+      </c>
+      <c r="BS132" t="n">
+        <v>0.30989</v>
+      </c>
+      <c r="BT132" t="n">
+        <v>0.31217</v>
+      </c>
+      <c r="BU132" t="n">
+        <v>0.29301</v>
+      </c>
+      <c r="BV132" t="n">
+        <v>0.31547</v>
+      </c>
+      <c r="BW132" t="n">
+        <v>0.24435</v>
+      </c>
+      <c r="BX132" t="n">
+        <v>0.31698</v>
+      </c>
+      <c r="BY132" t="n">
+        <v>0.20637</v>
+      </c>
+      <c r="BZ132" t="n">
+        <v>0.34162</v>
+      </c>
+      <c r="CA132" t="n">
+        <v>0.6120599999999999</v>
+      </c>
+      <c r="CB132" t="n">
+        <v>0.57013</v>
+      </c>
+      <c r="CC132" t="n">
+        <v>0.5476</v>
+      </c>
+      <c r="CD132" t="n">
+        <v>0.40451</v>
+      </c>
+      <c r="CE132" t="n">
+        <v>0.7827999999999999</v>
+      </c>
+      <c r="CF132" t="n">
+        <v>0.40471</v>
+      </c>
+      <c r="CG132" t="n">
+        <v>0.5997899999999999</v>
+      </c>
+      <c r="CH132" t="n">
+        <v>0.25736</v>
+      </c>
+      <c r="CI132" t="n">
+        <v>0.45757</v>
+      </c>
+      <c r="CJ132" t="n">
+        <v>0.36893</v>
+      </c>
+      <c r="CK132" t="n">
+        <v>0.28639</v>
+      </c>
+      <c r="CL132" t="n">
+        <v>0.25165</v>
+      </c>
+      <c r="CM132" t="n">
+        <v>0.4043</v>
+      </c>
+      <c r="CN132" t="n">
+        <v>0.40042</v>
+      </c>
+      <c r="CO132" t="n">
+        <v>0.39197</v>
+      </c>
+      <c r="CP132" t="n">
+        <v>0.36308</v>
+      </c>
+      <c r="CQ132" t="n">
+        <v>0.36689</v>
+      </c>
+      <c r="CR132" t="n">
+        <v>0.35383</v>
+      </c>
+      <c r="CS132" t="n">
+        <v>0.34793</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B133" t="n">
+        <v>0.34583</v>
+      </c>
+      <c r="C133" t="n">
+        <v>0.44844</v>
+      </c>
+      <c r="D133" t="n">
+        <v>0.5182100000000001</v>
+      </c>
+      <c r="E133" t="n">
+        <v>0.46707</v>
+      </c>
+      <c r="F133" t="n">
+        <v>0.60314</v>
+      </c>
+      <c r="G133" t="n">
+        <v>0.39196</v>
+      </c>
+      <c r="H133" t="n">
+        <v>0.39203</v>
+      </c>
+      <c r="I133" t="n">
+        <v>0.38145</v>
+      </c>
+      <c r="J133" t="n">
+        <v>0.38589</v>
+      </c>
+      <c r="K133" t="n">
+        <v>0.38566</v>
+      </c>
+      <c r="L133" t="n">
+        <v>0.39138</v>
+      </c>
+      <c r="M133" t="n">
+        <v>0.37871</v>
+      </c>
+      <c r="N133" t="n">
+        <v>0.38692</v>
+      </c>
+      <c r="O133" t="n">
+        <v>0.39063</v>
+      </c>
+      <c r="P133" t="n">
+        <v>0.38888</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>0.37699</v>
+      </c>
+      <c r="R133" t="n">
+        <v>0.38018</v>
+      </c>
+      <c r="S133" t="n">
+        <v>0.39101</v>
+      </c>
+      <c r="T133" t="n">
+        <v>0.36779</v>
+      </c>
+      <c r="U133" t="n">
+        <v>0.38947</v>
+      </c>
+      <c r="V133" t="n">
+        <v>0.36957</v>
+      </c>
+      <c r="W133" t="n">
+        <v>0.37114</v>
+      </c>
+      <c r="X133" t="n">
+        <v>0.37525</v>
+      </c>
+      <c r="Y133" t="n">
+        <v>0.38642</v>
+      </c>
+      <c r="Z133" t="n">
+        <v>0.37285</v>
+      </c>
+      <c r="AA133" t="n">
+        <v>0.40719</v>
+      </c>
+      <c r="AB133" t="n">
+        <v>0.41006</v>
+      </c>
+      <c r="AC133" t="n">
+        <v>0.49236</v>
+      </c>
+      <c r="AD133" t="n">
+        <v>0.45133</v>
+      </c>
+      <c r="AE133" t="n">
+        <v>0.4149</v>
+      </c>
+      <c r="AF133" t="n">
+        <v>0.44983</v>
+      </c>
+      <c r="AG133" t="n">
+        <v>0.41359</v>
+      </c>
+      <c r="AH133" t="n">
+        <v>0.4883</v>
+      </c>
+      <c r="AI133" t="n">
+        <v>0.45068</v>
+      </c>
+      <c r="AJ133" t="n">
+        <v>0.36673</v>
+      </c>
+      <c r="AK133" t="n">
+        <v>0.49781</v>
+      </c>
+      <c r="AL133" t="n">
+        <v>0.53431</v>
+      </c>
+      <c r="AM133" t="n">
+        <v>0.5220399999999999</v>
+      </c>
+      <c r="AN133" t="n">
+        <v>0.61398</v>
+      </c>
+      <c r="AO133" t="n">
+        <v>0.42659</v>
+      </c>
+      <c r="AP133" t="n">
+        <v>0.36197</v>
+      </c>
+      <c r="AQ133" t="n">
+        <v>0.34677</v>
+      </c>
+      <c r="AR133" t="n">
+        <v>0.35391</v>
+      </c>
+      <c r="AS133" t="n">
+        <v>0.38541</v>
+      </c>
+      <c r="AT133" t="n">
+        <v>0.38816</v>
+      </c>
+      <c r="AU133" t="n">
+        <v>0.41279</v>
+      </c>
+      <c r="AV133" t="n">
+        <v>0.36961</v>
+      </c>
+      <c r="AW133" t="n">
+        <v>0.36145</v>
+      </c>
+      <c r="AX133" t="n">
+        <v>0.30381</v>
+      </c>
+      <c r="AY133" t="n">
+        <v>0.33537</v>
+      </c>
+      <c r="AZ133" t="n">
+        <v>0.32654</v>
+      </c>
+      <c r="BA133" t="n">
+        <v>0.40598</v>
+      </c>
+      <c r="BB133" t="n">
+        <v>0.65491</v>
+      </c>
+      <c r="BC133" t="n">
+        <v>0.48575</v>
+      </c>
+      <c r="BD133" t="n">
+        <v>0.9222899999999999</v>
+      </c>
+      <c r="BE133" t="n">
+        <v>0.37964</v>
+      </c>
+      <c r="BF133" t="n">
+        <v>0.38908</v>
+      </c>
+      <c r="BG133" t="n">
+        <v>0.38777</v>
+      </c>
+      <c r="BH133" t="n">
+        <v>0.37094</v>
+      </c>
+      <c r="BI133" t="n">
+        <v>0.35654</v>
+      </c>
+      <c r="BJ133" t="n">
+        <v>0.33894</v>
+      </c>
+      <c r="BK133" t="n">
+        <v>0.31538</v>
+      </c>
+      <c r="BL133" t="n">
+        <v>0.33355</v>
+      </c>
+      <c r="BM133" t="n">
+        <v>0.34825</v>
+      </c>
+      <c r="BN133" t="n">
+        <v>0.33648</v>
+      </c>
+      <c r="BO133" t="n">
+        <v>0.35615</v>
+      </c>
+      <c r="BP133" t="n">
+        <v>0.35086</v>
+      </c>
+      <c r="BQ133" t="n">
+        <v>0.35207</v>
+      </c>
+      <c r="BR133" t="n">
+        <v>0.35713</v>
+      </c>
+      <c r="BS133" t="n">
+        <v>0.36726</v>
+      </c>
+      <c r="BT133" t="n">
+        <v>0.34216</v>
+      </c>
+      <c r="BU133" t="n">
+        <v>0.36096</v>
+      </c>
+      <c r="BV133" t="n">
+        <v>0.33064</v>
+      </c>
+      <c r="BW133" t="n">
+        <v>0.38845</v>
+      </c>
+      <c r="BX133" t="n">
+        <v>0.40776</v>
+      </c>
+      <c r="BY133" t="n">
+        <v>0.45037</v>
+      </c>
+      <c r="BZ133" t="n">
+        <v>0.41399</v>
+      </c>
+      <c r="CA133" t="n">
+        <v>0.46185</v>
+      </c>
+      <c r="CB133" t="n">
+        <v>0.46224</v>
+      </c>
+      <c r="CC133" t="n">
+        <v>0.49298</v>
+      </c>
+      <c r="CD133" t="n">
+        <v>0.6030399999999999</v>
+      </c>
+      <c r="CE133" t="n">
+        <v>0.70421</v>
+      </c>
+      <c r="CF133" t="n">
+        <v>0.7858200000000001</v>
+      </c>
+      <c r="CG133" t="n">
+        <v>0.55601</v>
+      </c>
+      <c r="CH133" t="n">
+        <v>0.6900499999999999</v>
+      </c>
+      <c r="CI133" t="n">
+        <v>0.60162</v>
+      </c>
+      <c r="CJ133" t="n">
+        <v>0.48358</v>
+      </c>
+      <c r="CK133" t="n">
+        <v>0.70923</v>
+      </c>
+      <c r="CL133" t="n">
+        <v>0.76334</v>
+      </c>
+      <c r="CM133" t="n">
+        <v>0.61619</v>
+      </c>
+      <c r="CN133" t="n">
+        <v>0.6648500000000001</v>
+      </c>
+      <c r="CO133" t="n">
+        <v>0.42717</v>
+      </c>
+      <c r="CP133" t="n">
+        <v>0.4407</v>
+      </c>
+      <c r="CQ133" t="n">
+        <v>0.44029</v>
+      </c>
+      <c r="CR133" t="n">
+        <v>0.43707</v>
+      </c>
+      <c r="CS133" t="n">
+        <v>0.43034</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="n">
+        <v>46157</v>
+      </c>
+      <c r="B134" t="n">
+        <v>0.39284</v>
+      </c>
+      <c r="C134" t="n">
+        <v>0.49494</v>
+      </c>
+      <c r="D134" t="n">
+        <v>0.40061</v>
+      </c>
+      <c r="E134" t="n">
+        <v>0.41078</v>
+      </c>
+      <c r="F134" t="n">
+        <v>0.42051</v>
+      </c>
+      <c r="G134" t="n">
+        <v>0.42671</v>
+      </c>
+      <c r="H134" t="n">
+        <v>0.41662</v>
+      </c>
+      <c r="I134" t="n">
+        <v>0.41227</v>
+      </c>
+      <c r="J134" t="n">
+        <v>0.40836</v>
+      </c>
+      <c r="K134" t="n">
+        <v>0.37689</v>
+      </c>
+      <c r="L134" t="n">
+        <v>0.4064700000000001</v>
+      </c>
+      <c r="M134" t="n">
+        <v>0.36903</v>
+      </c>
+      <c r="N134" t="n">
+        <v>0.37537</v>
+      </c>
+      <c r="O134" t="n">
+        <v>0.37079</v>
+      </c>
+      <c r="P134" t="n">
+        <v>0.36597</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>0.36142</v>
+      </c>
+      <c r="R134" t="n">
+        <v>0.35545</v>
+      </c>
+      <c r="S134" t="n">
+        <v>0.35238</v>
+      </c>
+      <c r="T134" t="n">
+        <v>0.34918</v>
+      </c>
+      <c r="U134" t="n">
+        <v>0.35816</v>
+      </c>
+      <c r="V134" t="n">
+        <v>0.27882</v>
+      </c>
+      <c r="W134" t="n">
+        <v>0.34656</v>
+      </c>
+      <c r="X134" t="n">
+        <v>0.3404700000000001</v>
+      </c>
+      <c r="Y134" t="n">
+        <v>0.35206</v>
+      </c>
+      <c r="Z134" t="n">
+        <v>0.35816</v>
+      </c>
+      <c r="AA134" t="n">
+        <v>0.35785</v>
+      </c>
+      <c r="AB134" t="n">
+        <v>0.36256</v>
+      </c>
+      <c r="AC134" t="n">
+        <v>0.37173</v>
+      </c>
+      <c r="AD134" t="n">
+        <v>0.34701</v>
+      </c>
+      <c r="AE134" t="n">
+        <v>0.35359</v>
+      </c>
+      <c r="AF134" t="n">
+        <v>0.34736</v>
+      </c>
+      <c r="AG134" t="n">
+        <v>0.37167</v>
+      </c>
+      <c r="AH134" t="n">
+        <v>0.39558</v>
+      </c>
+      <c r="AI134" t="n">
+        <v>0.35588</v>
+      </c>
+      <c r="AJ134" t="n">
+        <v>0.38012</v>
+      </c>
+      <c r="AK134" t="n">
+        <v>0.39136</v>
+      </c>
+      <c r="AL134" t="n">
+        <v>0.3762200000000001</v>
+      </c>
+      <c r="AM134" t="n">
+        <v>0.37875</v>
+      </c>
+      <c r="AN134" t="n">
+        <v>0.35131</v>
+      </c>
+      <c r="AO134" t="n">
+        <v>0.35799</v>
+      </c>
+      <c r="AP134" t="n">
+        <v>1.33851</v>
+      </c>
+      <c r="AQ134" t="n">
+        <v>0.33282</v>
+      </c>
+      <c r="AR134" t="n">
+        <v>0.33996</v>
+      </c>
+      <c r="AS134" t="n">
+        <v>0.36723</v>
+      </c>
+      <c r="AT134" t="n">
+        <v>0.28943</v>
+      </c>
+      <c r="AU134" t="n">
+        <v>0.38592</v>
+      </c>
+      <c r="AV134" t="n">
+        <v>0.36805</v>
+      </c>
+      <c r="AW134" t="n">
+        <v>0.34543</v>
+      </c>
+      <c r="AX134" t="n">
+        <v>0.26219</v>
+      </c>
+      <c r="AY134" t="n">
+        <v>0.3728</v>
+      </c>
+      <c r="AZ134" t="n">
+        <v>0.36173</v>
+      </c>
+      <c r="BA134" t="n">
+        <v>0.41656</v>
+      </c>
+      <c r="BB134" t="n">
+        <v>0.3736</v>
+      </c>
+      <c r="BC134" t="n">
+        <v>0.44538</v>
+      </c>
+      <c r="BD134" t="n">
+        <v>0.41017</v>
+      </c>
+      <c r="BE134" t="n">
+        <v>0.45871</v>
+      </c>
+      <c r="BF134" t="n">
+        <v>0.36147</v>
+      </c>
+      <c r="BG134" t="n">
+        <v>0.32426</v>
+      </c>
+      <c r="BH134" t="n">
+        <v>0.16285</v>
+      </c>
+      <c r="BI134" t="n">
+        <v>0.2239</v>
+      </c>
+      <c r="BJ134" t="n">
+        <v>0.29508</v>
+      </c>
+      <c r="BK134" t="n">
+        <v>0.29923</v>
+      </c>
+      <c r="BL134" t="n">
+        <v>0.32181</v>
+      </c>
+      <c r="BM134" t="n">
+        <v>0.34227</v>
+      </c>
+      <c r="BN134" t="n">
+        <v>0.33439</v>
+      </c>
+      <c r="BO134" t="n">
+        <v>0.33692</v>
+      </c>
+      <c r="BP134" t="n">
+        <v>0.33759</v>
+      </c>
+      <c r="BQ134" t="n">
+        <v>0.35507</v>
+      </c>
+      <c r="BR134" t="n">
+        <v>1.3764</v>
+      </c>
+      <c r="BS134" t="n">
+        <v>1.37585</v>
+      </c>
+      <c r="BT134" t="n">
+        <v>1.38074</v>
+      </c>
+      <c r="BU134" t="n">
+        <v>1.39221</v>
+      </c>
+      <c r="BV134" t="n">
+        <v>0.33161</v>
+      </c>
+      <c r="BW134" t="n">
+        <v>0.42424</v>
+      </c>
+      <c r="BX134" t="n">
+        <v>0.40966</v>
+      </c>
+      <c r="BY134" t="n">
+        <v>0.41945</v>
+      </c>
+      <c r="BZ134" t="n">
+        <v>0.40035</v>
+      </c>
+      <c r="CA134" t="n">
+        <v>0.39116</v>
+      </c>
+      <c r="CB134" t="n">
+        <v>0.34382</v>
+      </c>
+      <c r="CC134" t="n">
+        <v>0.34678</v>
+      </c>
+      <c r="CD134" t="n">
+        <v>0.36566</v>
+      </c>
+      <c r="CE134" t="n">
+        <v>0.3748</v>
+      </c>
+      <c r="CF134" t="n">
+        <v>0.32369</v>
+      </c>
+      <c r="CG134" t="n">
+        <v>0.33441</v>
+      </c>
+      <c r="CH134" t="n">
+        <v>0.36818</v>
+      </c>
+      <c r="CI134" t="n">
+        <v>0.36524</v>
+      </c>
+      <c r="CJ134" t="n">
+        <v>0.35237</v>
+      </c>
+      <c r="CK134" t="n">
+        <v>0.35743</v>
+      </c>
+      <c r="CL134" t="n">
+        <v>0.35394</v>
+      </c>
+      <c r="CM134" t="n">
+        <v>0.37085</v>
+      </c>
+      <c r="CN134" t="n">
+        <v>0.32966</v>
+      </c>
+      <c r="CO134" t="n">
+        <v>0.35434</v>
+      </c>
+      <c r="CP134" t="n">
+        <v>0.31019</v>
+      </c>
+      <c r="CQ134" t="n">
+        <v>0.34298</v>
+      </c>
+      <c r="CR134" t="n">
+        <v>0.32986</v>
+      </c>
+      <c r="CS134" t="n">
+        <v>0.32587</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="n">
+        <v>46158</v>
+      </c>
+      <c r="B135" t="n">
+        <v>0.29287</v>
+      </c>
+      <c r="C135" t="n">
+        <v>0.45067</v>
+      </c>
+      <c r="D135" t="n">
+        <v>0.3564</v>
+      </c>
+      <c r="E135" t="n">
+        <v>0.36926</v>
+      </c>
+      <c r="F135" t="n">
+        <v>0.35153</v>
+      </c>
+      <c r="G135" t="n">
+        <v>0.34866</v>
+      </c>
+      <c r="H135" t="n">
+        <v>0.33803</v>
+      </c>
+      <c r="I135" t="n">
+        <v>0.30304</v>
+      </c>
+      <c r="J135" t="n">
+        <v>0.28017</v>
+      </c>
+      <c r="K135" t="n">
+        <v>0.33193</v>
+      </c>
+      <c r="L135" t="n">
+        <v>0.26468</v>
+      </c>
+      <c r="M135" t="n">
+        <v>0.26227</v>
+      </c>
+      <c r="N135" t="n">
+        <v>0.30299</v>
+      </c>
+      <c r="O135" t="n">
+        <v>0.26219</v>
+      </c>
+      <c r="P135" t="n">
+        <v>0.30849</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>0.34365</v>
+      </c>
+      <c r="R135" t="n">
+        <v>0.30207</v>
+      </c>
+      <c r="S135" t="n">
+        <v>0.25064</v>
+      </c>
+      <c r="T135" t="n">
+        <v>0.2862</v>
+      </c>
+      <c r="U135" t="n">
+        <v>0.29379</v>
+      </c>
+      <c r="V135" t="n">
+        <v>0.30302</v>
+      </c>
+      <c r="W135" t="n">
+        <v>0.28973</v>
+      </c>
+      <c r="X135" t="n">
+        <v>0.29414</v>
+      </c>
+      <c r="Y135" t="n">
+        <v>0.29855</v>
+      </c>
+      <c r="Z135" t="n">
+        <v>0.24343</v>
+      </c>
+      <c r="AA135" t="n">
+        <v>0.30296</v>
+      </c>
+      <c r="AB135" t="n">
+        <v>0.24253</v>
+      </c>
+      <c r="AC135" t="n">
+        <v>0.23609</v>
+      </c>
+      <c r="AD135" t="n">
+        <v>0.32064</v>
+      </c>
+      <c r="AE135" t="n">
+        <v>0.28278</v>
+      </c>
+      <c r="AF135" t="n">
+        <v>0.27503</v>
+      </c>
+      <c r="AG135" t="n">
+        <v>0.30725</v>
+      </c>
+      <c r="AH135" t="n">
+        <v>0.23186</v>
+      </c>
+      <c r="AI135" t="n">
+        <v>0.34228</v>
+      </c>
+      <c r="AJ135" t="n">
+        <v>0.30663</v>
+      </c>
+      <c r="AK135" t="n">
+        <v>0.30591</v>
+      </c>
+      <c r="AL135" t="n">
+        <v>0.3013</v>
+      </c>
+      <c r="AM135" t="n">
+        <v>0.17576</v>
+      </c>
+      <c r="AN135" t="n">
+        <v>0.28181</v>
+      </c>
+      <c r="AO135" t="n">
+        <v>0.24882</v>
+      </c>
+      <c r="AP135" t="n">
+        <v>0.27069</v>
+      </c>
+      <c r="AQ135" t="n">
+        <v>0.26481</v>
+      </c>
+      <c r="AR135" t="n">
+        <v>0.26071</v>
+      </c>
+      <c r="AS135" t="n">
+        <v>0.08186</v>
+      </c>
+      <c r="AT135" t="n">
+        <v>0.31585</v>
+      </c>
+      <c r="AU135" t="n">
+        <v>0.30823</v>
+      </c>
+      <c r="AV135" t="n">
+        <v>0.26923</v>
+      </c>
+      <c r="AW135" t="n">
+        <v>0.25862</v>
+      </c>
+      <c r="AX135" t="n">
+        <v>0.03229</v>
+      </c>
+      <c r="AY135" t="n">
+        <v>0.28996</v>
+      </c>
+      <c r="AZ135" t="n">
+        <v>0.28271</v>
+      </c>
+      <c r="BA135" t="n">
+        <v>0.20028</v>
+      </c>
+      <c r="BB135" t="n">
+        <v>0.22263</v>
+      </c>
+      <c r="BC135" t="n">
+        <v>0.31164</v>
+      </c>
+      <c r="BD135" t="n">
+        <v>0.31292</v>
+      </c>
+      <c r="BE135" t="n">
+        <v>0.30789</v>
+      </c>
+      <c r="BF135" t="n">
+        <v>0.25334</v>
+      </c>
+      <c r="BG135" t="n">
+        <v>0.27135</v>
+      </c>
+      <c r="BH135" t="n">
+        <v>0.2578</v>
+      </c>
+      <c r="BI135" t="n">
+        <v>0.24178</v>
+      </c>
+      <c r="BJ135" t="n">
+        <v>0.27628</v>
+      </c>
+      <c r="BK135" t="n">
+        <v>0.28477</v>
+      </c>
+      <c r="BL135" t="n">
+        <v>0.27343</v>
+      </c>
+      <c r="BM135" t="n">
+        <v>0.32103</v>
+      </c>
+      <c r="BN135" t="n">
+        <v>0.32275</v>
+      </c>
+      <c r="BO135" t="n">
+        <v>0.31534</v>
+      </c>
+      <c r="BP135" t="n">
+        <v>0.33763</v>
+      </c>
+      <c r="BQ135" t="n">
+        <v>0.33527</v>
+      </c>
+      <c r="BR135" t="n">
+        <v>0.34493</v>
+      </c>
+      <c r="BS135" t="n">
+        <v>0.36144</v>
+      </c>
+      <c r="BT135" t="n">
+        <v>0.34029</v>
+      </c>
+      <c r="BU135" t="n">
+        <v>0.33329</v>
+      </c>
+      <c r="BV135" t="n">
+        <v>0.31261</v>
+      </c>
+      <c r="BW135" t="n">
+        <v>0.3613</v>
+      </c>
+      <c r="BX135" t="n">
+        <v>0.37624</v>
+      </c>
+      <c r="BY135" t="n">
+        <v>0.34438</v>
+      </c>
+      <c r="BZ135" t="n">
+        <v>0.30205</v>
+      </c>
+      <c r="CA135" t="n">
+        <v>0.34947</v>
+      </c>
+      <c r="CB135" t="n">
+        <v>0.3369</v>
+      </c>
+      <c r="CC135" t="n">
+        <v>0.35042</v>
+      </c>
+      <c r="CD135" t="n">
+        <v>0.3299</v>
+      </c>
+      <c r="CE135" t="n">
+        <v>0.33471</v>
+      </c>
+      <c r="CF135" t="n">
+        <v>0.35456</v>
+      </c>
+      <c r="CG135" t="n">
+        <v>0.32964</v>
+      </c>
+      <c r="CH135" t="n">
+        <v>0.32288</v>
+      </c>
+      <c r="CI135" t="n">
+        <v>0.34103</v>
+      </c>
+      <c r="CJ135" t="n">
+        <v>0.35831</v>
+      </c>
+      <c r="CK135" t="n">
+        <v>0.31885</v>
+      </c>
+      <c r="CL135" t="n">
+        <v>0.33447</v>
+      </c>
+      <c r="CM135" t="n">
+        <v>0.31899</v>
+      </c>
+      <c r="CN135" t="n">
+        <v>0.32983</v>
+      </c>
+      <c r="CO135" t="n">
+        <v>0.3241</v>
+      </c>
+      <c r="CP135" t="n">
+        <v>0.3009</v>
+      </c>
+      <c r="CQ135" t="n">
+        <v>0.32949</v>
+      </c>
+      <c r="CR135" t="n">
+        <v>0.30089</v>
+      </c>
+      <c r="CS135" t="n">
+        <v>0.31914</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="n">
+        <v>46159</v>
+      </c>
+      <c r="B136" t="n">
+        <v>0.29765</v>
+      </c>
+      <c r="C136" t="n">
+        <v>0.32411</v>
+      </c>
+      <c r="D136" t="n">
+        <v>0.32554</v>
+      </c>
+      <c r="E136" t="n">
+        <v>0.32499</v>
+      </c>
+      <c r="F136" t="n">
+        <v>0.32792</v>
+      </c>
+      <c r="G136" t="n">
+        <v>0.32162</v>
+      </c>
+      <c r="H136" t="n">
+        <v>0.25896</v>
+      </c>
+      <c r="I136" t="n">
+        <v>0.2878</v>
+      </c>
+      <c r="J136" t="n">
+        <v>0.28344</v>
+      </c>
+      <c r="K136" t="n">
+        <v>0.30449</v>
+      </c>
+      <c r="L136" t="n">
+        <v>0.2266</v>
+      </c>
+      <c r="M136" t="n">
+        <v>0.28211</v>
+      </c>
+      <c r="N136" t="n">
+        <v>0.29037</v>
+      </c>
+      <c r="O136" t="n">
+        <v>0.28617</v>
+      </c>
+      <c r="P136" t="n">
+        <v>0.2383</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>0.22525</v>
+      </c>
+      <c r="R136" t="n">
+        <v>0.22866</v>
+      </c>
+      <c r="S136" t="n">
+        <v>0.22865</v>
+      </c>
+      <c r="T136" t="n">
+        <v>0.22556</v>
+      </c>
+      <c r="U136" t="n">
+        <v>0.22556</v>
+      </c>
+      <c r="V136" t="n">
+        <v>0.22742</v>
+      </c>
+      <c r="W136" t="n">
+        <v>0.2775899999999999</v>
+      </c>
+      <c r="X136" t="n">
+        <v>0.22158</v>
+      </c>
+      <c r="Y136" t="n">
+        <v>0.22556</v>
+      </c>
+      <c r="Z136" t="n">
+        <v>0.22586</v>
+      </c>
+      <c r="AA136" t="n">
+        <v>0.27605</v>
+      </c>
+      <c r="AB136" t="n">
+        <v>0.22539</v>
+      </c>
+      <c r="AC136" t="n">
+        <v>0.22519</v>
+      </c>
+      <c r="AD136" t="n">
+        <v>0.32389</v>
+      </c>
+      <c r="AE136" t="n">
+        <v>0.23112</v>
+      </c>
+      <c r="AF136" t="n">
+        <v>0.1538</v>
+      </c>
+      <c r="AG136" t="n">
+        <v>0.26415</v>
+      </c>
+      <c r="AH136" t="n">
+        <v>0.20094</v>
+      </c>
+      <c r="AI136" t="n">
+        <v>0.01158</v>
+      </c>
+      <c r="AJ136" t="n">
+        <v>0.00044</v>
+      </c>
+      <c r="AK136" t="n">
+        <v>-0.00082</v>
+      </c>
+      <c r="AL136" t="n">
+        <v>-0.04956</v>
+      </c>
+      <c r="AM136" t="n">
+        <v>0.14596</v>
+      </c>
+      <c r="AN136" t="n">
+        <v>0.0205</v>
+      </c>
+      <c r="AO136" t="n">
+        <v>-0.03956</v>
+      </c>
+      <c r="AP136" t="n">
+        <v>-0.04958</v>
+      </c>
+      <c r="AQ136" t="n">
+        <v>-0.01523</v>
+      </c>
+      <c r="AR136" t="n">
+        <v>-0.04274</v>
+      </c>
+      <c r="AS136" t="n">
+        <v>-0.0406</v>
+      </c>
+      <c r="AT136" t="n">
+        <v>-0.04856</v>
+      </c>
+      <c r="AU136" t="n">
+        <v>-0.04821</v>
+      </c>
+      <c r="AV136" t="n">
+        <v>-0.02446</v>
+      </c>
+      <c r="AW136" t="n">
+        <v>-0.02911</v>
+      </c>
+      <c r="AX136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY136" t="n">
+        <v>-0.0496</v>
+      </c>
+      <c r="AZ136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BA136" t="n">
+        <v>-0.04958</v>
+      </c>
+      <c r="BB136" t="n">
+        <v>-0.04959</v>
+      </c>
+      <c r="BC136" t="n">
+        <v>-0.04939</v>
+      </c>
+      <c r="BD136" t="n">
+        <v>0.0003</v>
+      </c>
+      <c r="BE136" t="n">
+        <v>0.27287</v>
+      </c>
+      <c r="BF136" t="n">
+        <v>-0.04964</v>
+      </c>
+      <c r="BG136" t="n">
+        <v>-0.0493</v>
+      </c>
+      <c r="BH136" t="n">
+        <v>-0.04959</v>
+      </c>
+      <c r="BI136" t="n">
+        <v>-0.03879</v>
+      </c>
+      <c r="BJ136" t="n">
+        <v>-0.01861</v>
+      </c>
+      <c r="BK136" t="n">
+        <v>-0.04957</v>
+      </c>
+      <c r="BL136" t="n">
+        <v>-0.04962</v>
+      </c>
+      <c r="BM136" t="n">
+        <v>-0.03623</v>
+      </c>
+      <c r="BN136" t="n">
+        <v>0.20093</v>
+      </c>
+      <c r="BO136" t="n">
+        <v>0.26371</v>
+      </c>
+      <c r="BP136" t="n">
+        <v>0.28763</v>
+      </c>
+      <c r="BQ136" t="n">
+        <v>0.27943</v>
+      </c>
+      <c r="BR136" t="n">
+        <v>0.30237</v>
+      </c>
+      <c r="BS136" t="n">
+        <v>0.30657</v>
+      </c>
+      <c r="BT136" t="n">
+        <v>0.22892</v>
+      </c>
+      <c r="BU136" t="n">
+        <v>0.30898</v>
+      </c>
+      <c r="BV136" t="n">
+        <v>0.32598</v>
+      </c>
+      <c r="BW136" t="n">
+        <v>0.34192</v>
+      </c>
+      <c r="BX136" t="n">
+        <v>0.33469</v>
+      </c>
+      <c r="BY136" t="n">
+        <v>0.33753</v>
+      </c>
+      <c r="BZ136" t="n">
+        <v>0.30709</v>
+      </c>
+      <c r="CA136" t="n">
+        <v>0.31359</v>
+      </c>
+      <c r="CB136" t="n">
+        <v>0.34642</v>
+      </c>
+      <c r="CC136" t="n">
+        <v>0.33487</v>
+      </c>
+      <c r="CD136" t="n">
+        <v>0.33898</v>
+      </c>
+      <c r="CE136" t="n">
+        <v>0.33759</v>
+      </c>
+      <c r="CF136" t="n">
+        <v>0.33625</v>
+      </c>
+      <c r="CG136" t="n">
+        <v>0.34125</v>
+      </c>
+      <c r="CH136" t="n">
+        <v>0.33527</v>
+      </c>
+      <c r="CI136" t="n">
+        <v>0.36078</v>
+      </c>
+      <c r="CJ136" t="n">
+        <v>0.41104</v>
+      </c>
+      <c r="CK136" t="n">
+        <v>0.34982</v>
+      </c>
+      <c r="CL136" t="n">
+        <v>0.36285</v>
+      </c>
+      <c r="CM136" t="n">
+        <v>0.3452</v>
+      </c>
+      <c r="CN136" t="n">
+        <v>0.33989</v>
+      </c>
+      <c r="CO136" t="n">
+        <v>0.33997</v>
+      </c>
+      <c r="CP136" t="n">
+        <v>0.33134</v>
+      </c>
+      <c r="CQ136" t="n">
+        <v>0.34089</v>
+      </c>
+      <c r="CR136" t="n">
+        <v>0.30333</v>
+      </c>
+      <c r="CS136" t="n">
+        <v>0.32329</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="n">
+        <v>46160</v>
+      </c>
+      <c r="B137" t="n">
+        <v>0.29801</v>
+      </c>
+      <c r="C137" t="n">
+        <v>0.6981799999999999</v>
+      </c>
+      <c r="D137" t="n">
+        <v>0.59178</v>
+      </c>
+      <c r="E137" t="n">
+        <v>0.376</v>
+      </c>
+      <c r="F137" t="n">
+        <v>0.3982</v>
+      </c>
+      <c r="G137" t="n">
+        <v>0.3828</v>
+      </c>
+      <c r="H137" t="n">
+        <v>0.40473</v>
+      </c>
+      <c r="I137" t="n">
+        <v>0.40662</v>
+      </c>
+      <c r="J137" t="n">
+        <v>0.35402</v>
+      </c>
+      <c r="K137" t="n">
+        <v>0.32066</v>
+      </c>
+      <c r="L137" t="n">
+        <v>0.3349</v>
+      </c>
+      <c r="M137" t="n">
+        <v>0.2983</v>
+      </c>
+      <c r="N137" t="n">
+        <v>0.30857</v>
+      </c>
+      <c r="O137" t="n">
+        <v>0.30378</v>
+      </c>
+      <c r="P137" t="n">
+        <v>0.26644</v>
+      </c>
+      <c r="Q137" t="n">
+        <v>0.2968</v>
+      </c>
+      <c r="R137" t="n">
+        <v>0.27646</v>
+      </c>
+      <c r="S137" t="n">
+        <v>0.27734</v>
+      </c>
+      <c r="T137" t="n">
+        <v>0.22225</v>
+      </c>
+      <c r="U137" t="n">
+        <v>0.2535</v>
+      </c>
+      <c r="V137" t="n">
+        <v>0.24924</v>
+      </c>
+      <c r="W137" t="n">
+        <v>0.27437</v>
+      </c>
+      <c r="X137" t="n">
+        <v>0.24089</v>
+      </c>
+      <c r="Y137" t="n">
+        <v>0.26728</v>
+      </c>
+      <c r="Z137" t="n">
+        <v>0.27803</v>
+      </c>
+      <c r="AA137" t="n">
+        <v>0.3007</v>
+      </c>
+      <c r="AB137" t="n">
+        <v>0.43332</v>
+      </c>
+      <c r="AC137" t="n">
+        <v>0.34695</v>
+      </c>
+      <c r="AD137" t="n">
+        <v>0.33581</v>
+      </c>
+      <c r="AE137" t="n">
+        <v>0.34316</v>
+      </c>
+      <c r="AF137" t="n">
+        <v>0.24642</v>
+      </c>
+      <c r="AG137" t="n">
+        <v>0.35491</v>
+      </c>
+      <c r="AH137" t="n">
+        <v>0.62166</v>
+      </c>
+      <c r="AI137" t="n">
+        <v>0.79803</v>
+      </c>
+      <c r="AJ137" t="n">
+        <v>0.871</v>
+      </c>
+      <c r="AK137" t="n">
+        <v>0.83989</v>
+      </c>
+      <c r="AL137" t="n">
+        <v>0.32253</v>
+      </c>
+      <c r="AM137" t="n">
+        <v>0.37729</v>
+      </c>
+      <c r="AN137" t="n">
+        <v>0.10455</v>
+      </c>
+      <c r="AO137" t="n">
+        <v>0.18456</v>
+      </c>
+      <c r="AP137" t="n">
+        <v>0.28737</v>
+      </c>
+      <c r="AQ137" t="n">
+        <v>0.29272</v>
+      </c>
+      <c r="AR137" t="n">
+        <v>0.28238</v>
+      </c>
+      <c r="AS137" t="n">
+        <v>0.28515</v>
+      </c>
+      <c r="AT137" t="n">
+        <v>0.25536</v>
+      </c>
+      <c r="AU137" t="n">
+        <v>0.29547</v>
+      </c>
+      <c r="AV137" t="n">
+        <v>0.34066</v>
+      </c>
+      <c r="AW137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY137" t="n">
+        <v>0.22853</v>
+      </c>
+      <c r="AZ137" t="n">
+        <v>0.25453</v>
+      </c>
+      <c r="BA137" t="n">
+        <v>-0.00334</v>
+      </c>
+      <c r="BB137" t="n">
+        <v>0.26003</v>
+      </c>
+      <c r="BC137" t="n">
+        <v>-0.00276</v>
+      </c>
+      <c r="BD137" t="n">
+        <v>0.30705</v>
+      </c>
+      <c r="BE137" t="n">
+        <v>0.31308</v>
+      </c>
+      <c r="BF137" t="n">
+        <v>0.27773</v>
+      </c>
+      <c r="BG137" t="n">
+        <v>0.05512</v>
+      </c>
+      <c r="BH137" t="n">
+        <v>0.27075</v>
+      </c>
+      <c r="BI137" t="n">
+        <v>0.29523</v>
+      </c>
+      <c r="BJ137" t="n">
+        <v>0.27558</v>
+      </c>
+      <c r="BK137" t="n">
+        <v>0.29691</v>
+      </c>
+      <c r="BL137" t="n">
+        <v>0.25479</v>
+      </c>
+      <c r="BM137" t="n">
+        <v>0.29201</v>
+      </c>
+      <c r="BN137" t="n">
+        <v>0.46866</v>
+      </c>
+      <c r="BO137" t="n">
+        <v>0.32093</v>
+      </c>
+      <c r="BP137" t="n">
+        <v>0.32526</v>
+      </c>
+      <c r="BQ137" t="n">
+        <v>0.34523</v>
+      </c>
+      <c r="BR137" t="n">
+        <v>0.37374</v>
+      </c>
+      <c r="BS137" t="n">
+        <v>1.38523</v>
+      </c>
+      <c r="BT137" t="n">
+        <v>0.3436</v>
+      </c>
+      <c r="BU137" t="n">
+        <v>0.36744</v>
+      </c>
+      <c r="BV137" t="n">
+        <v>0.35775</v>
+      </c>
+      <c r="BW137" t="n">
+        <v>0.38687</v>
+      </c>
+      <c r="BX137" t="n">
+        <v>1.44725</v>
+      </c>
+      <c r="BY137" t="n">
+        <v>0.77391</v>
+      </c>
+      <c r="BZ137" t="n">
+        <v>0.73384</v>
+      </c>
+      <c r="CA137" t="n">
+        <v>0.7485000000000001</v>
+      </c>
+      <c r="CB137" t="n">
+        <v>1.30718</v>
+      </c>
+      <c r="CC137" t="n">
+        <v>0.97929</v>
+      </c>
+      <c r="CD137" t="n">
+        <v>0.7364700000000001</v>
+      </c>
+      <c r="CE137" t="n">
+        <v>0.81964</v>
+      </c>
+      <c r="CF137" t="n">
+        <v>0.7708700000000001</v>
+      </c>
+      <c r="CG137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CH137" t="n">
+        <v>0.83829</v>
+      </c>
+      <c r="CI137" t="n">
+        <v>0.83646</v>
+      </c>
+      <c r="CJ137" t="n">
+        <v>0.8408300000000001</v>
+      </c>
+      <c r="CK137" t="n">
+        <v>0.93791</v>
+      </c>
+      <c r="CL137" t="n">
+        <v>0.72894</v>
+      </c>
+      <c r="CM137" t="n">
+        <v>0.76677</v>
+      </c>
+      <c r="CN137" t="n">
+        <v>0.7324299999999999</v>
+      </c>
+      <c r="CO137" t="n">
+        <v>0.36658</v>
+      </c>
+      <c r="CP137" t="n">
+        <v>0.35341</v>
+      </c>
+      <c r="CQ137" t="n">
+        <v>0.3708</v>
+      </c>
+      <c r="CR137" t="n">
+        <v>0.36037</v>
+      </c>
+      <c r="CS137" t="n">
+        <v>0.36021</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="n">
+        <v>46161</v>
+      </c>
+      <c r="B138" t="n">
+        <v>0.33007</v>
+      </c>
+      <c r="C138" t="n">
+        <v>0.45816</v>
+      </c>
+      <c r="D138" t="n">
+        <v>0.59285</v>
+      </c>
+      <c r="E138" t="n">
+        <v>0.60415</v>
+      </c>
+      <c r="F138" t="n">
+        <v>0.55547</v>
+      </c>
+      <c r="G138" t="n">
+        <v>0.4915</v>
+      </c>
+      <c r="H138" t="n">
+        <v>0.45199</v>
+      </c>
+      <c r="I138" t="n">
+        <v>0.3955</v>
+      </c>
+      <c r="J138" t="n">
+        <v>0.38478</v>
+      </c>
+      <c r="K138" t="n">
+        <v>0.37927</v>
+      </c>
+      <c r="L138" t="n">
+        <v>0.36629</v>
+      </c>
+      <c r="M138" t="n">
+        <v>0.34665</v>
+      </c>
+      <c r="N138" t="n">
+        <v>0.3281</v>
+      </c>
+      <c r="O138" t="n">
+        <v>0.33206</v>
+      </c>
+      <c r="P138" t="n">
+        <v>0.32176</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>0.3132799999999999</v>
+      </c>
+      <c r="R138" t="n">
+        <v>0.47458</v>
+      </c>
+      <c r="S138" t="n">
+        <v>0.31448</v>
+      </c>
+      <c r="T138" t="n">
+        <v>0.30767</v>
+      </c>
+      <c r="U138" t="n">
+        <v>0.30917</v>
+      </c>
+      <c r="V138" t="n">
+        <v>0.29858</v>
+      </c>
+      <c r="W138" t="n">
+        <v>0.30328</v>
+      </c>
+      <c r="X138" t="n">
+        <v>0.26344</v>
+      </c>
+      <c r="Y138" t="n">
+        <v>0.3335</v>
+      </c>
+      <c r="Z138" t="n">
+        <v>0.33179</v>
+      </c>
+      <c r="AA138" t="n">
+        <v>0.3588</v>
+      </c>
+      <c r="AB138" t="n">
+        <v>0.45368</v>
+      </c>
+      <c r="AC138" t="n">
+        <v>0.4621499999999999</v>
+      </c>
+      <c r="AD138" t="n">
+        <v>0.36032</v>
+      </c>
+      <c r="AE138" t="n">
+        <v>0.37662</v>
+      </c>
+      <c r="AF138" t="n">
+        <v>0.32081</v>
+      </c>
+      <c r="AG138" t="n">
+        <v>0.31901</v>
+      </c>
+      <c r="AH138" t="n">
+        <v>0.32906</v>
+      </c>
+      <c r="AI138" t="n">
+        <v>0.41043</v>
+      </c>
+      <c r="AJ138" t="n">
+        <v>0.37555</v>
+      </c>
+      <c r="AK138" t="n">
+        <v>0.44635</v>
+      </c>
+      <c r="AL138" t="n">
+        <v>0.36222</v>
+      </c>
+      <c r="AM138" t="n">
+        <v>0.41131</v>
+      </c>
+      <c r="AN138" t="n">
+        <v>0.38936</v>
+      </c>
+      <c r="AO138" t="n">
+        <v>0.3488</v>
+      </c>
+      <c r="AP138" t="n">
+        <v>0.34435</v>
+      </c>
+      <c r="AQ138" t="n">
+        <v>0.32756</v>
+      </c>
+      <c r="AR138" t="n">
+        <v>0.38153</v>
+      </c>
+      <c r="AS138" t="n">
+        <v>0.34546</v>
+      </c>
+      <c r="AT138" t="n">
+        <v>0.31673</v>
+      </c>
+      <c r="AU138" t="n">
+        <v>0.3312</v>
+      </c>
+      <c r="AV138" t="n">
+        <v>0.33793</v>
+      </c>
+      <c r="AW138" t="n">
+        <v>0.31142</v>
+      </c>
+      <c r="AX138" t="n">
+        <v>0.26204</v>
+      </c>
+      <c r="AY138" t="n">
+        <v>0.31424</v>
+      </c>
+      <c r="AZ138" t="n">
+        <v>0.30528</v>
+      </c>
+      <c r="BA138" t="n">
+        <v>0.30539</v>
+      </c>
+      <c r="BB138" t="n">
+        <v>0.32683</v>
+      </c>
+      <c r="BC138" t="n">
+        <v>0.3236</v>
+      </c>
+      <c r="BD138" t="n">
+        <v>0.32109</v>
+      </c>
+      <c r="BE138" t="n">
+        <v>0.35234</v>
+      </c>
+      <c r="BF138" t="n">
+        <v>0.31802</v>
+      </c>
+      <c r="BG138" t="n">
+        <v>0.32908</v>
+      </c>
+      <c r="BH138" t="n">
+        <v>1.3153</v>
+      </c>
+      <c r="BI138" t="n">
+        <v>1.31689</v>
+      </c>
+      <c r="BJ138" t="n">
+        <v>1.32203</v>
+      </c>
+      <c r="BK138" t="n">
+        <v>1.33655</v>
+      </c>
+      <c r="BL138" t="n">
+        <v>1.33946</v>
+      </c>
+      <c r="BM138" t="n">
+        <v>1.32887</v>
+      </c>
+      <c r="BN138" t="n">
+        <v>0.3307</v>
+      </c>
+      <c r="BO138" t="n">
+        <v>0.32555</v>
+      </c>
+      <c r="BP138" t="n">
+        <v>0.34315</v>
+      </c>
+      <c r="BQ138" t="n">
+        <v>0.34424</v>
+      </c>
+      <c r="BR138" t="n">
+        <v>0.34151</v>
+      </c>
+      <c r="BS138" t="n">
+        <v>0.35217</v>
+      </c>
+      <c r="BT138" t="n">
+        <v>0.34211</v>
+      </c>
+      <c r="BU138" t="n">
+        <v>0.35015</v>
+      </c>
+      <c r="BV138" t="n">
+        <v>0.33348</v>
+      </c>
+      <c r="BW138" t="n">
+        <v>0.3611</v>
+      </c>
+      <c r="BX138" t="n">
+        <v>0.39997</v>
+      </c>
+      <c r="BY138" t="n">
+        <v>0.38912</v>
+      </c>
+      <c r="BZ138" t="n">
+        <v>0.37506</v>
+      </c>
+      <c r="CA138" t="n">
+        <v>0.34701</v>
+      </c>
+      <c r="CB138" t="n">
+        <v>0.37451</v>
+      </c>
+      <c r="CC138" t="n">
+        <v>0.36851</v>
+      </c>
+      <c r="CD138" t="n">
+        <v>0.42411</v>
+      </c>
+      <c r="CE138" t="n">
+        <v>0.45252</v>
+      </c>
+      <c r="CF138" t="n">
+        <v>0.7302999999999999</v>
+      </c>
+      <c r="CG138" t="n">
+        <v>0.40416</v>
+      </c>
+      <c r="CH138" t="n">
+        <v>0.596</v>
+      </c>
+      <c r="CI138" t="n">
+        <v>0.45909</v>
+      </c>
+      <c r="CJ138" t="n">
+        <v>0.37663</v>
+      </c>
+      <c r="CK138" t="n">
+        <v>0.42242</v>
+      </c>
+      <c r="CL138" t="n">
+        <v>0.41471</v>
+      </c>
+      <c r="CM138" t="n">
+        <v>0.39305</v>
+      </c>
+      <c r="CN138" t="n">
+        <v>0.47913</v>
+      </c>
+      <c r="CO138" t="n">
+        <v>0.35518</v>
+      </c>
+      <c r="CP138" t="n">
+        <v>0.35954</v>
+      </c>
+      <c r="CQ138" t="n">
+        <v>0.342</v>
+      </c>
+      <c r="CR138" t="n">
+        <v>0.34411</v>
+      </c>
+      <c r="CS138" t="n">
+        <v>0.34041</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="B139" t="n">
+        <v>0.3271</v>
+      </c>
+      <c r="C139" t="n">
+        <v>0.42283</v>
+      </c>
+      <c r="D139" t="n">
+        <v>0.42687</v>
+      </c>
+      <c r="E139" t="n">
+        <v>0.41081</v>
+      </c>
+      <c r="F139" t="n">
+        <v>0.39341</v>
+      </c>
+      <c r="G139" t="n">
+        <v>0.3864</v>
+      </c>
+      <c r="H139" t="n">
+        <v>0.38224</v>
+      </c>
+      <c r="I139" t="n">
+        <v>0.37897</v>
+      </c>
+      <c r="J139" t="n">
+        <v>0.35896</v>
+      </c>
+      <c r="K139" t="n">
+        <v>0.36206</v>
+      </c>
+      <c r="L139" t="n">
+        <v>0.35447</v>
+      </c>
+      <c r="M139" t="n">
+        <v>0.3539</v>
+      </c>
+      <c r="N139" t="n">
+        <v>0.3470299999999999</v>
+      </c>
+      <c r="O139" t="n">
+        <v>0.34925</v>
+      </c>
+      <c r="P139" t="n">
+        <v>0.34788</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>0.34258</v>
+      </c>
+      <c r="R139" t="n">
+        <v>0.35476</v>
+      </c>
+      <c r="S139" t="n">
+        <v>0.33855</v>
+      </c>
+      <c r="T139" t="n">
+        <v>0.33772</v>
+      </c>
+      <c r="U139" t="n">
+        <v>0.33213</v>
+      </c>
+      <c r="V139" t="n">
+        <v>0.33352</v>
+      </c>
+      <c r="W139" t="n">
+        <v>0.33495</v>
+      </c>
+      <c r="X139" t="n">
+        <v>0.33502</v>
+      </c>
+      <c r="Y139" t="n">
+        <v>0.34544</v>
+      </c>
+      <c r="Z139" t="n">
+        <v>0.33753</v>
+      </c>
+      <c r="AA139" t="n">
+        <v>0.35362</v>
+      </c>
+      <c r="AB139" t="n">
+        <v>0.34639</v>
+      </c>
+      <c r="AC139" t="n">
+        <v>0.35432</v>
+      </c>
+      <c r="AD139" t="n">
+        <v>0.34695</v>
+      </c>
+      <c r="AE139" t="n">
+        <v>0.35681</v>
+      </c>
+      <c r="AF139" t="n">
+        <v>0.41199</v>
+      </c>
+      <c r="AG139" t="n">
+        <v>0.36891</v>
+      </c>
+      <c r="AH139" t="n">
+        <v>0.35898</v>
+      </c>
+      <c r="AI139" t="n">
+        <v>0.56348</v>
+      </c>
+      <c r="AJ139" t="n">
+        <v>0.7677200000000001</v>
+      </c>
+      <c r="AK139" t="n">
+        <v>0.54592</v>
+      </c>
+      <c r="AL139" t="n">
+        <v>0.5253</v>
+      </c>
+      <c r="AM139" t="n">
+        <v>0.56224</v>
+      </c>
+      <c r="AN139" t="n">
+        <v>0.45346</v>
+      </c>
+      <c r="AO139" t="n">
+        <v>0.35819</v>
+      </c>
+      <c r="AP139" t="n">
+        <v>0.35344</v>
+      </c>
+      <c r="AQ139" t="n">
+        <v>0.34728</v>
+      </c>
+      <c r="AR139" t="n">
+        <v>0.3476</v>
+      </c>
+      <c r="AS139" t="n">
+        <v>0.35632</v>
+      </c>
+      <c r="AT139" t="n">
+        <v>0.34639</v>
+      </c>
+      <c r="AU139" t="n">
+        <v>0.35404</v>
+      </c>
+      <c r="AV139" t="n">
+        <v>0.38777</v>
+      </c>
+      <c r="AW139" t="n">
+        <v>0.35037</v>
+      </c>
+      <c r="AX139" t="n">
+        <v>0.30388</v>
+      </c>
+      <c r="AY139" t="n">
+        <v>0.34014</v>
+      </c>
+      <c r="AZ139" t="n">
+        <v>0.32076</v>
+      </c>
+      <c r="BA139" t="n">
+        <v>0.33471</v>
+      </c>
+      <c r="BB139" t="n">
+        <v>0.3044</v>
+      </c>
+      <c r="BC139" t="n">
+        <v>0.332</v>
+      </c>
+      <c r="BD139" t="n">
+        <v>0.3415899999999999</v>
+      </c>
+      <c r="BE139" t="n">
+        <v>0.35367</v>
+      </c>
+      <c r="BF139" t="n">
+        <v>0.32597</v>
+      </c>
+      <c r="BG139" t="n">
+        <v>0.32381</v>
+      </c>
+      <c r="BH139" t="n">
+        <v>0.31773</v>
+      </c>
+      <c r="BI139" t="n">
+        <v>0.33081</v>
+      </c>
+      <c r="BJ139" t="n">
+        <v>0.32915</v>
+      </c>
+      <c r="BK139" t="n">
+        <v>0.33371</v>
+      </c>
+      <c r="BL139" t="n">
+        <v>0.32311</v>
+      </c>
+      <c r="BM139" t="n">
+        <v>0.34624</v>
+      </c>
+      <c r="BN139" t="n">
+        <v>0.3456</v>
+      </c>
+      <c r="BO139" t="n">
+        <v>0.42567</v>
+      </c>
+      <c r="BP139" t="n">
+        <v>0.40238</v>
+      </c>
+      <c r="BQ139" t="n">
+        <v>0.47529</v>
+      </c>
+      <c r="BR139" t="n">
+        <v>0.48526</v>
+      </c>
+      <c r="BS139" t="n">
+        <v>0.8124</v>
+      </c>
+      <c r="BT139" t="n">
+        <v>0.5513899999999999</v>
+      </c>
+      <c r="BU139" t="n">
+        <v>0.42343</v>
+      </c>
+      <c r="BV139" t="n">
+        <v>0.47178</v>
+      </c>
+      <c r="BW139" t="n">
+        <v>0.54153</v>
+      </c>
+      <c r="BX139" t="n">
+        <v>0.58045</v>
+      </c>
+      <c r="BY139" t="n">
+        <v>0.83151</v>
+      </c>
+      <c r="BZ139" t="n">
+        <v>0.46793</v>
+      </c>
+      <c r="CA139" t="n">
+        <v>0.7235900000000001</v>
+      </c>
+      <c r="CB139" t="n">
+        <v>0.56463</v>
+      </c>
+      <c r="CC139" t="n">
+        <v>0.46275</v>
+      </c>
+      <c r="CD139" t="n">
+        <v>0.46178</v>
+      </c>
+      <c r="CE139" t="n">
+        <v>0.42498</v>
+      </c>
+      <c r="CF139" t="n">
+        <v>0.38178</v>
+      </c>
+      <c r="CG139" t="n">
+        <v>0.40439</v>
+      </c>
+      <c r="CH139" t="n">
+        <v>0.35781</v>
+      </c>
+      <c r="CI139" t="n">
+        <v>0.3687</v>
+      </c>
+      <c r="CJ139" t="n">
+        <v>0.35381</v>
+      </c>
+      <c r="CK139" t="n">
+        <v>0.4252</v>
+      </c>
+      <c r="CL139" t="n">
+        <v>0.38155</v>
+      </c>
+      <c r="CM139" t="n">
+        <v>0.35765</v>
+      </c>
+      <c r="CN139" t="n">
+        <v>0.38327</v>
+      </c>
+      <c r="CO139" t="n">
+        <v>0.36567</v>
+      </c>
+      <c r="CP139" t="n">
+        <v>0.2371</v>
+      </c>
+      <c r="CQ139" t="n">
+        <v>0.35811</v>
+      </c>
+      <c r="CR139" t="n">
+        <v>0.34629</v>
+      </c>
+      <c r="CS139" t="n">
+        <v>0.35436</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B140" t="n">
+        <v>0.33899</v>
+      </c>
+      <c r="C140" t="n">
+        <v>0.45673</v>
+      </c>
+      <c r="D140" t="n">
+        <v>0.38398</v>
+      </c>
+      <c r="E140" t="n">
+        <v>0.38071</v>
+      </c>
+      <c r="F140" t="n">
+        <v>0.37281</v>
+      </c>
+      <c r="G140" t="n">
+        <v>0.36786</v>
+      </c>
+      <c r="H140" t="n">
+        <v>0.34838</v>
+      </c>
+      <c r="I140" t="n">
+        <v>0.35903</v>
+      </c>
+      <c r="J140" t="n">
+        <v>0.36648</v>
+      </c>
+      <c r="K140" t="n">
+        <v>0.36322</v>
+      </c>
+      <c r="L140" t="n">
+        <v>0.36165</v>
+      </c>
+      <c r="M140" t="n">
+        <v>0.35411</v>
+      </c>
+      <c r="N140" t="n">
+        <v>0.35321</v>
+      </c>
+      <c r="O140" t="n">
+        <v>0.34941</v>
+      </c>
+      <c r="P140" t="n">
+        <v>0.34719</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>0.34855</v>
+      </c>
+      <c r="R140" t="n">
+        <v>0.34815</v>
+      </c>
+      <c r="S140" t="n">
+        <v>0.34169</v>
+      </c>
+      <c r="T140" t="n">
+        <v>0.32025</v>
+      </c>
+      <c r="U140" t="n">
+        <v>0.342</v>
+      </c>
+      <c r="V140" t="n">
+        <v>0.33637</v>
+      </c>
+      <c r="W140" t="n">
+        <v>0.33425</v>
+      </c>
+      <c r="X140" t="n">
+        <v>0.33266</v>
+      </c>
+      <c r="Y140" t="n">
+        <v>0.34168</v>
+      </c>
+      <c r="Z140" t="n">
+        <v>0.34229</v>
+      </c>
+      <c r="AA140" t="n">
+        <v>0.35223</v>
+      </c>
+      <c r="AB140" t="n">
+        <v>0.37481</v>
+      </c>
+      <c r="AC140" t="n">
+        <v>0.35531</v>
+      </c>
+      <c r="AD140" t="n">
+        <v>0.35736</v>
+      </c>
+      <c r="AE140" t="n">
+        <v>0.34638</v>
+      </c>
+      <c r="AF140" t="n">
+        <v>0.35211</v>
+      </c>
+      <c r="AG140" t="n">
+        <v>0.35084</v>
+      </c>
+      <c r="AH140" t="n">
+        <v>0.35039</v>
+      </c>
+      <c r="AI140" t="n">
+        <v>0.38217</v>
+      </c>
+      <c r="AJ140" t="n">
+        <v>0.39165</v>
+      </c>
+      <c r="AK140" t="n">
+        <v>0.36675</v>
+      </c>
+      <c r="AL140" t="n">
+        <v>0.35425</v>
+      </c>
+      <c r="AM140" t="n">
+        <v>0.43549</v>
+      </c>
+      <c r="AN140" t="n">
+        <v>0.38038</v>
+      </c>
+      <c r="AO140" t="n">
+        <v>0.36358</v>
+      </c>
+      <c r="AP140" t="n">
+        <v>0.37855</v>
+      </c>
+      <c r="AQ140" t="n">
+        <v>0.35656</v>
+      </c>
+      <c r="AR140" t="n">
+        <v>0.31064</v>
+      </c>
+      <c r="AS140" t="n">
+        <v>0.36365</v>
+      </c>
+      <c r="AT140" t="n">
+        <v>0.3055</v>
+      </c>
+      <c r="AU140" t="n">
+        <v>0.36747</v>
+      </c>
+      <c r="AV140" t="n">
+        <v>0.36076</v>
+      </c>
+      <c r="AW140" t="n">
+        <v>0.35223</v>
+      </c>
+      <c r="AX140" t="n">
+        <v>0.29256</v>
+      </c>
+      <c r="AY140" t="n">
+        <v>0.32802</v>
+      </c>
+      <c r="AZ140" t="n">
+        <v>0.33232</v>
+      </c>
+      <c r="BA140" t="n">
+        <v>0.33841</v>
+      </c>
+      <c r="BB140" t="n">
+        <v>0.32193</v>
+      </c>
+      <c r="BC140" t="n">
+        <v>0.31608</v>
+      </c>
+      <c r="BD140" t="n">
+        <v>0.33648</v>
+      </c>
+      <c r="BE140" t="n">
+        <v>0.3436</v>
+      </c>
+      <c r="BF140" t="n">
+        <v>0.3253</v>
+      </c>
+      <c r="BG140" t="n">
+        <v>0.33364</v>
+      </c>
+      <c r="BH140" t="n">
+        <v>0.3420299999999999</v>
+      </c>
+      <c r="BI140" t="n">
+        <v>0.3385</v>
+      </c>
+      <c r="BJ140" t="n">
+        <v>0.32493</v>
+      </c>
+      <c r="BK140" t="n">
+        <v>0.34429</v>
+      </c>
+      <c r="BL140" t="n">
+        <v>0.34375</v>
+      </c>
+      <c r="BM140" t="n">
+        <v>0.37069</v>
+      </c>
+      <c r="BN140" t="n">
+        <v>0.3669</v>
+      </c>
+      <c r="BO140" t="n">
+        <v>0.37288</v>
+      </c>
+      <c r="BP140" t="n">
+        <v>0.36949</v>
+      </c>
+      <c r="BQ140" t="n">
+        <v>0.37721</v>
+      </c>
+      <c r="BR140" t="n">
+        <v>0.39488</v>
+      </c>
+      <c r="BS140" t="n">
+        <v>0.37452</v>
+      </c>
+      <c r="BT140" t="n">
+        <v>0.37499</v>
+      </c>
+      <c r="BU140" t="n">
+        <v>0.41926</v>
+      </c>
+      <c r="BV140" t="n">
+        <v>0.41447</v>
+      </c>
+      <c r="BW140" t="n">
+        <v>0.53134</v>
+      </c>
+      <c r="BX140" t="n">
+        <v>0.5900599999999999</v>
+      </c>
+      <c r="BY140" t="n">
+        <v>0.73825</v>
+      </c>
+      <c r="BZ140" t="n">
+        <v>0.67684</v>
+      </c>
+      <c r="CA140" t="n">
+        <v>0.74119</v>
+      </c>
+      <c r="CB140" t="n">
+        <v>0.69224</v>
+      </c>
+      <c r="CC140" t="n">
+        <v>0.49392</v>
+      </c>
+      <c r="CD140" t="n">
+        <v>0.5825199999999999</v>
+      </c>
+      <c r="CE140" t="n">
+        <v>0.62963</v>
+      </c>
+      <c r="CF140" t="n">
+        <v>0.48632</v>
+      </c>
+      <c r="CG140" t="n">
+        <v>0.79326</v>
+      </c>
+      <c r="CH140" t="n">
+        <v>0.767</v>
+      </c>
+      <c r="CI140" t="n">
+        <v>1.01378</v>
+      </c>
+      <c r="CJ140" t="n">
+        <v>0.8901</v>
+      </c>
+      <c r="CK140" t="n">
+        <v>0.8160499999999999</v>
+      </c>
+      <c r="CL140" t="n">
+        <v>0.78252</v>
+      </c>
+      <c r="CM140" t="n">
+        <v>0.38883</v>
+      </c>
+      <c r="CN140" t="n">
+        <v>0.43915</v>
+      </c>
+      <c r="CO140" t="n">
+        <v>0.38315</v>
+      </c>
+      <c r="CP140" t="n">
+        <v>0.36111</v>
+      </c>
+      <c r="CQ140" t="n">
+        <v>0.36474</v>
+      </c>
+      <c r="CR140" t="n">
+        <v>0.35437</v>
+      </c>
+      <c r="CS140" t="n">
+        <v>0.35874</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="n">
+        <v>46164</v>
+      </c>
+      <c r="B141" t="n">
+        <v>0.30292</v>
+      </c>
+      <c r="C141" t="n">
+        <v>0.35914</v>
+      </c>
+      <c r="D141" t="n">
+        <v>0.35959</v>
+      </c>
+      <c r="E141" t="n">
+        <v>0.35077</v>
+      </c>
+      <c r="F141" t="n">
+        <v>0.34992</v>
+      </c>
+      <c r="G141" t="n">
+        <v>0.34073</v>
+      </c>
+      <c r="H141" t="n">
+        <v>0.32975</v>
+      </c>
+      <c r="I141" t="n">
+        <v>0.34025</v>
+      </c>
+      <c r="J141" t="n">
+        <v>0.33421</v>
+      </c>
+      <c r="K141" t="n">
+        <v>0.33474</v>
+      </c>
+      <c r="L141" t="n">
+        <v>0.34379</v>
+      </c>
+      <c r="M141" t="n">
+        <v>0.32494</v>
+      </c>
+      <c r="N141" t="n">
+        <v>0.36985</v>
+      </c>
+      <c r="O141" t="n">
+        <v>0.3434700000000001</v>
+      </c>
+      <c r="P141" t="n">
+        <v>0.33335</v>
+      </c>
+      <c r="Q141" t="n">
+        <v>0.34162</v>
+      </c>
+      <c r="R141" t="n">
+        <v>0.33783</v>
+      </c>
+      <c r="S141" t="n">
+        <v>0.24565</v>
+      </c>
+      <c r="T141" t="n">
+        <v>0.327</v>
+      </c>
+      <c r="U141" t="n">
+        <v>0.3296</v>
+      </c>
+      <c r="V141" t="n">
+        <v>0.3384</v>
+      </c>
+      <c r="W141" t="n">
+        <v>0.32979</v>
+      </c>
+      <c r="X141" t="n">
+        <v>0.33374</v>
+      </c>
+      <c r="Y141" t="n">
+        <v>0.3461</v>
+      </c>
+      <c r="Z141" t="n">
+        <v>0.34664</v>
+      </c>
+      <c r="AA141" t="n">
+        <v>0.34136</v>
+      </c>
+      <c r="AB141" t="n">
+        <v>0.37627</v>
+      </c>
+      <c r="AC141" t="n">
+        <v>0.37531</v>
+      </c>
+      <c r="AD141" t="n">
+        <v>0.35286</v>
+      </c>
+      <c r="AE141" t="n">
+        <v>0.34139</v>
+      </c>
+      <c r="AF141" t="n">
+        <v>0.33879</v>
+      </c>
+      <c r="AG141" t="n">
+        <v>0.3388</v>
+      </c>
+      <c r="AH141" t="n">
+        <v>0.3655</v>
+      </c>
+      <c r="AI141" t="n">
+        <v>0.33491</v>
+      </c>
+      <c r="AJ141" t="n">
+        <v>0.34927</v>
+      </c>
+      <c r="AK141" t="n">
+        <v>0.35314</v>
+      </c>
+      <c r="AL141" t="n">
+        <v>0.3367</v>
+      </c>
+      <c r="AM141" t="n">
+        <v>0.34619</v>
+      </c>
+      <c r="AN141" t="n">
+        <v>0.33999</v>
+      </c>
+      <c r="AO141" t="n">
+        <v>0.22636</v>
+      </c>
+      <c r="AP141" t="n">
+        <v>0.30148</v>
+      </c>
+      <c r="AQ141" t="n">
+        <v>0.30136</v>
+      </c>
+      <c r="AR141" t="n">
+        <v>0.20034</v>
+      </c>
+      <c r="AS141" t="n">
+        <v>0.35979</v>
+      </c>
+      <c r="AT141" t="n">
+        <v>0.33767</v>
+      </c>
+      <c r="AU141" t="n">
+        <v>0.30504</v>
+      </c>
+      <c r="AV141" t="n">
+        <v>0.26116</v>
+      </c>
+      <c r="AW141" t="n">
+        <v>0.25893</v>
+      </c>
+      <c r="AX141" t="n">
+        <v>0.16104</v>
+      </c>
+      <c r="AY141" t="n">
+        <v>0.13651</v>
+      </c>
+      <c r="AZ141" t="n">
+        <v>0.30501</v>
+      </c>
+      <c r="BA141" t="n">
+        <v>0.27427</v>
+      </c>
+      <c r="BB141" t="n">
+        <v>0.20269</v>
+      </c>
+      <c r="BC141" t="n">
+        <v>0.3817</v>
+      </c>
+      <c r="BD141" t="n">
+        <v>0.22731</v>
+      </c>
+      <c r="BE141" t="n">
+        <v>0.1729</v>
+      </c>
+      <c r="BF141" t="n">
+        <v>0.25265</v>
+      </c>
+      <c r="BG141" t="n">
+        <v>0.15886</v>
+      </c>
+      <c r="BH141" t="n">
+        <v>0.30129</v>
+      </c>
+      <c r="BI141" t="n">
+        <v>0.25829</v>
+      </c>
+      <c r="BJ141" t="n">
+        <v>0.22114</v>
+      </c>
+      <c r="BK141" t="n">
+        <v>0.23654</v>
+      </c>
+      <c r="BL141" t="n">
+        <v>0.32066</v>
+      </c>
+      <c r="BM141" t="n">
+        <v>0.34743</v>
+      </c>
+      <c r="BN141" t="n">
+        <v>0.34083</v>
+      </c>
+      <c r="BO141" t="n">
+        <v>0.32366</v>
+      </c>
+      <c r="BP141" t="n">
+        <v>0.35836</v>
+      </c>
+      <c r="BQ141" t="n">
+        <v>0.36329</v>
+      </c>
+      <c r="BR141" t="n">
+        <v>0.35051</v>
+      </c>
+      <c r="BS141" t="n">
+        <v>0.38595</v>
+      </c>
+      <c r="BT141" t="n">
+        <v>0.36756</v>
+      </c>
+      <c r="BU141" t="n">
+        <v>0.35579</v>
+      </c>
+      <c r="BV141" t="n">
+        <v>0.36796</v>
+      </c>
+      <c r="BW141" t="n">
+        <v>0.37227</v>
+      </c>
+      <c r="BX141" t="n">
+        <v>0.36921</v>
+      </c>
+      <c r="BY141" t="n">
+        <v>0.39469</v>
+      </c>
+      <c r="BZ141" t="n">
+        <v>0.35505</v>
+      </c>
+      <c r="CA141" t="n">
+        <v>0.39201</v>
+      </c>
+      <c r="CB141" t="n">
+        <v>0.50164</v>
+      </c>
+      <c r="CC141" t="n">
+        <v>0.41638</v>
+      </c>
+      <c r="CD141" t="n">
+        <v>0.41589</v>
+      </c>
+      <c r="CE141" t="n">
+        <v>0.44634</v>
+      </c>
+      <c r="CF141" t="n">
+        <v>0.446</v>
+      </c>
+      <c r="CG141" t="n">
+        <v>0.44432</v>
+      </c>
+      <c r="CH141" t="n">
+        <v>0.39541</v>
+      </c>
+      <c r="CI141" t="n">
+        <v>0.43235</v>
+      </c>
+      <c r="CJ141" t="n">
+        <v>0.39748</v>
+      </c>
+      <c r="CK141" t="n">
+        <v>0.39623</v>
+      </c>
+      <c r="CL141" t="n">
+        <v>0.40023</v>
+      </c>
+      <c r="CM141" t="n">
+        <v>0.37225</v>
+      </c>
+      <c r="CN141" t="n">
+        <v>0.40914</v>
+      </c>
+      <c r="CO141" t="n">
+        <v>0.37094</v>
+      </c>
+      <c r="CP141" t="n">
+        <v>0.36633</v>
+      </c>
+      <c r="CQ141" t="n">
+        <v>0.35315</v>
+      </c>
+      <c r="CR141" t="n">
+        <v>0.34557</v>
+      </c>
+      <c r="CS141" t="n">
+        <v>0.365</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="n">
+        <v>46165</v>
+      </c>
+      <c r="B142" t="n">
+        <v>0.34236</v>
+      </c>
+      <c r="C142" t="n">
+        <v>0.94675</v>
+      </c>
+      <c r="D142" t="n">
+        <v>0.40111</v>
+      </c>
+      <c r="E142" t="n">
+        <v>0.60807</v>
+      </c>
+      <c r="F142" t="n">
+        <v>0.50497</v>
+      </c>
+      <c r="G142" t="n">
+        <v>0.41331</v>
+      </c>
+      <c r="H142" t="n">
+        <v>0.36661</v>
+      </c>
+      <c r="I142" t="n">
+        <v>0.46631</v>
+      </c>
+      <c r="J142" t="n">
+        <v>0.37098</v>
+      </c>
+      <c r="K142" t="n">
+        <v>0.38694</v>
+      </c>
+      <c r="L142" t="n">
+        <v>0.37109</v>
+      </c>
+      <c r="M142" t="n">
+        <v>0.36862</v>
+      </c>
+      <c r="N142" t="n">
+        <v>0.37179</v>
+      </c>
+      <c r="O142" t="n">
+        <v>0.36883</v>
+      </c>
+      <c r="P142" t="n">
+        <v>0.36455</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>0.36994</v>
+      </c>
+      <c r="R142" t="n">
+        <v>0.36842</v>
+      </c>
+      <c r="S142" t="n">
+        <v>0.3666</v>
+      </c>
+      <c r="T142" t="n">
+        <v>0.36756</v>
+      </c>
+      <c r="U142" t="n">
+        <v>0.36349</v>
+      </c>
+      <c r="V142" t="n">
+        <v>0.35783</v>
+      </c>
+      <c r="W142" t="n">
+        <v>0.36341</v>
+      </c>
+      <c r="X142" t="n">
+        <v>0.36251</v>
+      </c>
+      <c r="Y142" t="n">
+        <v>0.36125</v>
+      </c>
+      <c r="Z142" t="n">
+        <v>0.35963</v>
+      </c>
+      <c r="AA142" t="n">
+        <v>0.3503</v>
+      </c>
+      <c r="AB142" t="n">
+        <v>0.35753</v>
+      </c>
+      <c r="AC142" t="n">
+        <v>0.35333</v>
+      </c>
+      <c r="AD142" t="n">
+        <v>0.37164</v>
+      </c>
+      <c r="AE142" t="n">
+        <v>0.35753</v>
+      </c>
+      <c r="AF142" t="n">
+        <v>0.34532</v>
+      </c>
+      <c r="AG142" t="n">
+        <v>0.34749</v>
+      </c>
+      <c r="AH142" t="n">
+        <v>0.35272</v>
+      </c>
+      <c r="AI142" t="n">
+        <v>0.35978</v>
+      </c>
+      <c r="AJ142" t="n">
+        <v>0.36168</v>
+      </c>
+      <c r="AK142" t="n">
+        <v>0.35602</v>
+      </c>
+      <c r="AL142" t="n">
+        <v>0.34188</v>
+      </c>
+      <c r="AM142" t="n">
+        <v>0.37705</v>
+      </c>
+      <c r="AN142" t="n">
+        <v>0.36432</v>
+      </c>
+      <c r="AO142" t="n">
+        <v>0.36235</v>
+      </c>
+      <c r="AP142" t="n">
+        <v>0.36736</v>
+      </c>
+      <c r="AQ142" t="n">
+        <v>0.29853</v>
+      </c>
+      <c r="AR142" t="n">
+        <v>0.36198</v>
+      </c>
+      <c r="AS142" t="n">
+        <v>0.36565</v>
+      </c>
+      <c r="AT142" t="n">
+        <v>0.36562</v>
+      </c>
+      <c r="AU142" t="n">
+        <v>0.54312</v>
+      </c>
+      <c r="AV142" t="n">
+        <v>0.33325</v>
+      </c>
+      <c r="AW142" t="n">
+        <v>0.37425</v>
+      </c>
+      <c r="AX142" t="n">
+        <v>0.33433</v>
+      </c>
+      <c r="AY142" t="n">
+        <v>0.35088</v>
+      </c>
+      <c r="AZ142" t="n">
+        <v>0.37028</v>
+      </c>
+      <c r="BA142" t="n">
+        <v>0.37211</v>
+      </c>
+      <c r="BB142" t="n">
+        <v>0.42463</v>
+      </c>
+      <c r="BC142" t="n">
+        <v>0.38128</v>
+      </c>
+      <c r="BD142" t="n">
+        <v>0.41728</v>
+      </c>
+      <c r="BE142" t="n">
+        <v>0.48764</v>
+      </c>
+      <c r="BF142" t="n">
+        <v>0.35058</v>
+      </c>
+      <c r="BG142" t="n">
+        <v>0.32093</v>
+      </c>
+      <c r="BH142" t="n">
+        <v>0.35195</v>
+      </c>
+      <c r="BI142" t="n">
+        <v>0.34808</v>
+      </c>
+      <c r="BJ142" t="n">
+        <v>0.32348</v>
+      </c>
+      <c r="BK142" t="n">
+        <v>0.35929</v>
+      </c>
+      <c r="BL142" t="n">
+        <v>0.36152</v>
+      </c>
+      <c r="BM142" t="n">
+        <v>0.33455</v>
+      </c>
+      <c r="BN142" t="n">
+        <v>0.35862</v>
+      </c>
+      <c r="BO142" t="n">
+        <v>0.35027</v>
+      </c>
+      <c r="BP142" t="n">
+        <v>0.35568</v>
+      </c>
+      <c r="BQ142" t="n">
+        <v>0.38425</v>
+      </c>
+      <c r="BR142" t="n">
+        <v>0.38389</v>
+      </c>
+      <c r="BS142" t="n">
+        <v>0.42957</v>
+      </c>
+      <c r="BT142" t="n">
+        <v>0.40951</v>
+      </c>
+      <c r="BU142" t="n">
+        <v>0.39719</v>
+      </c>
+      <c r="BV142" t="n">
+        <v>0.35756</v>
+      </c>
+      <c r="BW142" t="n">
+        <v>0.36494</v>
+      </c>
+      <c r="BX142" t="n">
+        <v>0.38459</v>
+      </c>
+      <c r="BY142" t="n">
+        <v>0.37887</v>
+      </c>
+      <c r="BZ142" t="n">
+        <v>0.35925</v>
+      </c>
+      <c r="CA142" t="n">
+        <v>0.37126</v>
+      </c>
+      <c r="CB142" t="n">
+        <v>0.38009</v>
+      </c>
+      <c r="CC142" t="n">
+        <v>0.37171</v>
+      </c>
+      <c r="CD142" t="n">
+        <v>0.37921</v>
+      </c>
+      <c r="CE142" t="n">
+        <v>0.38515</v>
+      </c>
+      <c r="CF142" t="n">
+        <v>0.37301</v>
+      </c>
+      <c r="CG142" t="n">
+        <v>0.38614</v>
+      </c>
+      <c r="CH142" t="n">
+        <v>0.39327</v>
+      </c>
+      <c r="CI142" t="n">
+        <v>0.43079</v>
+      </c>
+      <c r="CJ142" t="n">
+        <v>0.37855</v>
+      </c>
+      <c r="CK142" t="n">
+        <v>0.37285</v>
+      </c>
+      <c r="CL142" t="n">
+        <v>0.42086</v>
+      </c>
+      <c r="CM142" t="n">
+        <v>0.39255</v>
+      </c>
+      <c r="CN142" t="n">
+        <v>0.39622</v>
+      </c>
+      <c r="CO142" t="n">
+        <v>0.34967</v>
+      </c>
+      <c r="CP142" t="n">
+        <v>0.35786</v>
+      </c>
+      <c r="CQ142" t="n">
+        <v>0.35778</v>
+      </c>
+      <c r="CR142" t="n">
+        <v>0.35877</v>
+      </c>
+      <c r="CS142" t="n">
+        <v>0.3595</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="n">
+        <v>46166</v>
+      </c>
+      <c r="B143" t="n">
+        <v>0.3479</v>
+      </c>
+      <c r="C143" t="n">
+        <v>0.41101</v>
+      </c>
+      <c r="D143" t="n">
+        <v>0.38556</v>
+      </c>
+      <c r="E143" t="n">
+        <v>0.36955</v>
+      </c>
+      <c r="F143" t="n">
+        <v>0.37051</v>
+      </c>
+      <c r="G143" t="n">
+        <v>0.37664</v>
+      </c>
+      <c r="H143" t="n">
+        <v>0.37501</v>
+      </c>
+      <c r="I143" t="n">
+        <v>0.36811</v>
+      </c>
+      <c r="J143" t="n">
+        <v>0.36998</v>
+      </c>
+      <c r="K143" t="n">
+        <v>0.36113</v>
+      </c>
+      <c r="L143" t="n">
+        <v>0.36844</v>
+      </c>
+      <c r="M143" t="n">
+        <v>0.35813</v>
+      </c>
+      <c r="N143" t="n">
+        <v>0.36012</v>
+      </c>
+      <c r="O143" t="n">
+        <v>0.36219</v>
+      </c>
+      <c r="P143" t="n">
+        <v>0.3543</v>
+      </c>
+      <c r="Q143" t="n">
+        <v>0.36489</v>
+      </c>
+      <c r="R143" t="n">
+        <v>0.35153</v>
+      </c>
+      <c r="S143" t="n">
+        <v>0.3575</v>
+      </c>
+      <c r="T143" t="n">
+        <v>0.35772</v>
+      </c>
+      <c r="U143" t="n">
+        <v>0.35824</v>
+      </c>
+      <c r="V143" t="n">
+        <v>0.35371</v>
+      </c>
+      <c r="W143" t="n">
+        <v>0.35436</v>
+      </c>
+      <c r="X143" t="n">
+        <v>0.35643</v>
+      </c>
+      <c r="Y143" t="n">
+        <v>0.3551</v>
+      </c>
+      <c r="Z143" t="n">
+        <v>0.35774</v>
+      </c>
+      <c r="AA143" t="n">
+        <v>0.34911</v>
+      </c>
+      <c r="AB143" t="n">
+        <v>0.34289</v>
+      </c>
+      <c r="AC143" t="n">
+        <v>0.35515</v>
+      </c>
+      <c r="AD143" t="n">
+        <v>0.34895</v>
+      </c>
+      <c r="AE143" t="n">
+        <v>0.34968</v>
+      </c>
+      <c r="AF143" t="n">
+        <v>0.31194</v>
+      </c>
+      <c r="AG143" t="n">
+        <v>0.31551</v>
+      </c>
+      <c r="AH143" t="n">
+        <v>0.32032</v>
+      </c>
+      <c r="AI143" t="n">
+        <v>0.17476</v>
+      </c>
+      <c r="AJ143" t="n">
+        <v>0.30835</v>
+      </c>
+      <c r="AK143" t="n">
+        <v>0.29294</v>
+      </c>
+      <c r="AL143" t="n">
+        <v>0.30897</v>
+      </c>
+      <c r="AM143" t="n">
+        <v>0.14447</v>
+      </c>
+      <c r="AN143" t="n">
+        <v>0.19677</v>
+      </c>
+      <c r="AO143" t="n">
+        <v>0.13812</v>
+      </c>
+      <c r="AP143" t="n">
+        <v>0.29685</v>
+      </c>
+      <c r="AQ143" t="n">
+        <v>0.04135</v>
+      </c>
+      <c r="AR143" t="n">
+        <v>0.1238</v>
+      </c>
+      <c r="AS143" t="n">
+        <v>0.33075</v>
+      </c>
+      <c r="AT143" t="n">
+        <v>0.23041</v>
+      </c>
+      <c r="AU143" t="n">
+        <v>0.27946</v>
+      </c>
+      <c r="AV143" t="n">
+        <v>0.1621</v>
+      </c>
+      <c r="AW143" t="n">
+        <v>0.14379</v>
+      </c>
+      <c r="AX143" t="n">
+        <v>0.30061</v>
+      </c>
+      <c r="AY143" t="n">
+        <v>0.20801</v>
+      </c>
+      <c r="AZ143" t="n">
+        <v>0.31169</v>
+      </c>
+      <c r="BA143" t="n">
+        <v>0.22475</v>
+      </c>
+      <c r="BB143" t="n">
+        <v>0.26142</v>
+      </c>
+      <c r="BC143" t="n">
+        <v>0.15287</v>
+      </c>
+      <c r="BD143" t="n">
+        <v>0.35009</v>
+      </c>
+      <c r="BE143" t="n">
+        <v>0.30579</v>
+      </c>
+      <c r="BF143" t="n">
+        <v>0.14549</v>
+      </c>
+      <c r="BG143" t="n">
+        <v>0.33876</v>
+      </c>
+      <c r="BH143" t="n">
+        <v>0.28792</v>
+      </c>
+      <c r="BI143" t="n">
+        <v>0.19601</v>
+      </c>
+      <c r="BJ143" t="n">
+        <v>0.14301</v>
+      </c>
+      <c r="BK143" t="n">
+        <v>0.27879</v>
+      </c>
+      <c r="BL143" t="n">
+        <v>0.25588</v>
+      </c>
+      <c r="BM143" t="n">
+        <v>0.32269</v>
+      </c>
+      <c r="BN143" t="n">
+        <v>0.31929</v>
+      </c>
+      <c r="BO143" t="n">
+        <v>0.31205</v>
+      </c>
+      <c r="BP143" t="n">
+        <v>0.30651</v>
+      </c>
+      <c r="BQ143" t="n">
+        <v>0.3445299999999999</v>
+      </c>
+      <c r="BR143" t="n">
+        <v>0.35106</v>
+      </c>
+      <c r="BS143" t="n">
+        <v>0.36481</v>
+      </c>
+      <c r="BT143" t="n">
+        <v>0.35508</v>
+      </c>
+      <c r="BU143" t="n">
+        <v>0.35874</v>
+      </c>
+      <c r="BV143" t="n">
+        <v>0.3618</v>
+      </c>
+      <c r="BW143" t="n">
+        <v>0.38476</v>
+      </c>
+      <c r="BX143" t="n">
+        <v>0.39195</v>
+      </c>
+      <c r="BY143" t="n">
+        <v>0.37444</v>
+      </c>
+      <c r="BZ143" t="n">
+        <v>0.35855</v>
+      </c>
+      <c r="CA143" t="n">
+        <v>0.40324</v>
+      </c>
+      <c r="CB143" t="n">
+        <v>0.35612</v>
+      </c>
+      <c r="CC143" t="n">
+        <v>0.37211</v>
+      </c>
+      <c r="CD143" t="n">
+        <v>0.37295</v>
+      </c>
+      <c r="CE143" t="n">
+        <v>0.36556</v>
+      </c>
+      <c r="CF143" t="n">
+        <v>0.37836</v>
+      </c>
+      <c r="CG143" t="n">
+        <v>0.39048</v>
+      </c>
+      <c r="CH143" t="n">
+        <v>0.38189</v>
+      </c>
+      <c r="CI143" t="n">
+        <v>0.37801</v>
+      </c>
+      <c r="CJ143" t="n">
+        <v>0.39621</v>
+      </c>
+      <c r="CK143" t="n">
+        <v>0.46876</v>
+      </c>
+      <c r="CL143" t="n">
+        <v>0.39399</v>
+      </c>
+      <c r="CM143" t="n">
+        <v>0.39306</v>
+      </c>
+      <c r="CN143" t="n">
+        <v>0.38393</v>
+      </c>
+      <c r="CO143" t="n">
+        <v>0.39065</v>
+      </c>
+      <c r="CP143" t="n">
+        <v>0.38032</v>
+      </c>
+      <c r="CQ143" t="n">
+        <v>0.37955</v>
+      </c>
+      <c r="CR143" t="n">
+        <v>0.38416</v>
+      </c>
+      <c r="CS143" t="n">
+        <v>0.38465</v>
       </c>
     </row>
   </sheetData>
